--- a/output/BIFM_UT_Processing_Report.xlsx
+++ b/output/BIFM_UT_Processing_Report.xlsx
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -476,7 +476,73 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ADD - GOI</t>
+          <t>STATIC - AMOLEMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>DIS - AMOLEMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>DEBIT</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>DEBIT - AMOLEMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ADD - AMOLEMO</t>
         </is>
       </c>
     </row>
@@ -593,12 +659,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="27" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
@@ -651,17 +717,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-29T12:30:36</t>
+          <t>2026-06-29T14:13:19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ADD - GOI.pdf</t>
+          <t>STATIC - AMOLEMO.pdf</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>STATIC_NA_UNKNOWN_20260629.pdf</t>
+          <t>STATIC_NA_UNKNOWN_20260629_1_2.pdf</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -679,10 +745,130 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\STATIC_NA_UNKNOWN_20260629.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\STATIC_NA_UNKNOWN_20260629_1_2.pdf</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
+        <is>
+          <t>marvel.ai-local-poc</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-06-29T14:15:07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>DIS - AMOLEMO.pdf</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>DIS_NA_UNKNOWN_20260629_1.pdf</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>95</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>NOT_EXTRACTED</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\DIS_NA_UNKNOWN_20260629_1.pdf</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>marvel.ai-local-poc</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-06-29T14:16:55</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>DEBIT - AMOLEMO.pdf</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>DEBIT_NA_UNKNOWN_20260629_1.pdf</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>DEBIT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>95</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>NOT_EXTRACTED</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\DEBIT_NA_UNKNOWN_20260629_1.pdf</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>marvel.ai-local-poc</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-06-29T14:18:51</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ADD - AMOLEMO.pdf</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ADD_NA_UNKNOWN_20260629_1.pdf</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>95</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>NOT_EXTRACTED</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\ADD_NA_UNKNOWN_20260629_1.pdf</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>marvel.ai-local-poc</t>
         </is>

--- a/output/BIFM_UT_Processing_Report.xlsx
+++ b/output/BIFM_UT_Processing_Report.xlsx
@@ -33,7 +33,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -44,6 +44,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="00305496"/>
         <bgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -59,9 +71,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -427,124 +441,668 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:AB7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="37" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="42" customWidth="1" min="11" max="11"/>
+    <col width="27" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="21" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="18" customWidth="1" min="21" max="21"/>
+    <col width="18" customWidth="1" min="22" max="22"/>
+    <col width="23" customWidth="1" min="23" max="23"/>
+    <col width="19" customWidth="1" min="24" max="24"/>
+    <col width="19" customWidth="1" min="25" max="25"/>
+    <col width="18" customWidth="1" min="26" max="26"/>
+    <col width="21" customWidth="1" min="27" max="27"/>
+    <col width="22" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>source_file</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>form_code</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>form_type</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>entity_number</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>form_code</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>full_name</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_number</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>date_of_birth</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>fund_name</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>fund_number</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>fund_category</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>processing_cutoff</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>overall_validation_status</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>source_file</t>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>contact_number</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>account_number</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>bank_name</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>branch_code</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>change_type</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>disinvestment_amount</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>instruction_mode</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>instruction_type</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>kyc_certified_id</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>kyc_completeness_flag</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>kyc_proof_address</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>kyc_proof_banking</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>kyc_proof_source</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>static_sub_type</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>sub_instruction_type</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>report_ADD</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Additional Investment Form</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>ENT001</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Boitumelo Tau</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>BIFM Pula Money Market Fund</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>MM001</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Money Market</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>12:00 PM</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>75123456</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>b.tau@email.bw</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr"/>
+      <c r="P2" s="2" t="inlineStr"/>
+      <c r="Q2" s="2" t="inlineStr"/>
+      <c r="R2" s="2" t="inlineStr"/>
+      <c r="S2" s="2" t="inlineStr"/>
+      <c r="T2" s="2" t="inlineStr"/>
+      <c r="U2" s="2" t="inlineStr"/>
+      <c r="V2" s="2" t="inlineStr"/>
+      <c r="W2" s="2" t="inlineStr"/>
+      <c r="X2" s="2" t="inlineStr"/>
+      <c r="Y2" s="2" t="inlineStr"/>
+      <c r="Z2" s="2" t="inlineStr"/>
+      <c r="AA2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>report_DEBIT</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>DEBIT</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Debit Order Form</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>ENT002</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Mpho Setlhare</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>BIFM Balanced Prudential Fund</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Non-Money Market</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>3:00 PM</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>76234567</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr"/>
+      <c r="O3" s="2" t="inlineStr"/>
+      <c r="P3" s="2" t="inlineStr"/>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>282672</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr"/>
+      <c r="S3" s="2" t="inlineStr"/>
+      <c r="T3" s="2" t="inlineStr"/>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t>New debit order</t>
+        </is>
+      </c>
+      <c r="V3" s="2" t="inlineStr"/>
+      <c r="W3" s="2" t="inlineStr"/>
+      <c r="X3" s="2" t="inlineStr"/>
+      <c r="Y3" s="2" t="inlineStr"/>
+      <c r="Z3" s="2" t="inlineStr"/>
+      <c r="AA3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>report_DIS</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Disinvestment Form (Standard)</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>ENT003</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Lesedi Motswana</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>BIFM Local Equity Fund</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Non-Money Market</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>3:00 PM</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>77345678</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr"/>
+      <c r="O4" s="2" t="inlineStr"/>
+      <c r="P4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>282672</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr"/>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>25000</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>Partial Amount</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr"/>
+      <c r="V4" s="2" t="inlineStr"/>
+      <c r="W4" s="2" t="inlineStr"/>
+      <c r="X4" s="2" t="inlineStr"/>
+      <c r="Y4" s="2" t="inlineStr"/>
+      <c r="Z4" s="2" t="inlineStr"/>
+      <c r="AA4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>report_DIS_GSG</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>DIS_GSG</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Disinvestment Form (GSGF)</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>ENT004</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Olebogeng Moeti</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>BIFM Global Sustainable Growth Fund</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Non-Money Market (GSGF)</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>Quarterly - 7th of last month of quarter</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>78456789</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>282672</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr"/>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>Partial Amount</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr"/>
+      <c r="V5" s="2" t="inlineStr"/>
+      <c r="W5" s="2" t="inlineStr"/>
+      <c r="X5" s="2" t="inlineStr"/>
+      <c r="Y5" s="2" t="inlineStr"/>
+      <c r="Z5" s="2" t="inlineStr"/>
+      <c r="AA5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>report_STATIC</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>STATIC</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>STATIC - AMOLEMO</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>DIS - AMOLEMO</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>DEBIT</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>DEBIT - AMOLEMO</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>ADD - AMOLEMO</t>
-        </is>
-      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Static / Change of Investor Details Form</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>ENT005</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Tlotlo Kgosidintsi</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>9100987654</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>Stanbic Bank</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>060144</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>Update Bank Details</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="inlineStr"/>
+      <c r="V6" s="2" t="inlineStr"/>
+      <c r="W6" s="2" t="inlineStr"/>
+      <c r="X6" s="2" t="inlineStr"/>
+      <c r="Y6" s="2" t="inlineStr"/>
+      <c r="Z6" s="2" t="inlineStr"/>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
+          <t>Update Bank Details</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>report_KYC</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>KYC</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>KYC (Know Your Customer)</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>502345678</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Neo Gaotlhobogwe</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>502345678</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1980-05-15</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>79567890</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>neo@email.bw</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr"/>
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr"/>
+      <c r="S7" s="2" t="inlineStr"/>
+      <c r="T7" s="2" t="inlineStr"/>
+      <c r="U7" s="2" t="inlineStr"/>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -605,15 +1163,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -629,24 +1188,1254 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>form_code</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>field</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>message</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>ENT001</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>report_ADD</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>id_number</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>ID number not captured</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>ENT001</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>report_ADD</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>id_expiry_date</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>ID expiry date not captured</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>ENT001</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>report_ADD</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>b.tau@email.bw</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>ENT001</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>report_ADD</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>contact_number</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>75123456</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>ENT001</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>report_ADD</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>branch_code</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Branch code not captured</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>ENT001</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>report_ADD</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>fund_category</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Money Market</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>ENT002</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>report_DEBIT</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>DEBIT</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>id_number</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>ID number not captured</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>ENT002</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>report_DEBIT</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>DEBIT</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>id_expiry_date</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>ID expiry date not captured</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>ENT002</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>report_DEBIT</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>DEBIT</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Field is blank - cannot validate format</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>ENT002</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>report_DEBIT</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>contact_number</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>76234567</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>ENT002</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>report_DEBIT</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>branch_code</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>282672</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>ENT002</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>report_DEBIT</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>fund_category</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Non-Money Market</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>ENT003</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>report_DIS</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>id_number</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n"/>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>ID number not captured</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>ENT003</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>report_DIS</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>id_expiry_date</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n"/>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>ID expiry date not captured</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>ENT003</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>report_DIS</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n"/>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Field is blank - cannot validate format</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>ENT003</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>report_DIS</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>contact_number</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>77345678</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>ENT003</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>report_DIS</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>branch_code</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>282672</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>ENT003</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>report_DIS</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>fund_category</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Non-Money Market</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>ENT004</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>report_DIS_GSG</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>DIS_GSG</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>id_number</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n"/>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>ID number not captured</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>ENT004</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>report_DIS_GSG</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>DIS_GSG</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>id_expiry_date</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n"/>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>ID expiry date not captured</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>ENT004</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>report_DIS_GSG</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>DIS_GSG</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n"/>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Field is blank - cannot validate format</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>ENT004</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>report_DIS_GSG</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>DIS_GSG</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>contact_number</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>78456789</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>ENT004</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>report_DIS_GSG</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>DIS_GSG</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>branch_code</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>282672</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>ENT004</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>report_DIS_GSG</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>DIS_GSG</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>fund_category</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Non-Money Market (GSGF)</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>ENT005</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>report_STATIC</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>STATIC</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>id_number</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n"/>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>ID number not captured</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>ENT005</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>report_STATIC</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>STATIC</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>id_expiry_date</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n"/>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>ID expiry date not captured</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>ENT005</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>report_STATIC</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>STATIC</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="n"/>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Field is blank - cannot validate format</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>ENT005</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>report_STATIC</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>STATIC</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>contact_number</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="n"/>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Field is blank</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>ENT005</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>report_STATIC</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>STATIC</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>branch_code</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>060144</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>502345678</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>report_KYC</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>KYC</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>id_number</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>502345678</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Unknown ID type 'None' - cannot apply digit validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>502345678</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>report_KYC</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>KYC</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>gender</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="n"/>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>Gender derivation not applicable for this ID type</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>502345678</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>report_KYC</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>KYC</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>id_expiry_date</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="n"/>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>ID expiry date not captured</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>502345678</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>report_KYC</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>KYC</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>date_of_birth</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>1980-05-15</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>502345678</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>report_KYC</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>KYC</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>neo@email.bw</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>502345678</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>report_KYC</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>KYC</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>contact_number</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>79567890</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>502345678</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>report_KYC</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>KYC</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>branch_code</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="n"/>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Branch code not captured</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>502345678</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>report_KYC</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>KYC</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>kyc_completeness_flag</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -659,12 +2448,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="43" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="27" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
@@ -717,35 +2506,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-29T14:13:19</t>
+          <t>2026-06-30T11:04:17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>STATIC - AMOLEMO.pdf</t>
+          <t>report_ADD.pdf</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>STATIC_NA_UNKNOWN_20260629_1_2.pdf</t>
+          <t>ADD_ENT001_TAU_20260630_1.pdf</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>STATIC</t>
+          <t>ADD</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>NOT_EXTRACTED</t>
+          <t>WARNING</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\STATIC_NA_UNKNOWN_20260629_1_2.pdf</t>
+          <t>/home/claude/bifm_ocr_app/output/filed_documents/ADD_ENT001_TAU_20260630_1.pdf</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -757,35 +2546,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-29T14:15:07</t>
+          <t>2026-06-30T11:04:17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DIS - AMOLEMO.pdf</t>
+          <t>report_DEBIT.pdf</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DIS_NA_UNKNOWN_20260629_1.pdf</t>
+          <t>DEBIT_ENT002_SETLHARE_20260630_1.pdf</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>DEBIT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>NOT_EXTRACTED</t>
+          <t>WARNING</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\DIS_NA_UNKNOWN_20260629_1.pdf</t>
+          <t>/home/claude/bifm_ocr_app/output/filed_documents/DEBIT_ENT002_SETLHARE_20260630_1.pdf</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -797,35 +2586,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-29T14:16:55</t>
+          <t>2026-06-30T11:04:17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DEBIT - AMOLEMO.pdf</t>
+          <t>report_DIS.pdf</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DEBIT_NA_UNKNOWN_20260629_1.pdf</t>
+          <t>DIS_ENT003_MOTSWANA_20260630_1.pdf</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>DEBIT</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>NOT_EXTRACTED</t>
+          <t>WARNING</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\DEBIT_NA_UNKNOWN_20260629_1.pdf</t>
+          <t>/home/claude/bifm_ocr_app/output/filed_documents/DIS_ENT003_MOTSWANA_20260630_1.pdf</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -837,38 +2626,118 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-29T14:18:51</t>
+          <t>2026-06-30T11:04:17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ADD - AMOLEMO.pdf</t>
+          <t>report_DIS_GSG.pdf</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ADD_NA_UNKNOWN_20260629_1.pdf</t>
+          <t>DIS_GSG_ENT004_MOETI_20260630_1.pdf</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ADD</t>
+          <t>DIS_GSG</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>NOT_EXTRACTED</t>
+          <t>WARNING</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\ADD_NA_UNKNOWN_20260629_1.pdf</t>
+          <t>/home/claude/bifm_ocr_app/output/filed_documents/DIS_GSG_ENT004_MOETI_20260630_1.pdf</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
+        <is>
+          <t>marvel.ai-local-poc</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-06-30T11:04:17</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>report_STATIC.pdf</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>STATIC_ENT005_KGOSIDINTSI_20260630_1.pdf</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>STATIC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>91</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>/home/claude/bifm_ocr_app/output/filed_documents/STATIC_ENT005_KGOSIDINTSI_20260630_1.pdf</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>marvel.ai-local-poc</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-06-30T11:04:18</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>report_KYC.pdf</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>KYC_502345678_GAOTLHOBOGWE_20260630_1.pdf</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>KYC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>91</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>/home/claude/bifm_ocr_app/output/filed_documents/KYC_502345678_GAOTLHOBOGWE_20260630_1.pdf</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t>marvel.ai-local-poc</t>
         </is>

--- a/output/BIFM_UT_Processing_Report.xlsx
+++ b/output/BIFM_UT_Processing_Report.xlsx
@@ -33,7 +33,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -44,6 +44,24 @@
       <patternFill patternType="solid">
         <fgColor rgb="00305496"/>
         <bgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -59,9 +77,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -427,15 +448,371 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:U4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="27" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="45" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="27" customWidth="1" min="17" max="17"/>
+    <col width="28" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="28" customWidth="1" min="21" max="21"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>No data</t>
-        </is>
-      </c>
+          <t>source_file</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>form_code</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>form_type</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>entity_number</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>full_name</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_number</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>fund_category</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>processing_cutoff</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>overall_validation_status</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>instruction_status</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>rejection_reason</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>channel</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>upload_date</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>captured_by</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>authorized_by</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>contact_number</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>change_type</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>id_expiry_date</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>instruction_mode</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>static_sub_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>DIS - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Disinvestment Form (Standard)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>DIS - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Unknown - Fund Name Not Extracted</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Validation failed: entity_number, full_name, contact_number, fund_name</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01T13:33:32</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>marvel.ai-local-poc</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr"/>
+      <c r="P2" s="2" t="inlineStr"/>
+      <c r="Q2" s="2" t="inlineStr"/>
+      <c r="R2" s="2" t="inlineStr"/>
+      <c r="S2" s="2" t="inlineStr"/>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>STATIC - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>STATIC</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Static / Change of Investor Details Form</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>381346789</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Amolemo P Mantiwe</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>2239222827</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Captured</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr"/>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-01T13:33:32</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>marvel.ai-local-poc</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr"/>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>748710497</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr">
+        <is>
+          <t>amolemo.mantiwe@gmail.com</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>Change of personal details</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr">
+        <is>
+          <t>03/10/2034</t>
+        </is>
+      </c>
+      <c r="T3" s="3" t="inlineStr"/>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>Change of personal details</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>ADD - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Additional Investment Form</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>ADD - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Unknown - Fund Name Not Extracted</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Validation failed: entity_number, full_name, contact_number, email, fund_name, fund_number</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01T13:33:32</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>marvel.ai-local-poc</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr"/>
+      <c r="P4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr"/>
+      <c r="R4" s="2" t="inlineStr"/>
+      <c r="S4" s="2" t="inlineStr"/>
+      <c r="T4" s="2" t="inlineStr"/>
+      <c r="U4" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -496,16 +873,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,6 +919,913 @@
       <c r="G1" s="1" t="inlineStr">
         <is>
           <t>message</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>DIS - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>DIS - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>entity_number</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Mandatory field missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>DIS - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>DIS - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>full_name</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Mandatory field missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>DIS - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>DIS - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>contact_number</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Mandatory field missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>DIS - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>DIS - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>fund_name</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Mandatory field missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>DIS - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>DIS - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>id_number</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>ID number not captured</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>DIS - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>DIS - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>id_expiry_date</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>ID expiry date not captured</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>DIS - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>DIS - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Field is blank - cannot validate format</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>DIS - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>DIS - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>contact_number</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Field is blank</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>DIS - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>DIS - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>branch_code</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n"/>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Branch code not captured</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>DIS - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>DIS - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>fund_category</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Unknown - Fund Name Not Extracted</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Fund category could not be determined - fund name unclear</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>381346789</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>STATIC - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>STATIC</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>id_number</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>2239222827</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Unknown ID type 'None' - cannot apply digit validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>381346789</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>STATIC - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>STATIC</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>id_expiry_date</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>03/10/2034</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>381346789</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>STATIC - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>STATIC</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>amolemo.mantiwe@gmail.com</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>381346789</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>STATIC - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>STATIC</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>contact_number</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>748710497</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Expected 8 digits, got 9</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>381346789</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>STATIC - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>STATIC</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>branch_code</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n"/>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>Branch code not captured</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>ADD - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>ADD - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>entity_number</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n"/>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Mandatory field missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>ADD - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>ADD - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>full_name</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n"/>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Mandatory field missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>ADD - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>ADD - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>contact_number</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n"/>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Mandatory field missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>ADD - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>ADD - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n"/>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Mandatory field missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>ADD - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>ADD - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>fund_name</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n"/>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Mandatory field missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>ADD - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>ADD - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>fund_number</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n"/>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Mandatory field missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>ADD - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>ADD - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>id_number</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="n"/>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>ID number not captured</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>ADD - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>ADD - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>id_expiry_date</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="n"/>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>ID expiry date not captured</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>ADD - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>ADD - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="n"/>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Field is blank - cannot validate format</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>ADD - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>ADD - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>contact_number</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="n"/>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>Field is blank</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>ADD - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>ADD - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>branch_code</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="n"/>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>Branch code not captured</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>ADD - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>ADD - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>fund_category</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Unknown - Fund Name Not Extracted</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>Fund category could not be determined - fund name unclear</t>
         </is>
       </c>
     </row>
@@ -556,23 +1840,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="27" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="45" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -647,6 +1931,200 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-01T13:33:41</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>DIS - AMOLEMO.pdf</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>DIS_NA_UNKNOWN_20260701_VALIDATIONFAILEDENTITY_NUMBERFULL_NAMECONTACT_NUMBERFUND_NAME.pdf</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Validation failed: entity_number, full_name, contact_number, fund_name</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2026-07-01T13:33:32</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\01\NonMoneyMarket\Captured\Rejected\DIS_NA_UNKNOWN_20260701_VALIDATIONFAILEDENTITY_NUMBERFULL_NAMECONTACT_NUMBERFUND_NAME.pdf</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>marvel.ai-local-poc</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>marvel.ai-local-poc</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-01T13:33:45</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>STATIC - AMOLEMO.pdf</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>STATIC_381346789_MANTIWE_20260701.pdf</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>STATIC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>95</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Captured</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2026-07-01T13:33:32</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\01\NonMoneyMarket\Captured\STATIC_381346789_MANTIWE_20260701.pdf</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>marvel.ai-local-poc</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>marvel.ai-local-poc</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-01T13:34:02</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ADD - AMOLEMO.pdf</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ADD_NA_UNKNOWN_20260701_VALIDATIONFAILEDENTITY_NUMBERFULL_NAMECONTACT_NUMBEREMAILFUND_NAMEFUND_NUMBER.pdf</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Validation failed: entity_number, full_name, contact_number, email, fund_name, fund_number</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2026-07-01T13:33:32</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\01\NonMoneyMarket\Captured\Rejected\ADD_NA_UNKNOWN_20260701_VALIDATIONFAILEDENTITY_NUMBERFULL_NAMECONTACT_NUMBEREMAILFUND_NAMEFUND_NUMBER.pdf</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>marvel.ai-local-poc</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>marvel.ai-local-poc</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/BIFM_UT_Processing_Report.xlsx
+++ b/output/BIFM_UT_Processing_Report.xlsx
@@ -7,10 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Investor Master" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Beneficiary Details" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation Flags" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Processing Log" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consolidated Investor Profile" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Investor Master" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Beneficiary Details" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation Flags" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Processing Log" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -48,14 +49,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-        <bgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -448,7 +449,124 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U4"/>
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="27" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>person_key</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>document_count</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>source_documents</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>entity_number</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>full_name</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_number</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>id_expiry_date</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>contact_number</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>AMOLEMO</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>STATIC - AMOLEMO.pdf, DIS - AMOLEMO.pdf, DEBIT - AMOLEMO.pdf, ADD - AMOLEMO.pdf</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>381346789</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Amolemo P Mantiwe</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2239222827</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>03/10/2034</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>amolemo.mantiwe@gmail.com</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>748710497</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:U5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -461,7 +579,7 @@
     <col width="19" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="45" customWidth="1" min="11" max="11"/>
+    <col width="43" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="21" customWidth="1" min="13" max="13"/>
     <col width="21" customWidth="1" min="14" max="14"/>
@@ -584,51 +702,47 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>DIS - AMOLEMO</t>
+          <t>STATIC - AMOLEMO</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>STATIC</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Disinvestment Form (Standard)</t>
+          <t>Static / Change of Investor Details Form</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>DIS - AMOLEMO</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Unknown - Fund Name Not Extracted</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+          <t>381346789</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Amolemo P Mantiwe</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>2239222827</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>WARNING</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Rejected</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>Validation failed: entity_number, full_name, contact_number, fund_name</t>
-        </is>
-      </c>
+          <t>Captured</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
           <t>Email</t>
@@ -636,7 +750,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T13:33:32</t>
+          <t>2026-07-01T14:22:23</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -645,31 +759,47 @@
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr"/>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="inlineStr"/>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>748710497</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>amolemo.mantiwe@gmail.com</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>Change of personal details</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>03/10/2034</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr"/>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>Change of personal details</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>STATIC - AMOLEMO</t>
+          <t>DIS - AMOLEMO</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>STATIC</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Static / Change of Investor Details Form</t>
+          <t>Disinvestment Form (Standard)</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -687,19 +817,31 @@
           <t>2239222827</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Unknown - Fund Name Not Extracted</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>WARNING</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>Captured</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr"/>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>Validation failed: fund_name</t>
+        </is>
+      </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
           <t>Email</t>
@@ -707,7 +849,7 @@
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>2026-07-01T13:33:32</t>
+          <t>2026-07-01T14:22:23</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -726,100 +868,195 @@
           <t>amolemo.mantiwe@gmail.com</t>
         </is>
       </c>
-      <c r="R3" s="3" t="inlineStr">
-        <is>
-          <t>Change of personal details</t>
-        </is>
-      </c>
-      <c r="S3" s="3" t="inlineStr">
+      <c r="R3" s="3" t="inlineStr"/>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Debit Order Form</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>381346789</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Amolemo P Mantiwe</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>2239222827</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Unknown - Fund Name Not Extracted</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Validation failed: instruction_type</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-01T14:22:23</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>marvel.ai-local-poc</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr"/>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>748710497</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>amolemo.mantiwe@gmail.com</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr"/>
+      <c r="S4" s="3" t="inlineStr">
         <is>
           <t>03/10/2034</t>
         </is>
       </c>
-      <c r="T3" s="3" t="inlineStr"/>
-      <c r="U3" s="3" t="inlineStr">
-        <is>
-          <t>Change of personal details</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="T4" s="3" t="inlineStr"/>
+      <c r="U4" s="3" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>ADD - AMOLEMO</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>ADD</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Additional Investment Form</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>ADD - AMOLEMO</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>381346789</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Amolemo P Mantiwe</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Unknown - Fund Name Not Extracted</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>Rejected</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>Validation failed: entity_number, full_name, contact_number, email, fund_name, fund_number</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Validation failed: fund_name, fund_number</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01T13:33:32</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-01T14:22:23</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>marvel.ai-local-poc</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr"/>
-      <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr"/>
-      <c r="R4" s="2" t="inlineStr"/>
-      <c r="S4" s="2" t="inlineStr"/>
-      <c r="T4" s="2" t="inlineStr"/>
-      <c r="U4" s="2" t="inlineStr"/>
+      <c r="O5" s="3" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>748710497</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t>amolemo.mantiwe@gmail.com</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr"/>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -867,7 +1104,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -879,7 +1116,7 @@
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="35" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
@@ -925,179 +1162,187 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>DIS - AMOLEMO</t>
+          <t>381346789</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>DIS - AMOLEMO</t>
+          <t>STATIC - AMOLEMO</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>STATIC</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>entity_number</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="n"/>
+          <t>id_number</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>2239222827</t>
+        </is>
+      </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>WARNING</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Mandatory field missing</t>
+          <t>Unknown ID type 'None' - cannot apply digit validation</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>DIS - AMOLEMO</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>DIS - AMOLEMO</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>full_name</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Mandatory field missing</t>
-        </is>
-      </c>
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>381346789</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>STATIC - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>STATIC</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>id_expiry_date</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>03/10/2034</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>DIS - AMOLEMO</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>DIS - AMOLEMO</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>contact_number</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Mandatory field missing</t>
-        </is>
-      </c>
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>381346789</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>STATIC - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>STATIC</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>amolemo.mantiwe@gmail.com</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>DIS - AMOLEMO</t>
+          <t>381346789</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>DIS - AMOLEMO</t>
+          <t>STATIC - AMOLEMO</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>STATIC</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>fund_name</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="n"/>
+          <t>contact_number</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>748710497</t>
+        </is>
+      </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>WARNING</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Mandatory field missing</t>
+          <t>Expected 8 digits, got 9</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>DIS - AMOLEMO</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>DIS - AMOLEMO</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>id_number</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="n"/>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>381346789</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>STATIC - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>STATIC</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>branch_code</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>WARNING</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>ID number not captured</t>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Branch code not captured</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
+          <t>381346789</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
           <t>DIS - AMOLEMO</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>DIS - AMOLEMO</t>
-        </is>
-      </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
           <t>DIS</t>
@@ -1105,725 +1350,741 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>id_expiry_date</t>
+          <t>fund_name</t>
         </is>
       </c>
       <c r="E7" s="3" t="n"/>
       <c r="F7" s="3" t="inlineStr">
         <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Mandatory field missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>381346789</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>DIS - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>id_number</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2239222827</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>WARNING</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Unknown ID type 'None' - cannot apply digit validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>381346789</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>DIS - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>id_expiry_date</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>ID expiry date not captured</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>381346789</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>DIS - AMOLEMO</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>amolemo.mantiwe@gmail.com</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>381346789</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>DIS - AMOLEMO</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>DIS</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>contact_number</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>748710497</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Expected 8 digits, got 9</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>381346789</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>DIS - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>branch_code</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Branch code not captured</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>381346789</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>DIS - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>fund_category</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Unknown - Fund Name Not Extracted</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Fund category could not be determined - fund name unclear</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>381346789</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>instruction_type</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="n"/>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>Mandatory field missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>381346789</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>DEBIT - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>DEBIT</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>id_number</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>2239222827</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Unknown ID type 'None' - cannot apply digit validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>381346789</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>DEBIT - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>DEBIT</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>id_expiry_date</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>03/10/2034</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>381346789</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>DEBIT - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>DEBIT</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="E8" s="3" t="n"/>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>Field is blank - cannot validate format</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>DIS - AMOLEMO</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>DIS - AMOLEMO</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>contact_number</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n"/>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>Field is blank</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>DIS - AMOLEMO</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>DIS - AMOLEMO</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>branch_code</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="n"/>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>Branch code not captured</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>DIS - AMOLEMO</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>DIS - AMOLEMO</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>fund_category</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>Unknown - Fund Name Not Extracted</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>Fund category could not be determined - fund name unclear</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>381346789</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>STATIC - AMOLEMO</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>STATIC</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>id_number</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>2239222827</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>Unknown ID type 'None' - cannot apply digit validation</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>381346789</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>STATIC - AMOLEMO</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>STATIC</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>id_expiry_date</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>03/10/2034</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>amolemo.mantiwe@gmail.com</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>381346789</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>STATIC - AMOLEMO</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>STATIC</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>amolemo.mantiwe@gmail.com</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>381346789</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>STATIC - AMOLEMO</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>STATIC</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>contact_number</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>748710497</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>Expected 8 digits, got 9</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>381346789</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>STATIC - AMOLEMO</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>STATIC</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>branch_code</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="n"/>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>Branch code not captured</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>ADD - AMOLEMO</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>ADD - AMOLEMO</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>entity_number</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="n"/>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>Mandatory field missing</t>
-        </is>
-      </c>
+      <c r="G17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>ADD - AMOLEMO</t>
+          <t>381346789</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>ADD - AMOLEMO</t>
+          <t>DEBIT - AMOLEMO</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>ADD</t>
+          <t>DEBIT</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>full_name</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="n"/>
+          <t>contact_number</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>748710497</t>
+        </is>
+      </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>WARNING</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Mandatory field missing</t>
+          <t>Expected 8 digits, got 9</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>ADD - AMOLEMO</t>
+          <t>381346789</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>ADD - AMOLEMO</t>
+          <t>DEBIT - AMOLEMO</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>ADD</t>
+          <t>DEBIT</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>contact_number</t>
+          <t>branch_code</t>
         </is>
       </c>
       <c r="E19" s="2" t="n"/>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>WARNING</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Mandatory field missing</t>
+          <t>Branch code not captured</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>381346789</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>DEBIT - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>DEBIT</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>fund_category</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Unknown - Fund Name Not Extracted</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Fund category could not be determined - fund name unclear</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>381346789</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
           <t>ADD - AMOLEMO</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>fund_name</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n"/>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>Mandatory field missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>381346789</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>ADD - AMOLEMO</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>ADD</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>fund_number</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n"/>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>Mandatory field missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>381346789</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>ADD - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>id_number</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n"/>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>ID number not captured</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>381346789</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>ADD - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>id_expiry_date</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n"/>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>ID expiry date not captured</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>381346789</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>ADD - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="E20" s="2" t="n"/>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>Mandatory field missing</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>amolemo.mantiwe@gmail.com</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>381346789</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>ADD - AMOLEMO</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>contact_number</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>748710497</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Expected 8 digits, got 9</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>381346789</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>ADD - AMOLEMO</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>ADD</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>fund_name</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="n"/>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>Mandatory field missing</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>branch_code</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n"/>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Branch code not captured</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>381346789</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>ADD - AMOLEMO</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>ADD - AMOLEMO</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>ADD</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>fund_number</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="n"/>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>Mandatory field missing</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>ADD - AMOLEMO</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>ADD - AMOLEMO</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>id_number</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="n"/>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>fund_category</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Unknown - Fund Name Not Extracted</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>WARNING</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>ID number not captured</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>ADD - AMOLEMO</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>ADD - AMOLEMO</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>id_expiry_date</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="n"/>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>ID expiry date not captured</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>ADD - AMOLEMO</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>ADD - AMOLEMO</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="n"/>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>Field is blank - cannot validate format</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>ADD - AMOLEMO</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>ADD - AMOLEMO</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>contact_number</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="n"/>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>Field is blank</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>ADD - AMOLEMO</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>ADD - AMOLEMO</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>branch_code</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="n"/>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>Branch code not captured</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>ADD - AMOLEMO</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>ADD - AMOLEMO</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>fund_category</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>Unknown - Fund Name Not Extracted</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>Fund category could not be determined - fund name unclear</t>
         </is>
@@ -1834,13 +2095,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -1850,7 +2111,7 @@
     <col width="27" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="43" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
     <col width="45" customWidth="1" min="11" max="11"/>
@@ -1934,42 +2195,38 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-01T13:33:41</t>
+          <t>2026-07-01T14:23:35</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DIS - AMOLEMO.pdf</t>
+          <t>STATIC - AMOLEMO.pdf</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DIS_NA_UNKNOWN_20260701_VALIDATIONFAILEDENTITY_NUMBERFULL_NAMECONTACT_NUMBERFUND_NAME.pdf</t>
+          <t>STATIC_381346789_MANTIWE_20260701_1.pdf</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>STATIC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>WARNING</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rejected</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Validation failed: entity_number, full_name, contact_number, fund_name</t>
-        </is>
-      </c>
+          <t>Captured</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Email</t>
@@ -1977,12 +2234,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-01T13:33:32</t>
+          <t>2026-07-01T14:22:23</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\01\NonMoneyMarket\Captured\Rejected\DIS_NA_UNKNOWN_20260701_VALIDATIONFAILEDENTITY_NUMBERFULL_NAMECONTACT_NUMBERFUND_NAME.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\01\NonMoneyMarket\Captured\STATIC_381346789_MANTIWE_20260701_1.pdf</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -2000,38 +2257,42 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-01T13:33:45</t>
+          <t>2026-07-01T14:23:35</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>STATIC - AMOLEMO.pdf</t>
+          <t>DIS - AMOLEMO.pdf</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>STATIC_381346789_MANTIWE_20260701.pdf</t>
+          <t>DIS_381346789_MANTIWE_20260701_VALIDATIONFAILEDFUND_NAME.pdf</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>STATIC</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>WARNING</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Captured</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Validation failed: fund_name</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>Email</t>
@@ -2039,12 +2300,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-07-01T13:33:32</t>
+          <t>2026-07-01T14:22:23</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\01\NonMoneyMarket\Captured\STATIC_381346789_MANTIWE_20260701.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\01\NonMoneyMarket\Captured\Rejected\DIS_381346789_MANTIWE_20260701_VALIDATIONFAILEDFUND_NAME.pdf</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -2062,22 +2323,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-01T13:34:02</t>
+          <t>2026-07-01T14:23:35</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ADD - AMOLEMO.pdf</t>
+          <t>DEBIT - AMOLEMO.pdf</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ADD_NA_UNKNOWN_20260701_VALIDATIONFAILEDENTITY_NUMBERFULL_NAMECONTACT_NUMBEREMAILFUND_NAMEFUND_NUMBER.pdf</t>
+          <t>DEBIT_381346789_MANTIWE_20260701_VALIDATIONFAILEDINSTRUCTION_TYPE.pdf</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ADD</t>
+          <t>DEBIT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -2095,7 +2356,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Validation failed: entity_number, full_name, contact_number, email, fund_name, fund_number</t>
+          <t>Validation failed: instruction_type</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -2105,12 +2366,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-07-01T13:33:32</t>
+          <t>2026-07-01T14:22:23</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\01\NonMoneyMarket\Captured\Rejected\ADD_NA_UNKNOWN_20260701_VALIDATIONFAILEDENTITY_NUMBERFULL_NAMECONTACT_NUMBEREMAILFUND_NAMEFUND_NUMBER.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\01\NonMoneyMarket\Captured\Rejected\DEBIT_381346789_MANTIWE_20260701_VALIDATIONFAILEDINSTRUCTION_TYPE.pdf</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -2120,6 +2381,72 @@
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
+        <is>
+          <t>marvel.ai-local-poc</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-01T14:23:35</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ADD - AMOLEMO.pdf</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ADD_381346789_MANTIWE_20260701_VALIDATIONFAILEDFUND_NAMEFUND_NUMBER.pdf</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Validation failed: fund_name, fund_number</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-07-01T14:22:23</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\01\NonMoneyMarket\Captured\Rejected\ADD_381346789_MANTIWE_20260701_VALIDATIONFAILEDFUND_NAMEFUND_NUMBER.pdf</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>marvel.ai-local-poc</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
         <is>
           <t>marvel.ai-local-poc</t>
         </is>

--- a/output/BIFM_UT_Processing_Report.xlsx
+++ b/output/BIFM_UT_Processing_Report.xlsx
@@ -750,7 +750,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T14:22:23</t>
+          <t>2026-07-01T16:10:18</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>2026-07-01T14:22:23</t>
+          <t>2026-07-01T16:10:18</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>2026-07-01T14:22:23</t>
+          <t>2026-07-01T16:10:18</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>2026-07-01T14:22:23</t>
+          <t>2026-07-01T16:10:18</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
@@ -1110,7 +1110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1263,41 +1263,37 @@
       <c r="G4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>381346789</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>381346789</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>STATIC - AMOLEMO</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>STATIC</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>contact_number</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>748710497</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Expected 8 digits, got 9</t>
-        </is>
-      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1469,41 +1465,37 @@
       <c r="G10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>381346789</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>381346789</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>DIS - AMOLEMO</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>DIS</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>contact_number</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>748710497</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>Expected 8 digits, got 9</t>
-        </is>
-      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1556,127 +1548,127 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>fund_number</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n"/>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Field is blank</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>381346789</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>DIS - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
           <t>fund_category</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Unknown - Fund Name Not Extracted</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>WARNING</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>Fund category could not be determined - fund name unclear</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>381346789</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>381346789</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>DEBIT - AMOLEMO</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>DEBIT</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>instruction_type</t>
         </is>
       </c>
-      <c r="E14" s="3" t="n"/>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>Mandatory field missing</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>381346789</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>381346789</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>DEBIT - AMOLEMO</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>DEBIT</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>id_number</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>2239222827</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>WARNING</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>Unknown ID type 'None' - cannot apply digit validation</t>
         </is>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>381346789</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>DEBIT - AMOLEMO</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>DEBIT</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>id_expiry_date</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>03/10/2034</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -1696,90 +1688,86 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
+          <t>id_expiry_date</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>03/10/2034</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>381346789</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>DEBIT - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>DEBIT</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
           <t>email</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>amolemo.mantiwe@gmail.com</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>381346789</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>381346789</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>DEBIT - AMOLEMO</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>DEBIT</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>contact_number</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>748710497</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>Expected 8 digits, got 9</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>381346789</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>DEBIT - AMOLEMO</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>DEBIT</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>branch_code</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="n"/>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>Branch code not captured</t>
-        </is>
-      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1799,189 +1787,189 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>branch_code</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n"/>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Branch code not captured</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>381346789</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>DEBIT - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>DEBIT</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>fund_number</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n"/>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Field is blank</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>381346789</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>DEBIT - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>DEBIT</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>fund_category</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Unknown - Fund Name Not Extracted</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>WARNING</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>Fund category could not be determined - fund name unclear</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>381346789</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>381346789</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>ADD - AMOLEMO</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>ADD</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>fund_name</t>
         </is>
       </c>
-      <c r="E21" s="3" t="n"/>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="E23" s="3" t="n"/>
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="G23" s="3" t="inlineStr">
         <is>
           <t>Mandatory field missing</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>381346789</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>381346789</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>ADD - AMOLEMO</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>ADD</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>fund_number</t>
         </is>
       </c>
-      <c r="E22" s="3" t="n"/>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="E24" s="3" t="n"/>
+      <c r="F24" s="3" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="G24" s="3" t="inlineStr">
         <is>
           <t>Mandatory field missing</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>381346789</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>381346789</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>ADD - AMOLEMO</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>ADD</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>id_number</t>
         </is>
       </c>
-      <c r="E23" s="2" t="n"/>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="E25" s="2" t="n"/>
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>WARNING</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>ID number not captured</t>
         </is>
       </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>381346789</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>ADD - AMOLEMO</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>id_expiry_date</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="n"/>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>ID expiry date not captured</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>381346789</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>ADD - AMOLEMO</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>amolemo.mantiwe@gmail.com</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2001,90 +1989,185 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>id_expiry_date</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n"/>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>ID expiry date not captured</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>381346789</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>ADD - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>amolemo.mantiwe@gmail.com</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>381346789</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>ADD - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
           <t>contact_number</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E28" s="4" t="inlineStr">
         <is>
           <t>748710497</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>381346789</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>ADD - AMOLEMO</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>branch_code</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="n"/>
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>WARNING</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>Expected 8 digits, got 9</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>381346789</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Branch code not captured</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>381346789</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>ADD - AMOLEMO</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>ADD</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>branch_code</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="n"/>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>fund_number</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="n"/>
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>WARNING</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>Branch code not captured</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>381346789</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Field is blank</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>381346789</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>ADD - AMOLEMO</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>ADD</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>fund_category</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Unknown - Fund Name Not Extracted</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>WARNING</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>Fund category could not be determined - fund name unclear</t>
         </is>
@@ -2195,7 +2278,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-01T14:23:35</t>
+          <t>2026-07-01T16:12:22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2205,7 +2288,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>STATIC_381346789_MANTIWE_20260701_1.pdf</t>
+          <t>STATIC_381346789_MANTIWE_20260701_1_2.pdf</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -2234,12 +2317,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-01T14:22:23</t>
+          <t>2026-07-01T16:10:18</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\01\NonMoneyMarket\Captured\STATIC_381346789_MANTIWE_20260701_1.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\01\NonMoneyMarket\Captured\STATIC_381346789_MANTIWE_20260701_1_2.pdf</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -2257,7 +2340,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-01T14:23:35</t>
+          <t>2026-07-01T16:12:22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2267,7 +2350,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DIS_381346789_MANTIWE_20260701_VALIDATIONFAILEDFUND_NAME.pdf</t>
+          <t>DIS_381346789_MANTIWE_20260701_VALIDATIONFAILEDFUND_NAME_1.pdf</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2300,12 +2383,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-07-01T14:22:23</t>
+          <t>2026-07-01T16:10:18</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\01\NonMoneyMarket\Captured\Rejected\DIS_381346789_MANTIWE_20260701_VALIDATIONFAILEDFUND_NAME.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\01\NonMoneyMarket\Captured\Rejected\DIS_381346789_MANTIWE_20260701_VALIDATIONFAILEDFUND_NAME_1.pdf</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -2323,7 +2406,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-01T14:23:35</t>
+          <t>2026-07-01T16:12:22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2333,7 +2416,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DEBIT_381346789_MANTIWE_20260701_VALIDATIONFAILEDINSTRUCTION_TYPE.pdf</t>
+          <t>DEBIT_381346789_MANTIWE_20260701_VALIDATIONFAILEDINSTRUCTION_TYPE_1.pdf</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2366,12 +2449,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-07-01T14:22:23</t>
+          <t>2026-07-01T16:10:18</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\01\NonMoneyMarket\Captured\Rejected\DEBIT_381346789_MANTIWE_20260701_VALIDATIONFAILEDINSTRUCTION_TYPE.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\01\NonMoneyMarket\Captured\Rejected\DEBIT_381346789_MANTIWE_20260701_VALIDATIONFAILEDINSTRUCTION_TYPE_1.pdf</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -2389,7 +2472,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-01T14:23:35</t>
+          <t>2026-07-01T16:12:22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2399,7 +2482,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ADD_381346789_MANTIWE_20260701_VALIDATIONFAILEDFUND_NAMEFUND_NUMBER.pdf</t>
+          <t>ADD_381346789_MANTIWE_20260701_VALIDATIONFAILEDFUND_NAMEFUND_NUMBER_1.pdf</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2432,12 +2515,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-07-01T14:22:23</t>
+          <t>2026-07-01T16:10:18</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\01\NonMoneyMarket\Captured\Rejected\ADD_381346789_MANTIWE_20260701_VALIDATIONFAILEDFUND_NAMEFUND_NUMBER.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\01\NonMoneyMarket\Captured\Rejected\ADD_381346789_MANTIWE_20260701_VALIDATIONFAILEDFUND_NAMEFUND_NUMBER_1.pdf</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">

--- a/output/BIFM_UT_Processing_Report.xlsx
+++ b/output/BIFM_UT_Processing_Report.xlsx
@@ -49,14 +49,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-        <bgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
@@ -449,18 +449,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="27" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="37" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -481,39 +476,14 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>entity_number</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>full_name</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>id_number</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>id_expiry_date</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>contact_number</t>
+          <t>fund_name</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AMOLEMO</t>
+          <t>Copy</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -521,37 +491,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>STATIC - AMOLEMO.pdf, DIS - AMOLEMO.pdf, DEBIT - AMOLEMO.pdf, ADD - AMOLEMO.pdf</t>
+          <t>ADD - GAOLATHE - Copy.pdf, DEBIT - GAOLATHE.pdf, DIS - GAOLATHE.pdf, GSGF - GAOLATLHE.pdf</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>381346789</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Amolemo P Mantiwe</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2239222827</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>03/10/2034</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>amolemo.mantiwe@gmail.com</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>748710497</t>
+          <t>BIFM Global Sustainable Growth Fund</t>
         </is>
       </c>
     </row>
@@ -566,30 +511,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U5"/>
+  <dimension ref="A1:P5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="37" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="43" customWidth="1" min="11" max="11"/>
+    <col width="45" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="21" customWidth="1" min="13" max="13"/>
     <col width="21" customWidth="1" min="14" max="14"/>
     <col width="15" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="27" customWidth="1" min="17" max="17"/>
-    <col width="28" customWidth="1" min="18" max="18"/>
-    <col width="16" customWidth="1" min="19" max="19"/>
-    <col width="18" customWidth="1" min="20" max="20"/>
-    <col width="28" customWidth="1" min="21" max="21"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -615,22 +555,22 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>full_name</t>
+          <t>fund_name</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>id_number</t>
+          <t>fund_category</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>fund_category</t>
+          <t>processing_cutoff</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>processing_cutoff</t>
+          <t>fund_category_priority</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -670,79 +610,64 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>contact_number</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>change_type</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>id_expiry_date</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
           <t>instruction_mode</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>static_sub_type</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>STATIC - AMOLEMO</t>
+          <t>GSGF - GAOLATLHE</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>STATIC</t>
+          <t>DIS_GSG</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Static / Change of Investor Details Form</t>
+          <t>Disinvestment Form (GSGF)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>381346789</t>
+          <t>GSGF - GAOLATLHE</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Amolemo P Mantiwe</t>
+          <t>BIFM Global Sustainable Growth Fund</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2239222827</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
+          <t>Non-Money Market (GSGF)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Quarterly - 7th of last month of quarter</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>WARNING</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Captured</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr"/>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Validation failed: entity_number, full_name, contact_number</t>
+        </is>
+      </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
           <t>Email</t>
@@ -750,7 +675,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T16:10:18</t>
+          <t>2026-06-29T13:10:41</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -761,295 +686,229 @@
       <c r="O2" s="2" t="inlineStr"/>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>748710497</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>amolemo.mantiwe@gmail.com</t>
-        </is>
-      </c>
-      <c r="R2" s="2" t="inlineStr">
-        <is>
-          <t>Change of personal details</t>
-        </is>
-      </c>
-      <c r="S2" s="2" t="inlineStr">
-        <is>
-          <t>03/10/2034</t>
-        </is>
-      </c>
-      <c r="T2" s="2" t="inlineStr"/>
-      <c r="U2" s="2" t="inlineStr">
-        <is>
-          <t>Change of personal details</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>DIS - AMOLEMO</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>ADD - GAOLATHE - Copy</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Additional Investment Form</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>ADD - GAOLATHE - Copy</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>BIFM Global Sustainable Growth Fund</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Unknown - Fund Name Not Extracted</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>Validation failed: entity_number, full_name, contact_number, email, fund_number</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29T11:36:32</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>marvel.ai-local-poc</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr"/>
+      <c r="P3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>DEBIT - GAOLATHE</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>DEBIT</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Debit Order Form</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>DEBIT - GAOLATHE</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>BIFM Global Sustainable Growth Fund</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Unknown - Fund Name Not Extracted</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Validation failed: entity_number, full_name, contact_number, instruction_type</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29T13:09:59</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>marvel.ai-local-poc</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr"/>
+      <c r="P4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>DIS - GAOLATHE</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>DIS</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Disinvestment Form (Standard)</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>381346789</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>Amolemo P Mantiwe</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>2239222827</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>DIS - GAOLATHE</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>BIFM Global Sustainable Growth Fund</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Unknown - Fund Name Not Extracted</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="H5" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>Rejected</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>Validation failed: fund_name</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>Validation failed: entity_number, full_name, contact_number</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-01T16:10:18</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29T13:10:18</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>marvel.ai-local-poc</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr"/>
-      <c r="P3" s="3" t="inlineStr">
-        <is>
-          <t>748710497</t>
-        </is>
-      </c>
-      <c r="Q3" s="3" t="inlineStr">
-        <is>
-          <t>amolemo.mantiwe@gmail.com</t>
-        </is>
-      </c>
-      <c r="R3" s="3" t="inlineStr"/>
-      <c r="S3" s="3" t="inlineStr"/>
-      <c r="T3" s="3" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="U3" s="3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>DEBIT - AMOLEMO</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>DEBIT</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Debit Order Form</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>381346789</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Amolemo P Mantiwe</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>2239222827</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Unknown - Fund Name Not Extracted</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>Rejected</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>Validation failed: instruction_type</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-01T16:10:18</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>marvel.ai-local-poc</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr"/>
-      <c r="P4" s="3" t="inlineStr">
-        <is>
-          <t>748710497</t>
-        </is>
-      </c>
-      <c r="Q4" s="3" t="inlineStr">
-        <is>
-          <t>amolemo.mantiwe@gmail.com</t>
-        </is>
-      </c>
-      <c r="R4" s="3" t="inlineStr"/>
-      <c r="S4" s="3" t="inlineStr">
-        <is>
-          <t>03/10/2034</t>
-        </is>
-      </c>
-      <c r="T4" s="3" t="inlineStr"/>
-      <c r="U4" s="3" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>ADD - AMOLEMO</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Additional Investment Form</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>381346789</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>Amolemo P Mantiwe</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>Unknown - Fund Name Not Extracted</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>Rejected</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>Validation failed: fund_name, fund_number</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-01T16:10:18</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t>marvel.ai-local-poc</t>
-        </is>
-      </c>
-      <c r="O5" s="3" t="inlineStr"/>
-      <c r="P5" s="3" t="inlineStr">
-        <is>
-          <t>748710497</t>
-        </is>
-      </c>
-      <c r="Q5" s="3" t="inlineStr">
-        <is>
-          <t>amolemo.mantiwe@gmail.com</t>
-        </is>
-      </c>
-      <c r="R5" s="3" t="inlineStr"/>
-      <c r="S5" s="3" t="inlineStr"/>
-      <c r="T5" s="3" t="inlineStr"/>
-      <c r="U5" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1110,11 +969,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="35" customWidth="1" min="5" max="5"/>
@@ -1162,472 +1021,464 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>381346789</t>
+          <t>ADD - GAOLATHE - Copy</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>STATIC - AMOLEMO</t>
+          <t>ADD - GAOLATHE - Copy</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>STATIC</t>
+          <t>ADD</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>id_number</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>2239222827</t>
-        </is>
-      </c>
+          <t>entity_number</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>WARNING</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Unknown ID type 'None' - cannot apply digit validation</t>
+          <t>Mandatory field missing</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>381346789</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>STATIC - AMOLEMO</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>STATIC</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>id_expiry_date</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>03/10/2034</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr"/>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>ADD - GAOLATHE - Copy</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>ADD - GAOLATHE - Copy</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>full_name</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Mandatory field missing</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>381346789</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>STATIC - AMOLEMO</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>STATIC</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>ADD - GAOLATHE - Copy</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>ADD - GAOLATHE - Copy</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>contact_number</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Mandatory field missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>ADD - GAOLATHE - Copy</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>ADD - GAOLATHE - Copy</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>amolemo.mantiwe@gmail.com</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>381346789</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>STATIC - AMOLEMO</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>STATIC</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>contact_number</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>748710497</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Mandatory field missing</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>381346789</t>
+          <t>ADD - GAOLATHE - Copy</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>STATIC - AMOLEMO</t>
+          <t>ADD - GAOLATHE - Copy</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>STATIC</t>
+          <t>ADD</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>branch_code</t>
+          <t>fund_number</t>
         </is>
       </c>
       <c r="E6" s="2" t="n"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>WARNING</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Branch code not captured</t>
+          <t>Mandatory field missing</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>381346789</t>
+          <t>ADD - GAOLATHE - Copy</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>DIS - AMOLEMO</t>
+          <t>ADD - GAOLATHE - Copy</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>ADD</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>fund_name</t>
+          <t>id_number</t>
         </is>
       </c>
       <c r="E7" s="3" t="n"/>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>WARNING</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Mandatory field missing</t>
+          <t>ID number not captured</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>381346789</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>DIS - AMOLEMO</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>id_number</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2239222827</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>ADD - GAOLATHE - Copy</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>ADD - GAOLATHE - Copy</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>id_expiry_date</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>WARNING</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Unknown ID type 'None' - cannot apply digit validation</t>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>ID expiry date not captured</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>381346789</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>DIS - AMOLEMO</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>id_expiry_date</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="n"/>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>ADD - GAOLATHE - Copy</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>ADD - GAOLATHE - Copy</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>WARNING</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>ID expiry date not captured</t>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Field is blank - cannot validate format</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>381346789</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>DIS - AMOLEMO</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>amolemo.mantiwe@gmail.com</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr"/>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>ADD - GAOLATHE - Copy</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>ADD - GAOLATHE - Copy</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>contact_number</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n"/>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Field is blank</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>381346789</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>DIS - AMOLEMO</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>contact_number</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>748710497</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr"/>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>ADD - GAOLATHE - Copy</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>ADD - GAOLATHE - Copy</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>branch_code</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Branch code not captured</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>381346789</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>DIS - AMOLEMO</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>branch_code</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="n"/>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>ADD - GAOLATHE - Copy</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>ADD - GAOLATHE - Copy</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>fund_number</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>WARNING</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>Branch code not captured</t>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Field is blank</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>381346789</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>DIS - AMOLEMO</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>fund_number</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="n"/>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>ADD - GAOLATHE - Copy</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>ADD - GAOLATHE - Copy</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>fund_category</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Unknown - Fund Name Not Extracted</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>WARNING</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>Field is blank</t>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Fund category could not be determined - fund name unclear</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>381346789</t>
+          <t>DEBIT - GAOLATHE</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>DIS - AMOLEMO</t>
+          <t>DEBIT - GAOLATHE</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>DEBIT</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>fund_category</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Unknown - Fund Name Not Extracted</t>
-        </is>
-      </c>
+          <t>entity_number</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n"/>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>WARNING</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Fund category could not be determined - fund name unclear</t>
+          <t>Mandatory field missing</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>381346789</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>DEBIT - AMOLEMO</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>DEBIT - GAOLATHE</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>DEBIT - GAOLATHE</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>DEBIT</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>instruction_type</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="n"/>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>full_name</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n"/>
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>Mandatory field missing</t>
         </is>
@@ -1636,12 +1487,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>381346789</t>
+          <t>DEBIT - GAOLATHE</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>DEBIT - AMOLEMO</t>
+          <t>DEBIT - GAOLATHE</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1651,527 +1502,919 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>contact_number</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n"/>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Mandatory field missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>DEBIT - GAOLATHE</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>DEBIT - GAOLATHE</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>DEBIT</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>instruction_type</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n"/>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Mandatory field missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT - GAOLATHE</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT - GAOLATHE</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
           <t>id_number</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2239222827</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>WARNING</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>Unknown ID type 'None' - cannot apply digit validation</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>381346789</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>DEBIT - AMOLEMO</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>ID number not captured</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT - GAOLATHE</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT - GAOLATHE</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>DEBIT</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>id_expiry_date</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>03/10/2034</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>381346789</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>DEBIT - AMOLEMO</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>ID expiry date not captured</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT - GAOLATHE</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT - GAOLATHE</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>DEBIT</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>amolemo.mantiwe@gmail.com</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>381346789</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>DEBIT - AMOLEMO</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="E20" s="3" t="n"/>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>Field is blank - cannot validate format</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT - GAOLATHE</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT - GAOLATHE</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>DEBIT</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>contact_number</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>748710497</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>381346789</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>DEBIT - AMOLEMO</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="E21" s="3" t="n"/>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>Field is blank</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT - GAOLATHE</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT - GAOLATHE</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>DEBIT</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>branch_code</t>
         </is>
       </c>
-      <c r="E20" s="2" t="n"/>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="E22" s="3" t="n"/>
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>WARNING</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t>Branch code not captured</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>381346789</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>DEBIT - AMOLEMO</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>DEBIT</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>fund_number</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="n"/>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>Field is blank</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>381346789</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>DEBIT - AMOLEMO</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>DEBIT</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>fund_category</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Unknown - Fund Name Not Extracted</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>Fund category could not be determined - fund name unclear</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>381346789</t>
+          <t>DEBIT - GAOLATHE</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>ADD - AMOLEMO</t>
+          <t>DEBIT - GAOLATHE</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>ADD</t>
+          <t>DEBIT</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>fund_name</t>
+          <t>fund_number</t>
         </is>
       </c>
       <c r="E23" s="3" t="n"/>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>WARNING</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Mandatory field missing</t>
+          <t>Field is blank</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>381346789</t>
+          <t>DEBIT - GAOLATHE</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>ADD - AMOLEMO</t>
+          <t>DEBIT - GAOLATHE</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>ADD</t>
+          <t>DEBIT</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>fund_number</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="n"/>
+          <t>fund_category</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Unknown - Fund Name Not Extracted</t>
+        </is>
+      </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>WARNING</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Mandatory field missing</t>
+          <t>Fund category could not be determined - fund name unclear</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>381346789</t>
+          <t>DIS - GAOLATHE</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>ADD - AMOLEMO</t>
+          <t>DIS - GAOLATHE</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>ADD</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>id_number</t>
+          <t>entity_number</t>
         </is>
       </c>
       <c r="E25" s="2" t="n"/>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>WARNING</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>ID number not captured</t>
+          <t>Mandatory field missing</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>381346789</t>
+          <t>DIS - GAOLATHE</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>ADD - AMOLEMO</t>
+          <t>DIS - GAOLATHE</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>ADD</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>id_expiry_date</t>
+          <t>full_name</t>
         </is>
       </c>
       <c r="E26" s="2" t="n"/>
       <c r="F26" s="2" t="inlineStr">
         <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Mandatory field missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>DIS - GAOLATHE</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>DIS - GAOLATHE</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>contact_number</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n"/>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Mandatory field missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>DIS - GAOLATHE</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>DIS - GAOLATHE</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>id_number</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="n"/>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
           <t>WARNING</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>ID number not captured</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>DIS - GAOLATHE</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>DIS - GAOLATHE</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>id_expiry_date</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="n"/>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>ID expiry date not captured</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>381346789</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>ADD - AMOLEMO</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>DIS - GAOLATHE</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>DIS - GAOLATHE</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>amolemo.mantiwe@gmail.com</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="E30" s="3" t="n"/>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>Field is blank - cannot validate format</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>DIS - GAOLATHE</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>DIS - GAOLATHE</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>contact_number</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="n"/>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>Field is blank</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>DIS - GAOLATHE</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>DIS - GAOLATHE</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>branch_code</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="n"/>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>Branch code not captured</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>DIS - GAOLATHE</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>DIS - GAOLATHE</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>fund_number</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="n"/>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>Field is blank</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>DIS - GAOLATHE</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>DIS - GAOLATHE</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>fund_category</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Unknown - Fund Name Not Extracted</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>Fund category could not be determined - fund name unclear</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>GSGF - GAOLATLHE</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>GSGF - GAOLATLHE</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>DIS_GSG</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>entity_number</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="n"/>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Mandatory field missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>GSGF - GAOLATLHE</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>GSGF - GAOLATLHE</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>DIS_GSG</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>full_name</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="n"/>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Mandatory field missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>GSGF - GAOLATLHE</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>GSGF - GAOLATLHE</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>DIS_GSG</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>contact_number</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="n"/>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Mandatory field missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>GSGF - GAOLATLHE</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>GSGF - GAOLATLHE</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>DIS_GSG</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>id_number</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="n"/>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>ID number not captured</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>GSGF - GAOLATLHE</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>GSGF - GAOLATLHE</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>DIS_GSG</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>id_expiry_date</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="n"/>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>ID expiry date not captured</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>GSGF - GAOLATLHE</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>GSGF - GAOLATLHE</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>DIS_GSG</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="n"/>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>Field is blank - cannot validate format</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>GSGF - GAOLATLHE</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>GSGF - GAOLATLHE</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>DIS_GSG</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>contact_number</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="n"/>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>Field is blank</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>GSGF - GAOLATLHE</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>GSGF - GAOLATLHE</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>DIS_GSG</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>branch_code</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="n"/>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>Branch code not captured</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>GSGF - GAOLATLHE</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>GSGF - GAOLATLHE</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>DIS_GSG</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>fund_category</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>Non-Money Market (GSGF)</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G27" s="4" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>381346789</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>ADD - AMOLEMO</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>contact_number</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>748710497</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G28" s="4" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>381346789</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>ADD - AMOLEMO</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>branch_code</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="n"/>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>Branch code not captured</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>381346789</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>ADD - AMOLEMO</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>fund_number</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="n"/>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>Field is blank</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>381346789</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>ADD - AMOLEMO</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>fund_category</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>Unknown - Fund Name Not Extracted</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>Fund category could not be determined - fund name unclear</t>
-        </is>
-      </c>
+      <c r="G43" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2188,13 +2431,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="27" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="43" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
     <col width="45" customWidth="1" min="11" max="11"/>
@@ -2278,38 +2521,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-01T16:12:22</t>
+          <t>2026-07-01T16:31:41</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>STATIC - AMOLEMO.pdf</t>
+          <t>ADD - GAOLATHE - Copy.pdf</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>STATIC_381346789_MANTIWE_20260701_1_2.pdf</t>
+          <t>ADD_NA_UNKNOWN_20260701_VALIDATIONFAILEDENTITY_NUMBERFULL_NAMECONTACT_NUMBEREMAILFUND_NUMBER.pdf</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>STATIC</t>
+          <t>ADD</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>WARNING</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Captured</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Validation failed: entity_number, full_name, contact_number, email, fund_number</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>Email</t>
@@ -2317,12 +2564,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-01T16:10:18</t>
+          <t>2026-06-29T11:36:32</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\01\NonMoneyMarket\Captured\STATIC_381346789_MANTIWE_20260701_1_2.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\01\NonMoneyMarket\Captured\Rejected\ADD_NA_UNKNOWN_20260701_VALIDATIONFAILEDENTITY_NUMBERFULL_NAMECONTACT_NUMBEREMAILFUND_NUMBER.pdf</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -2340,22 +2587,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-01T16:12:22</t>
+          <t>2026-07-01T16:31:41</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DIS - AMOLEMO.pdf</t>
+          <t>DEBIT - GAOLATHE.pdf</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DIS_381346789_MANTIWE_20260701_VALIDATIONFAILEDFUND_NAME_1.pdf</t>
+          <t>DEBIT_NA_UNKNOWN_20260701_VALIDATIONFAILEDENTITY_NUMBERFULL_NAMECONTACT_NUMBERINSTRUCTION_TYPE_1.pdf</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>DEBIT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -2373,7 +2620,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Validation failed: fund_name</t>
+          <t>Validation failed: entity_number, full_name, contact_number, instruction_type</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -2383,12 +2630,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-07-01T16:10:18</t>
+          <t>2026-06-29T13:09:59</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\01\NonMoneyMarket\Captured\Rejected\DIS_381346789_MANTIWE_20260701_VALIDATIONFAILEDFUND_NAME_1.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\01\NonMoneyMarket\Captured\Rejected\DEBIT_NA_UNKNOWN_20260701_VALIDATIONFAILEDENTITY_NUMBERFULL_NAMECONTACT_NUMBERINSTRUCTION_TYPE_1.pdf</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -2406,22 +2653,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-01T16:12:22</t>
+          <t>2026-07-01T16:31:41</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DEBIT - AMOLEMO.pdf</t>
+          <t>DIS - GAOLATHE.pdf</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DEBIT_381346789_MANTIWE_20260701_VALIDATIONFAILEDINSTRUCTION_TYPE_1.pdf</t>
+          <t>DIS_NA_UNKNOWN_20260701_VALIDATIONFAILEDENTITY_NUMBERFULL_NAMECONTACT_NUMBER.pdf</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>DEBIT</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -2439,7 +2686,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Validation failed: instruction_type</t>
+          <t>Validation failed: entity_number, full_name, contact_number</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -2449,12 +2696,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-07-01T16:10:18</t>
+          <t>2026-06-29T13:10:18</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\01\NonMoneyMarket\Captured\Rejected\DEBIT_381346789_MANTIWE_20260701_VALIDATIONFAILEDINSTRUCTION_TYPE_1.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\01\NonMoneyMarket\Captured\Rejected\DIS_NA_UNKNOWN_20260701_VALIDATIONFAILEDENTITY_NUMBERFULL_NAMECONTACT_NUMBER.pdf</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -2472,22 +2719,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-01T16:12:22</t>
+          <t>2026-07-01T16:31:41</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ADD - AMOLEMO.pdf</t>
+          <t>GSGF - GAOLATLHE.pdf</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ADD_381346789_MANTIWE_20260701_VALIDATIONFAILEDFUND_NAMEFUND_NUMBER_1.pdf</t>
+          <t>DIS_GSG_NA_UNKNOWN_20260701_VALIDATIONFAILEDENTITY_NUMBERFULL_NAMECONTACT_NUMBER.pdf</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ADD</t>
+          <t>DIS_GSG</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -2505,7 +2752,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Validation failed: fund_name, fund_number</t>
+          <t>Validation failed: entity_number, full_name, contact_number</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2515,12 +2762,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-07-01T16:10:18</t>
+          <t>2026-06-29T13:10:41</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\01\NonMoneyMarket\Captured\Rejected\ADD_381346789_MANTIWE_20260701_VALIDATIONFAILEDFUND_NAMEFUND_NUMBER_1.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\01\NonMoneyMarket\Captured\Rejected\DIS_GSG_NA_UNKNOWN_20260701_VALIDATIONFAILEDENTITY_NUMBERFULL_NAMECONTACT_NUMBER.pdf</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">

--- a/output/BIFM_UT_Processing_Report.xlsx
+++ b/output/BIFM_UT_Processing_Report.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,8 +33,13 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <i val="1"/>
+      <color rgb="006B6B6B"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -45,6 +50,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00305496"/>
         <bgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5F5F5"/>
+        <bgColor rgb="00F5F5F5"/>
       </patternFill>
     </fill>
     <fill>
@@ -78,12 +89,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -449,30 +461,29 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:T3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="26" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="37" customWidth="1" min="15" max="15"/>
-    <col width="19" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="16" customWidth="1" min="18" max="18"/>
-    <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="13" customWidth="1" min="20" max="20"/>
-    <col width="22" customWidth="1" min="21" max="21"/>
+    <col width="41" customWidth="1" min="4" max="4"/>
+    <col width="41" customWidth="1" min="5" max="5"/>
+    <col width="41" customWidth="1" min="6" max="6"/>
+    <col width="41" customWidth="1" min="7" max="7"/>
+    <col width="41" customWidth="1" min="8" max="8"/>
+    <col width="41" customWidth="1" min="9" max="9"/>
+    <col width="41" customWidth="1" min="10" max="10"/>
+    <col width="41" customWidth="1" min="11" max="11"/>
+    <col width="41" customWidth="1" min="12" max="12"/>
+    <col width="41" customWidth="1" min="13" max="13"/>
+    <col width="41" customWidth="1" min="14" max="14"/>
+    <col width="41" customWidth="1" min="15" max="15"/>
+    <col width="41" customWidth="1" min="16" max="16"/>
+    <col width="41" customWidth="1" min="17" max="17"/>
+    <col width="41" customWidth="1" min="18" max="18"/>
+    <col width="41" customWidth="1" min="19" max="19"/>
+    <col width="41" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -548,35 +559,30 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>fund_name</t>
+          <t>bank_account_name</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>bank_account_name</t>
+          <t>bank_name</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>bank_name</t>
+          <t>account_number</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>account_number</t>
+          <t>branch_name</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>branch_name</t>
+          <t>branch_code</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>branch_code</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>account_type_banking</t>
         </is>
@@ -653,37 +659,122 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>BIFM Global Sustainable Growth Fund</t>
+          <t>Onalenya Bogosing</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Onalenya Bogosiny</t>
+          <t>ABSA</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>ABSA</t>
+          <t>1078631</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1078631</t>
+          <t>MALL</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>MALL</t>
+          <t>290167</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>290167</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
           <t>Current</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr"/>
+      <c r="B3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="inlineStr"/>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>100% confidence — 1/1 document(s) agree</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>100% confidence — 1/1 document(s) agree</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>100% confidence — 1/1 document(s) agree</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>100% confidence — 1/1 document(s) agree</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>100% confidence — 1/1 document(s) agree</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>100% confidence — 1/1 document(s) agree</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>100% confidence — 1/1 document(s) agree</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>100% confidence — 1/1 document(s) agree</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>100% confidence — 1/1 document(s) agree</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>100% confidence — 1/1 document(s) agree</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>100% confidence — 1/1 document(s) agree</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>100% confidence — 1/1 document(s) agree</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>100% confidence — 1/1 document(s) agree</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>100% confidence — 1/1 document(s) agree</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>100% confidence — 1/1 document(s) agree</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>100% confidence — 1/1 document(s) agree</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>100% confidence — 1/1 document(s) agree</t>
         </is>
       </c>
     </row>
@@ -698,20 +789,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP6"/>
+  <dimension ref="A1:AP11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="31" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="33" customWidth="1" min="7" max="7"/>
     <col width="37" customWidth="1" min="8" max="8"/>
     <col width="35" customWidth="1" min="9" max="9"/>
     <col width="42" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="29" customWidth="1" min="11" max="11"/>
     <col width="27" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="45" customWidth="1" min="14" max="14"/>
@@ -719,30 +810,30 @@
     <col width="21" customWidth="1" min="16" max="16"/>
     <col width="21" customWidth="1" min="17" max="17"/>
     <col width="15" customWidth="1" min="18" max="18"/>
-    <col width="16" customWidth="1" min="19" max="19"/>
-    <col width="22" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
-    <col width="19" customWidth="1" min="22" max="22"/>
-    <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="16" customWidth="1" min="24" max="24"/>
-    <col width="13" customWidth="1" min="25" max="25"/>
-    <col width="13" customWidth="1" min="26" max="26"/>
-    <col width="22" customWidth="1" min="27" max="27"/>
-    <col width="18" customWidth="1" min="28" max="28"/>
-    <col width="18" customWidth="1" min="29" max="29"/>
-    <col width="20" customWidth="1" min="30" max="30"/>
-    <col width="19" customWidth="1" min="31" max="31"/>
-    <col width="16" customWidth="1" min="32" max="32"/>
-    <col width="18" customWidth="1" min="33" max="33"/>
-    <col width="18" customWidth="1" min="34" max="34"/>
-    <col width="23" customWidth="1" min="35" max="35"/>
-    <col width="19" customWidth="1" min="36" max="36"/>
-    <col width="19" customWidth="1" min="37" max="37"/>
-    <col width="18" customWidth="1" min="38" max="38"/>
-    <col width="12" customWidth="1" min="39" max="39"/>
-    <col width="26" customWidth="1" min="40" max="40"/>
-    <col width="18" customWidth="1" min="41" max="41"/>
-    <col width="12" customWidth="1" min="42" max="42"/>
+    <col width="45" customWidth="1" min="19" max="19"/>
+    <col width="45" customWidth="1" min="20" max="20"/>
+    <col width="33" customWidth="1" min="21" max="21"/>
+    <col width="45" customWidth="1" min="22" max="22"/>
+    <col width="45" customWidth="1" min="23" max="23"/>
+    <col width="45" customWidth="1" min="24" max="24"/>
+    <col width="45" customWidth="1" min="25" max="25"/>
+    <col width="45" customWidth="1" min="26" max="26"/>
+    <col width="45" customWidth="1" min="27" max="27"/>
+    <col width="33" customWidth="1" min="28" max="28"/>
+    <col width="33" customWidth="1" min="29" max="29"/>
+    <col width="33" customWidth="1" min="30" max="30"/>
+    <col width="33" customWidth="1" min="31" max="31"/>
+    <col width="45" customWidth="1" min="32" max="32"/>
+    <col width="29" customWidth="1" min="33" max="33"/>
+    <col width="33" customWidth="1" min="34" max="34"/>
+    <col width="29" customWidth="1" min="35" max="35"/>
+    <col width="33" customWidth="1" min="36" max="36"/>
+    <col width="33" customWidth="1" min="37" max="37"/>
+    <col width="33" customWidth="1" min="38" max="38"/>
+    <col width="33" customWidth="1" min="39" max="39"/>
+    <col width="33" customWidth="1" min="40" max="40"/>
+    <col width="33" customWidth="1" min="41" max="41"/>
+    <col width="33" customWidth="1" min="42" max="42"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -958,736 +1049,1312 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>GSGF - ONALENNA BOGOSING</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>DIS_GSG</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Disinvestment Form (GSGF)</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>38344272</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>ONALENYA LORATO BOGOSING</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>224922314</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>BIFM Global Sustainable Growth Fund</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>Non-Money Market (GSGF)</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>Quarterly - 7th of last month of quarter</t>
         </is>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="K2" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>WARNING</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>Captured</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="N2" s="3" t="inlineStr"/>
+      <c r="O2" s="3" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01T16:59:40</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
+      <c r="P2" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-01T22:24:05</t>
+        </is>
+      </c>
+      <c r="Q2" s="3" t="inlineStr">
         <is>
           <t>marvel.ai-local-poc</t>
         </is>
       </c>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr">
+      <c r="R2" s="3" t="inlineStr"/>
+      <c r="S2" s="3" t="inlineStr">
         <is>
           <t>76749303</t>
         </is>
       </c>
-      <c r="T2" s="2" t="inlineStr">
+      <c r="T2" s="3" t="inlineStr">
         <is>
           <t>obogosinge@gmail.com</t>
         </is>
       </c>
-      <c r="U2" s="2" t="inlineStr"/>
-      <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t>Onalenya Bogosiny</t>
-        </is>
-      </c>
-      <c r="W2" s="2" t="inlineStr">
+      <c r="U2" s="3" t="inlineStr"/>
+      <c r="V2" s="3" t="inlineStr">
+        <is>
+          <t>Onalenya Bogosing</t>
+        </is>
+      </c>
+      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>ABSA</t>
         </is>
       </c>
-      <c r="X2" s="2" t="inlineStr">
+      <c r="X2" s="3" t="inlineStr">
         <is>
           <t>1078631</t>
         </is>
       </c>
-      <c r="Y2" s="2" t="inlineStr">
+      <c r="Y2" s="3" t="inlineStr">
         <is>
           <t>MALL</t>
         </is>
       </c>
-      <c r="Z2" s="2" t="inlineStr">
+      <c r="Z2" s="3" t="inlineStr">
         <is>
           <t>290167</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
+      <c r="AA2" s="3" t="inlineStr">
         <is>
           <t>Current</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr"/>
-      <c r="AC2" s="2" t="inlineStr"/>
-      <c r="AD2" s="2" t="inlineStr"/>
-      <c r="AE2" s="2" t="inlineStr"/>
-      <c r="AF2" s="2" t="inlineStr"/>
-      <c r="AG2" s="2" t="inlineStr">
+      <c r="AB2" s="3" t="inlineStr"/>
+      <c r="AC2" s="3" t="inlineStr"/>
+      <c r="AD2" s="3" t="inlineStr"/>
+      <c r="AE2" s="3" t="inlineStr"/>
+      <c r="AF2" s="3" t="inlineStr"/>
+      <c r="AG2" s="3" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="AH2" s="2" t="inlineStr"/>
-      <c r="AI2" s="2" t="inlineStr"/>
-      <c r="AJ2" s="2" t="inlineStr"/>
-      <c r="AK2" s="2" t="inlineStr"/>
-      <c r="AL2" s="2" t="inlineStr"/>
-      <c r="AM2" s="2" t="inlineStr"/>
-      <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr"/>
-      <c r="AP2" s="2" t="inlineStr"/>
+      <c r="AH2" s="3" t="inlineStr"/>
+      <c r="AI2" s="3" t="inlineStr"/>
+      <c r="AJ2" s="3" t="inlineStr"/>
+      <c r="AK2" s="3" t="inlineStr"/>
+      <c r="AL2" s="3" t="inlineStr"/>
+      <c r="AM2" s="3" t="inlineStr"/>
+      <c r="AN2" s="3" t="inlineStr"/>
+      <c r="AO2" s="3" t="inlineStr"/>
+      <c r="AP2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr"/>
+      <c r="B3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>100% confidence — extracted</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>100% confidence — extracted</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>100% confidence — extracted</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>100% confidence — extracted</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>100% confidence — extracted</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr"/>
+      <c r="N3" s="2" t="inlineStr"/>
+      <c r="O3" s="2" t="inlineStr"/>
+      <c r="P3" s="2" t="inlineStr"/>
+      <c r="Q3" s="2" t="inlineStr"/>
+      <c r="R3" s="2" t="inlineStr"/>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+        </is>
+      </c>
+      <c r="U3" s="2" t="inlineStr"/>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+        </is>
+      </c>
+      <c r="W3" s="2" t="inlineStr">
+        <is>
+          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+        </is>
+      </c>
+      <c r="X3" s="2" t="inlineStr">
+        <is>
+          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+        </is>
+      </c>
+      <c r="Y3" s="2" t="inlineStr">
+        <is>
+          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+        </is>
+      </c>
+      <c r="Z3" s="2" t="inlineStr">
+        <is>
+          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
+          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AC3" s="2" t="inlineStr"/>
+      <c r="AD3" s="2" t="inlineStr"/>
+      <c r="AE3" s="2" t="inlineStr"/>
+      <c r="AF3" s="2" t="inlineStr"/>
+      <c r="AG3" s="2" t="inlineStr">
+        <is>
+          <t>100% confidence — extracted</t>
+        </is>
+      </c>
+      <c r="AH3" s="2" t="inlineStr"/>
+      <c r="AI3" s="2" t="inlineStr"/>
+      <c r="AJ3" s="2" t="inlineStr"/>
+      <c r="AK3" s="2" t="inlineStr"/>
+      <c r="AL3" s="2" t="inlineStr"/>
+      <c r="AM3" s="2" t="inlineStr"/>
+      <c r="AN3" s="2" t="inlineStr"/>
+      <c r="AO3" s="2" t="inlineStr"/>
+      <c r="AP3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>KYC - ONALENNA</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>KYC</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>KYC (Know Your Customer)</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>38344272</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>ONALENYA LORATO BOGOSING</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>224922314</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>16/11/1993</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
-      <c r="J3" s="3" t="inlineStr"/>
-      <c r="K3" s="3" t="inlineStr"/>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="4" t="inlineStr"/>
+      <c r="J4" s="4" t="inlineStr"/>
+      <c r="K4" s="4" t="inlineStr"/>
+      <c r="L4" s="4" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="M4" s="4" t="inlineStr">
         <is>
           <t>Rejected</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="N4" s="4" t="inlineStr">
         <is>
           <t>Validation failed: id_expiry_date</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="P3" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-01T16:59:40</t>
-        </is>
-      </c>
-      <c r="Q3" s="3" t="inlineStr">
+      <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-01T22:24:05</t>
+        </is>
+      </c>
+      <c r="Q4" s="4" t="inlineStr">
         <is>
           <t>marvel.ai-local-poc</t>
         </is>
       </c>
-      <c r="R3" s="3" t="inlineStr"/>
-      <c r="S3" s="3" t="inlineStr">
+      <c r="R4" s="4" t="inlineStr"/>
+      <c r="S4" s="4" t="inlineStr">
         <is>
           <t>76749303</t>
         </is>
       </c>
-      <c r="T3" s="3" t="inlineStr">
+      <c r="T4" s="4" t="inlineStr">
         <is>
           <t>obogosinge@gmail.com</t>
         </is>
       </c>
-      <c r="U3" s="3" t="inlineStr">
+      <c r="U4" s="4" t="inlineStr">
         <is>
           <t>MOTSWANA</t>
         </is>
       </c>
-      <c r="V3" s="3" t="inlineStr">
-        <is>
-          <t>Onalenya Bogosiny</t>
-        </is>
-      </c>
-      <c r="W3" s="3" t="inlineStr">
+      <c r="V4" s="4" t="inlineStr">
+        <is>
+          <t>Onalenya Bogosing</t>
+        </is>
+      </c>
+      <c r="W4" s="4" t="inlineStr">
         <is>
           <t>ABSA</t>
         </is>
       </c>
-      <c r="X3" s="3" t="inlineStr">
+      <c r="X4" s="4" t="inlineStr">
         <is>
           <t>1078631</t>
         </is>
       </c>
-      <c r="Y3" s="3" t="inlineStr">
+      <c r="Y4" s="4" t="inlineStr">
         <is>
           <t>MALL</t>
         </is>
       </c>
-      <c r="Z3" s="3" t="inlineStr">
+      <c r="Z4" s="4" t="inlineStr">
         <is>
           <t>290167</t>
         </is>
       </c>
-      <c r="AA3" s="3" t="inlineStr">
+      <c r="AA4" s="4" t="inlineStr">
         <is>
           <t>Current</t>
         </is>
       </c>
-      <c r="AB3" s="3" t="inlineStr">
+      <c r="AB4" s="4" t="inlineStr">
         <is>
           <t>Joint Signature</t>
         </is>
       </c>
-      <c r="AC3" s="3" t="inlineStr">
+      <c r="AC4" s="4" t="inlineStr">
         <is>
           <t>BOTSWANA</t>
         </is>
       </c>
-      <c r="AD3" s="3" t="inlineStr">
+      <c r="AD4" s="4" t="inlineStr">
         <is>
           <t>THE UNITED NATIONS</t>
         </is>
       </c>
-      <c r="AE3" s="3" t="inlineStr">
+      <c r="AE4" s="4" t="inlineStr">
         <is>
           <t>ONALENYA BOGOSING</t>
         </is>
       </c>
-      <c r="AF3" s="3" t="inlineStr">
+      <c r="AF4" s="4" t="inlineStr">
         <is>
           <t>11/02/2026</t>
         </is>
       </c>
-      <c r="AG3" s="3" t="inlineStr"/>
-      <c r="AH3" s="3" t="b">
+      <c r="AG4" s="4" t="inlineStr"/>
+      <c r="AH4" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="AI3" s="3" t="inlineStr">
+      <c r="AI4" s="4" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
       </c>
-      <c r="AJ3" s="3" t="b">
+      <c r="AJ4" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="AK3" s="3" t="b">
+      <c r="AK4" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="AL3" s="3" t="b">
+      <c r="AL4" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="AM3" s="3" t="inlineStr">
+      <c r="AM4" s="4" t="inlineStr">
         <is>
           <t>DIPLOMAT</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
+      <c r="AN4" s="4" t="inlineStr">
         <is>
           <t>PLOT 40353, BLOCKS  GABS</t>
         </is>
       </c>
-      <c r="AO3" s="3" t="inlineStr">
+      <c r="AO4" s="4" t="inlineStr">
         <is>
           <t>Salary</t>
         </is>
       </c>
-      <c r="AP3" s="3" t="inlineStr">
+      <c r="AP4" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr"/>
+      <c r="B5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>100% confidence — extracted</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>100% confidence — extracted p.1</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>100% confidence — extracted p.1</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>100% confidence — extracted p.1</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100% confidence — extracted p.1</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="R5" s="2" t="inlineStr"/>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>100% confidence — extracted p.1</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>100% confidence — extracted p.1</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>100% confidence — extracted p.1</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>100% confidence — extracted p.1</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>100% confidence — extracted p.1</t>
+        </is>
+      </c>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t>100% confidence — extracted p.1</t>
+        </is>
+      </c>
+      <c r="Y5" s="2" t="inlineStr">
+        <is>
+          <t>100% confidence — extracted p.1</t>
+        </is>
+      </c>
+      <c r="Z5" s="2" t="inlineStr">
+        <is>
+          <t>100% confidence — extracted p.1</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
+          <t>100% confidence — extracted p.1</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>100% confidence — extracted p.1</t>
+        </is>
+      </c>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>100% confidence — extracted p.1</t>
+        </is>
+      </c>
+      <c r="AD5" s="2" t="inlineStr">
+        <is>
+          <t>100% confidence — extracted p.1</t>
+        </is>
+      </c>
+      <c r="AE5" s="2" t="inlineStr">
+        <is>
+          <t>100% confidence — extracted p.1</t>
+        </is>
+      </c>
+      <c r="AF5" s="2" t="inlineStr">
+        <is>
+          <t>100% confidence — extracted p.1</t>
+        </is>
+      </c>
+      <c r="AG5" s="2" t="inlineStr"/>
+      <c r="AH5" s="2" t="inlineStr">
+        <is>
+          <t>100% confidence — extracted p.1</t>
+        </is>
+      </c>
+      <c r="AI5" s="2" t="inlineStr">
+        <is>
+          <t>100% confidence — extracted</t>
+        </is>
+      </c>
+      <c r="AJ5" s="2" t="inlineStr">
+        <is>
+          <t>100% confidence — extracted p.1</t>
+        </is>
+      </c>
+      <c r="AK5" s="2" t="inlineStr">
+        <is>
+          <t>100% confidence — extracted p.1</t>
+        </is>
+      </c>
+      <c r="AL5" s="2" t="inlineStr">
+        <is>
+          <t>100% confidence — extracted p.1</t>
+        </is>
+      </c>
+      <c r="AM5" s="2" t="inlineStr">
+        <is>
+          <t>100% confidence — extracted p.1</t>
+        </is>
+      </c>
+      <c r="AN5" s="2" t="inlineStr">
+        <is>
+          <t>100% confidence — extracted p.1</t>
+        </is>
+      </c>
+      <c r="AO5" s="2" t="inlineStr">
+        <is>
+          <t>100% confidence — extracted p.1</t>
+        </is>
+      </c>
+      <c r="AP5" s="2" t="inlineStr">
+        <is>
+          <t>100% confidence — extracted p.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>DIS - ONALENNA BOGOSING</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>DIS</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>Disinvestment Form (Standard)</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>38344272</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>ONALENYA LORATO BOGOSING</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>224922314</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>BIFM Global Sustainable Growth Fund</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr"/>
+      <c r="I6" s="4" t="inlineStr">
         <is>
           <t>Unknown - Fund Name Not Extracted</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="K4" s="2" t="n">
+      <c r="K6" s="4" t="n">
         <v>99</v>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>Captured</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr"/>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>Validation failed: fund_name</t>
+        </is>
+      </c>
+      <c r="O6" s="4" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01T16:59:40</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
+      <c r="P6" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-01T22:24:05</t>
+        </is>
+      </c>
+      <c r="Q6" s="4" t="inlineStr">
         <is>
           <t>marvel.ai-local-poc</t>
         </is>
       </c>
-      <c r="R4" s="2" t="inlineStr"/>
-      <c r="S4" s="2" t="inlineStr">
+      <c r="R6" s="4" t="inlineStr"/>
+      <c r="S6" s="4" t="inlineStr">
         <is>
           <t>76749303</t>
         </is>
       </c>
-      <c r="T4" s="2" t="inlineStr">
+      <c r="T6" s="4" t="inlineStr">
         <is>
           <t>obogosinge@gmail.com</t>
         </is>
       </c>
-      <c r="U4" s="2" t="inlineStr"/>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Onalenya Bogosiny</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
+      <c r="U6" s="4" t="inlineStr"/>
+      <c r="V6" s="4" t="inlineStr">
+        <is>
+          <t>Onalenya Bogosing</t>
+        </is>
+      </c>
+      <c r="W6" s="4" t="inlineStr">
         <is>
           <t>ABSA</t>
         </is>
       </c>
-      <c r="X4" s="2" t="inlineStr">
+      <c r="X6" s="4" t="inlineStr">
         <is>
           <t>1078631</t>
         </is>
       </c>
-      <c r="Y4" s="2" t="inlineStr">
+      <c r="Y6" s="4" t="inlineStr">
         <is>
           <t>MALL</t>
         </is>
       </c>
-      <c r="Z4" s="2" t="inlineStr">
+      <c r="Z6" s="4" t="inlineStr">
         <is>
           <t>290167</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
+      <c r="AA6" s="4" t="inlineStr">
         <is>
           <t>Current</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr"/>
-      <c r="AC4" s="2" t="inlineStr"/>
-      <c r="AD4" s="2" t="inlineStr"/>
-      <c r="AE4" s="2" t="inlineStr"/>
-      <c r="AF4" s="2" t="inlineStr"/>
-      <c r="AG4" s="2" t="inlineStr">
+      <c r="AB6" s="4" t="inlineStr"/>
+      <c r="AC6" s="4" t="inlineStr"/>
+      <c r="AD6" s="4" t="inlineStr"/>
+      <c r="AE6" s="4" t="inlineStr"/>
+      <c r="AF6" s="4" t="inlineStr"/>
+      <c r="AG6" s="4" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="AH4" s="2" t="inlineStr"/>
-      <c r="AI4" s="2" t="inlineStr"/>
-      <c r="AJ4" s="2" t="inlineStr"/>
-      <c r="AK4" s="2" t="inlineStr"/>
-      <c r="AL4" s="2" t="inlineStr"/>
-      <c r="AM4" s="2" t="inlineStr"/>
-      <c r="AN4" s="2" t="inlineStr"/>
-      <c r="AO4" s="2" t="inlineStr"/>
-      <c r="AP4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="AH6" s="4" t="inlineStr"/>
+      <c r="AI6" s="4" t="inlineStr"/>
+      <c r="AJ6" s="4" t="inlineStr"/>
+      <c r="AK6" s="4" t="inlineStr"/>
+      <c r="AL6" s="4" t="inlineStr"/>
+      <c r="AM6" s="4" t="inlineStr"/>
+      <c r="AN6" s="4" t="inlineStr"/>
+      <c r="AO6" s="4" t="inlineStr"/>
+      <c r="AP6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr"/>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>100% confidence — extracted</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100% confidence — extracted</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>100% confidence — extracted</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>100% confidence — extracted</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr"/>
+      <c r="O7" s="2" t="inlineStr"/>
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr"/>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr"/>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
+          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AD7" s="2" t="inlineStr"/>
+      <c r="AE7" s="2" t="inlineStr"/>
+      <c r="AF7" s="2" t="inlineStr"/>
+      <c r="AG7" s="2" t="inlineStr">
+        <is>
+          <t>100% confidence — extracted</t>
+        </is>
+      </c>
+      <c r="AH7" s="2" t="inlineStr"/>
+      <c r="AI7" s="2" t="inlineStr"/>
+      <c r="AJ7" s="2" t="inlineStr"/>
+      <c r="AK7" s="2" t="inlineStr"/>
+      <c r="AL7" s="2" t="inlineStr"/>
+      <c r="AM7" s="2" t="inlineStr"/>
+      <c r="AN7" s="2" t="inlineStr"/>
+      <c r="AO7" s="2" t="inlineStr"/>
+      <c r="AP7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>DEBIT - ONALENNA BOGOSING</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>DEBIT</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>Debit Order Form</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>38344272</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>ONALENYA LORATO BOGOSING</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>224922314</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>BIFM Global Sustainable Growth Fund</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>Unknown - Fund Name Not Extracted</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="J8" s="4" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="K8" s="4" t="n">
         <v>99</v>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="L8" s="4" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="M8" s="4" t="inlineStr">
         <is>
           <t>Rejected</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="N8" s="4" t="inlineStr">
         <is>
           <t>Validation failed: instruction_type, id_expiry_date</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
+      <c r="O8" s="4" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="P5" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-01T16:59:40</t>
-        </is>
-      </c>
-      <c r="Q5" s="3" t="inlineStr">
+      <c r="P8" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-01T22:24:05</t>
+        </is>
+      </c>
+      <c r="Q8" s="4" t="inlineStr">
         <is>
           <t>marvel.ai-local-poc</t>
         </is>
       </c>
-      <c r="R5" s="3" t="inlineStr"/>
-      <c r="S5" s="3" t="inlineStr">
+      <c r="R8" s="4" t="inlineStr"/>
+      <c r="S8" s="4" t="inlineStr">
         <is>
           <t>76749303</t>
         </is>
       </c>
-      <c r="T5" s="3" t="inlineStr">
+      <c r="T8" s="4" t="inlineStr">
         <is>
           <t>obogosinge@gmail.com</t>
         </is>
       </c>
-      <c r="U5" s="3" t="inlineStr"/>
-      <c r="V5" s="3" t="inlineStr">
-        <is>
-          <t>Onalenya Bogosiny</t>
-        </is>
-      </c>
-      <c r="W5" s="3" t="inlineStr">
+      <c r="U8" s="4" t="inlineStr"/>
+      <c r="V8" s="4" t="inlineStr">
+        <is>
+          <t>Onalenya Bogosing</t>
+        </is>
+      </c>
+      <c r="W8" s="4" t="inlineStr">
         <is>
           <t>ABSA</t>
         </is>
       </c>
-      <c r="X5" s="3" t="inlineStr">
+      <c r="X8" s="4" t="inlineStr">
         <is>
           <t>1078631</t>
         </is>
       </c>
-      <c r="Y5" s="3" t="inlineStr">
+      <c r="Y8" s="4" t="inlineStr">
         <is>
           <t>MALL</t>
         </is>
       </c>
-      <c r="Z5" s="3" t="inlineStr">
+      <c r="Z8" s="4" t="inlineStr">
         <is>
           <t>290167</t>
         </is>
       </c>
-      <c r="AA5" s="3" t="inlineStr">
+      <c r="AA8" s="4" t="inlineStr">
         <is>
           <t>Current</t>
         </is>
       </c>
-      <c r="AB5" s="3" t="inlineStr"/>
-      <c r="AC5" s="3" t="inlineStr"/>
-      <c r="AD5" s="3" t="inlineStr"/>
-      <c r="AE5" s="3" t="inlineStr"/>
-      <c r="AF5" s="3" t="inlineStr">
+      <c r="AB8" s="4" t="inlineStr"/>
+      <c r="AC8" s="4" t="inlineStr"/>
+      <c r="AD8" s="4" t="inlineStr"/>
+      <c r="AE8" s="4" t="inlineStr"/>
+      <c r="AF8" s="4" t="inlineStr">
         <is>
           <t>11/02/2026</t>
         </is>
       </c>
-      <c r="AG5" s="3" t="inlineStr"/>
-      <c r="AH5" s="3" t="inlineStr"/>
-      <c r="AI5" s="3" t="inlineStr"/>
-      <c r="AJ5" s="3" t="inlineStr"/>
-      <c r="AK5" s="3" t="inlineStr"/>
-      <c r="AL5" s="3" t="inlineStr"/>
-      <c r="AM5" s="3" t="inlineStr"/>
-      <c r="AN5" s="3" t="inlineStr"/>
-      <c r="AO5" s="3" t="inlineStr"/>
-      <c r="AP5" s="3" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="AG8" s="4" t="inlineStr"/>
+      <c r="AH8" s="4" t="inlineStr"/>
+      <c r="AI8" s="4" t="inlineStr"/>
+      <c r="AJ8" s="4" t="inlineStr"/>
+      <c r="AK8" s="4" t="inlineStr"/>
+      <c r="AL8" s="4" t="inlineStr"/>
+      <c r="AM8" s="4" t="inlineStr"/>
+      <c r="AN8" s="4" t="inlineStr"/>
+      <c r="AO8" s="4" t="inlineStr"/>
+      <c r="AP8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr"/>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>100% confidence — extracted</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100% confidence — extracted</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>100% confidence — extracted</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>100% confidence — extracted</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr"/>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr"/>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr"/>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AD9" s="2" t="inlineStr"/>
+      <c r="AE9" s="2" t="inlineStr"/>
+      <c r="AF9" s="2" t="inlineStr">
+        <is>
+          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+        </is>
+      </c>
+      <c r="AG9" s="2" t="inlineStr"/>
+      <c r="AH9" s="2" t="inlineStr"/>
+      <c r="AI9" s="2" t="inlineStr"/>
+      <c r="AJ9" s="2" t="inlineStr"/>
+      <c r="AK9" s="2" t="inlineStr"/>
+      <c r="AL9" s="2" t="inlineStr"/>
+      <c r="AM9" s="2" t="inlineStr"/>
+      <c r="AN9" s="2" t="inlineStr"/>
+      <c r="AO9" s="2" t="inlineStr"/>
+      <c r="AP9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>ADD - ONALENNA</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>ADD</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>Additional Investment Form</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>38344272</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>ONALENYA LORATO BOGOSING</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr"/>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>BIFM Global Sustainable Growth Fund</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr"/>
+      <c r="G10" s="4" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr"/>
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>Unknown - Fund Name Not Extracted</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="J10" s="4" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="K10" s="4" t="n">
         <v>99</v>
       </c>
-      <c r="L6" s="3" t="inlineStr">
+      <c r="L10" s="4" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="M6" s="3" t="inlineStr">
+      <c r="M10" s="4" t="inlineStr">
         <is>
           <t>Rejected</t>
         </is>
       </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t>Validation failed: fund_number</t>
-        </is>
-      </c>
-      <c r="O6" s="3" t="inlineStr">
+      <c r="N10" s="4" t="inlineStr">
+        <is>
+          <t>Validation failed: fund_name, fund_number</t>
+        </is>
+      </c>
+      <c r="O10" s="4" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="P6" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-01T16:59:40</t>
-        </is>
-      </c>
-      <c r="Q6" s="3" t="inlineStr">
+      <c r="P10" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-01T22:24:05</t>
+        </is>
+      </c>
+      <c r="Q10" s="4" t="inlineStr">
         <is>
           <t>marvel.ai-local-poc</t>
         </is>
       </c>
-      <c r="R6" s="3" t="inlineStr"/>
-      <c r="S6" s="3" t="inlineStr">
+      <c r="R10" s="4" t="inlineStr"/>
+      <c r="S10" s="4" t="inlineStr">
         <is>
           <t>76749303</t>
         </is>
       </c>
-      <c r="T6" s="3" t="inlineStr">
+      <c r="T10" s="4" t="inlineStr">
         <is>
           <t>obogosinge@gmail.com</t>
         </is>
       </c>
-      <c r="U6" s="3" t="inlineStr"/>
-      <c r="V6" s="3" t="inlineStr">
-        <is>
-          <t>Onalenya Bogosiny</t>
-        </is>
-      </c>
-      <c r="W6" s="3" t="inlineStr">
+      <c r="U10" s="4" t="inlineStr"/>
+      <c r="V10" s="4" t="inlineStr">
+        <is>
+          <t>Onalenya Bogosing</t>
+        </is>
+      </c>
+      <c r="W10" s="4" t="inlineStr">
         <is>
           <t>ABSA</t>
         </is>
       </c>
-      <c r="X6" s="3" t="inlineStr">
+      <c r="X10" s="4" t="inlineStr">
         <is>
           <t>1078631</t>
         </is>
       </c>
-      <c r="Y6" s="3" t="inlineStr">
+      <c r="Y10" s="4" t="inlineStr">
         <is>
           <t>MALL</t>
         </is>
       </c>
-      <c r="Z6" s="3" t="inlineStr">
+      <c r="Z10" s="4" t="inlineStr">
         <is>
           <t>290167</t>
         </is>
       </c>
-      <c r="AA6" s="3" t="inlineStr">
+      <c r="AA10" s="4" t="inlineStr">
         <is>
           <t>Current</t>
         </is>
       </c>
-      <c r="AB6" s="3" t="inlineStr"/>
-      <c r="AC6" s="3" t="inlineStr"/>
-      <c r="AD6" s="3" t="inlineStr"/>
-      <c r="AE6" s="3" t="inlineStr"/>
-      <c r="AF6" s="3" t="inlineStr"/>
-      <c r="AG6" s="3" t="inlineStr"/>
-      <c r="AH6" s="3" t="inlineStr"/>
-      <c r="AI6" s="3" t="inlineStr"/>
-      <c r="AJ6" s="3" t="inlineStr"/>
-      <c r="AK6" s="3" t="inlineStr"/>
-      <c r="AL6" s="3" t="inlineStr"/>
-      <c r="AM6" s="3" t="inlineStr"/>
-      <c r="AN6" s="3" t="inlineStr"/>
-      <c r="AO6" s="3" t="inlineStr"/>
-      <c r="AP6" s="3" t="inlineStr"/>
+      <c r="AB10" s="4" t="inlineStr"/>
+      <c r="AC10" s="4" t="inlineStr"/>
+      <c r="AD10" s="4" t="inlineStr"/>
+      <c r="AE10" s="4" t="inlineStr"/>
+      <c r="AF10" s="4" t="inlineStr"/>
+      <c r="AG10" s="4" t="inlineStr"/>
+      <c r="AH10" s="4" t="inlineStr"/>
+      <c r="AI10" s="4" t="inlineStr"/>
+      <c r="AJ10" s="4" t="inlineStr"/>
+      <c r="AK10" s="4" t="inlineStr"/>
+      <c r="AL10" s="4" t="inlineStr"/>
+      <c r="AM10" s="4" t="inlineStr"/>
+      <c r="AN10" s="4" t="inlineStr"/>
+      <c r="AO10" s="4" t="inlineStr"/>
+      <c r="AP10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr"/>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>100% confidence — extracted</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100% confidence — extracted</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>100% confidence — extracted</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>100% confidence — extracted</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr"/>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr"/>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr"/>
+      <c r="AD11" s="2" t="inlineStr"/>
+      <c r="AE11" s="2" t="inlineStr"/>
+      <c r="AF11" s="2" t="inlineStr"/>
+      <c r="AG11" s="2" t="inlineStr"/>
+      <c r="AH11" s="2" t="inlineStr"/>
+      <c r="AI11" s="2" t="inlineStr"/>
+      <c r="AJ11" s="2" t="inlineStr"/>
+      <c r="AK11" s="2" t="inlineStr"/>
+      <c r="AL11" s="2" t="inlineStr"/>
+      <c r="AM11" s="2" t="inlineStr"/>
+      <c r="AN11" s="2" t="inlineStr"/>
+      <c r="AO11" s="2" t="inlineStr"/>
+      <c r="AP11" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1748,7 +2415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1798,715 +2465,711 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>38344272</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>KYC - ONALENNA</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>KYC</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>id_number</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>224922314</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>WARNING</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Unknown ID type 'None' - cannot apply digit validation</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>38344272</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>KYC - ONALENNA</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>KYC</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>gender</t>
         </is>
       </c>
-      <c r="E3" s="4" t="n"/>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Gender derivation not applicable for this ID type</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>38344272</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>KYC - ONALENNA</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>KYC</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>id_expiry_date</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>11/02/2026</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>ID expiry date is not in the future</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>38344272</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>KYC - ONALENNA</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>KYC</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>date_of_birth</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>16/11/1993</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr"/>
+      <c r="G5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>38344272</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>KYC - ONALENNA</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>KYC</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>obogosinge@gmail.com</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>38344272</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>KYC - ONALENNA</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>KYC</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>contact_number</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>76749303</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr"/>
+      <c r="G7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>38344272</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>KYC - ONALENNA</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>KYC</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>branch_code</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>290167</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr"/>
+      <c r="G8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>38344272</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>KYC - ONALENNA</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>KYC</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>kyc_completeness_flag</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>38344272</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>GSGF - ONALENNA BOGOSING</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>DIS_GSG</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>id_number</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>224922314</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>WARNING</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>Unknown ID type 'None' - cannot apply digit validation</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>38344272</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>GSGF - ONALENNA BOGOSING</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>DIS_GSG</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>id_expiry_date</t>
         </is>
       </c>
-      <c r="E11" s="2" t="n"/>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>WARNING</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>ID expiry date not captured</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>38344272</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>GSGF - ONALENNA BOGOSING</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>DIS_GSG</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>obogosinge@gmail.com</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr"/>
+      <c r="G12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>38344272</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>GSGF - ONALENNA BOGOSING</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>DIS_GSG</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>contact_number</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>76749303</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr"/>
+      <c r="G13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>38344272</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>GSGF - ONALENNA BOGOSING</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>DIS_GSG</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>branch_code</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>290167</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr"/>
+      <c r="G14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>38344272</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>GSGF - ONALENNA BOGOSING</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>DIS_GSG</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>fund_category</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>Non-Money Market (GSGF)</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr"/>
+      <c r="G15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>38344272</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>DIS - ONALENNA BOGOSING</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>DIS</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>fund_name</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="n"/>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>Mandatory field missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>38344272</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>DIS - ONALENNA BOGOSING</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>id_number</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>224922314</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>WARNING</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>Unknown ID type 'None' - cannot apply digit validation</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>38344272</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>DIS - ONALENNA BOGOSING</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>DIS</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>id_expiry_date</t>
         </is>
       </c>
-      <c r="E17" s="2" t="n"/>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>WARNING</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>ID expiry date not captured</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>38344272</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>DIS - ONALENNA BOGOSING</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>DIS</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>obogosinge@gmail.com</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>38344272</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>DIS - ONALENNA BOGOSING</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>DIS</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>contact_number</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>76749303</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>38344272</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>DIS - ONALENNA BOGOSING</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>DIS</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>branch_code</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>290167</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>38344272</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>DIS - ONALENNA BOGOSING</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>DIS</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>fund_number</t>
         </is>
       </c>
-      <c r="E21" s="2" t="n"/>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="E22" s="3" t="n"/>
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>WARNING</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t>Field is blank</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>DIS - ONALENNA BOGOSING</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>fund_category</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Unknown - Fund Name Not Extracted</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>Fund category could not be determined - fund name unclear</t>
         </is>
       </c>
     </row>
@@ -2518,65 +3181,65 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
+          <t>DIS - ONALENNA BOGOSING</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>fund_category</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Unknown - Fund Name Not Extracted</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>Fund category could not be determined - fund name unclear</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>38344272</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
           <t>DEBIT - ONALENNA BOGOSING</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>DEBIT</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>instruction_type</t>
         </is>
       </c>
-      <c r="E23" s="3" t="n"/>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="4" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>Mandatory field missing</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>DEBIT - ONALENNA BOGOSING</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>DEBIT</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>id_number</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>224922314</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>Unknown ID type 'None' - cannot apply digit validation</t>
         </is>
       </c>
     </row>
@@ -2598,22 +3261,22 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>id_expiry_date</t>
+          <t>id_number</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>11/02/2026</t>
+          <t>224922314</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>WARNING</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>ID expiry date is not in the future</t>
+          <t>Unknown ID type 'None' - cannot apply digit validation</t>
         </is>
       </c>
     </row>
@@ -2635,154 +3298,154 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
+          <t>id_expiry_date</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>11/02/2026</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>ID expiry date is not in the future</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>38344272</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>DEBIT - ONALENNA BOGOSING</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>DEBIT</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
           <t>email</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>obogosinge@gmail.com</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G26" s="4" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>38344272</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>DEBIT - ONALENNA BOGOSING</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>DEBIT</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>contact_number</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>76749303</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G27" s="4" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="G28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>38344272</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>DEBIT - ONALENNA BOGOSING</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>DEBIT</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>branch_code</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>290167</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G28" s="4" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>38344272</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>DEBIT - ONALENNA BOGOSING</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>DEBIT</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>fund_number</t>
         </is>
       </c>
-      <c r="E29" s="2" t="n"/>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="E30" s="3" t="n"/>
+      <c r="F30" s="3" t="inlineStr">
         <is>
           <t>WARNING</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G30" s="3" t="inlineStr">
         <is>
           <t>Field is blank</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>DEBIT - ONALENNA BOGOSING</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>DEBIT</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>fund_category</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>Unknown - Fund Name Not Extracted</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>Fund category could not be determined - fund name unclear</t>
         </is>
       </c>
     </row>
@@ -2794,261 +3457,331 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
+          <t>DEBIT - ONALENNA BOGOSING</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>fund_category</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Unknown - Fund Name Not Extracted</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>Fund category could not be determined - fund name unclear</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>38344272</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
           <t>ADD - ONALENNA</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>ADD</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>fund_name</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="n"/>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>Mandatory field missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>38344272</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>ADD - ONALENNA</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>fund_number</t>
         </is>
       </c>
-      <c r="E31" s="3" t="n"/>
-      <c r="F31" s="3" t="inlineStr">
+      <c r="E33" s="4" t="n"/>
+      <c r="F33" s="4" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
+      <c r="G33" s="4" t="inlineStr">
         <is>
           <t>Mandatory field missing</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>38344272</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>ADD - ONALENNA</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>ADD</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>id_number</t>
         </is>
       </c>
-      <c r="E32" s="2" t="n"/>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="E34" s="3" t="n"/>
+      <c r="F34" s="3" t="inlineStr">
         <is>
           <t>WARNING</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G34" s="3" t="inlineStr">
         <is>
           <t>ID number not captured</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>38344272</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>ADD - ONALENNA</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>ADD</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>id_expiry_date</t>
         </is>
       </c>
-      <c r="E33" s="2" t="n"/>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="E35" s="3" t="n"/>
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t>WARNING</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G35" s="3" t="inlineStr">
         <is>
           <t>ID expiry date not captured</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>38344272</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>ADD - ONALENNA</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>ADD</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>obogosinge@gmail.com</t>
         </is>
       </c>
-      <c r="F34" s="4" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G34" s="4" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>38344272</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>ADD - ONALENNA</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>ADD</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>contact_number</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>76749303</t>
         </is>
       </c>
-      <c r="F35" s="4" t="inlineStr">
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G35" s="4" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="G37" s="5" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>38344272</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>ADD - ONALENNA</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>ADD</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>branch_code</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>290167</t>
         </is>
       </c>
-      <c r="F36" s="4" t="inlineStr">
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G36" s="4" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="G38" s="5" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>38344272</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>ADD - ONALENNA</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>ADD</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D39" s="3" t="inlineStr">
         <is>
           <t>fund_number</t>
         </is>
       </c>
-      <c r="E37" s="2" t="n"/>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="E39" s="3" t="n"/>
+      <c r="F39" s="3" t="inlineStr">
         <is>
           <t>WARNING</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G39" s="3" t="inlineStr">
         <is>
           <t>Field is blank</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>38344272</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>ADD - ONALENNA</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>ADD</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D40" s="3" t="inlineStr">
         <is>
           <t>fund_category</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E40" s="3" t="inlineStr">
         <is>
           <t>Unknown - Fund Name Not Extracted</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F40" s="3" t="inlineStr">
         <is>
           <t>WARNING</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G40" s="3" t="inlineStr">
         <is>
           <t>Fund category could not be determined - fund name unclear</t>
         </is>
@@ -3159,7 +3892,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-01T17:00:51</t>
+          <t>2026-07-01T22:25:12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3169,7 +3902,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>KYC_38344272_BOGOSING_20260701_VALIDATIONFAILEDID_EXPIRY_DATE.pdf</t>
+          <t>KYC_38344272_BOGOSING_20260701_VALIDATIONFAILEDID_EXPIRY_DATE_1.pdf</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -3202,12 +3935,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-01T16:59:40</t>
+          <t>2026-07-01T22:24:05</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\01\NonMoneyMarket\Captured\Rejected\KYC_38344272_BOGOSING_20260701_VALIDATIONFAILEDID_EXPIRY_DATE.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\01\NonMoneyMarket\Captured\Rejected\KYC_38344272_BOGOSING_20260701_VALIDATIONFAILEDID_EXPIRY_DATE_1.pdf</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -3225,7 +3958,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-01T17:00:51</t>
+          <t>2026-07-01T22:25:12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3235,7 +3968,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DIS_GSG_38344272_BOGOSING_20260701.pdf</t>
+          <t>DIS_GSG_38344272_BOGOSING_20260701_1.pdf</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -3264,12 +3997,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-07-01T16:59:40</t>
+          <t>2026-07-01T22:24:05</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\01\NonMoneyMarket\Captured\DIS_GSG_38344272_BOGOSING_20260701.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\01\NonMoneyMarket\Captured\DIS_GSG_38344272_BOGOSING_20260701_1.pdf</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -3287,7 +4020,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-01T17:00:51</t>
+          <t>2026-07-01T22:25:12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3297,7 +4030,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DIS_38344272_BOGOSING_20260701.pdf</t>
+          <t>DIS_38344272_BOGOSING_20260701_VALIDATIONFAILEDFUND_NAME.pdf</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -3310,15 +4043,19 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>WARNING</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Captured</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Validation failed: fund_name</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>Email</t>
@@ -3326,12 +4063,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-07-01T16:59:40</t>
+          <t>2026-07-01T22:24:05</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\01\NonMoneyMarket\Captured\DIS_38344272_BOGOSING_20260701.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\01\NonMoneyMarket\Captured\Rejected\DIS_38344272_BOGOSING_20260701_VALIDATIONFAILEDFUND_NAME.pdf</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -3349,7 +4086,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-01T17:00:51</t>
+          <t>2026-07-01T22:25:12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3359,7 +4096,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DEBIT_38344272_BOGOSING_20260701_VALIDATIONFAILEDINSTRUCTION_TYPEID_EXPIRY_DATE.pdf</t>
+          <t>DEBIT_38344272_BOGOSING_20260701_VALIDATIONFAILEDINSTRUCTION_TYPEID_EXPIRY_DATE_1.pdf</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -3392,12 +4129,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-07-01T16:59:40</t>
+          <t>2026-07-01T22:24:05</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\01\NonMoneyMarket\Captured\Rejected\DEBIT_38344272_BOGOSING_20260701_VALIDATIONFAILEDINSTRUCTION_TYPEID_EXPIRY_DATE.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\01\NonMoneyMarket\Captured\Rejected\DEBIT_38344272_BOGOSING_20260701_VALIDATIONFAILEDINSTRUCTION_TYPEID_EXPIRY_DATE_1.pdf</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -3415,7 +4152,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-01T17:00:51</t>
+          <t>2026-07-01T22:25:12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3425,7 +4162,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ADD_38344272_BOGOSING_20260701_VALIDATIONFAILEDFUND_NUMBER.pdf</t>
+          <t>ADD_38344272_BOGOSING_20260701_VALIDATIONFAILEDFUND_NAMEFUND_NUMBER.pdf</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -3448,7 +4185,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Validation failed: fund_number</t>
+          <t>Validation failed: fund_name, fund_number</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -3458,12 +4195,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-07-01T16:59:40</t>
+          <t>2026-07-01T22:24:05</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\01\NonMoneyMarket\Captured\Rejected\ADD_38344272_BOGOSING_20260701_VALIDATIONFAILEDFUND_NUMBER.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\01\NonMoneyMarket\Captured\Rejected\ADD_38344272_BOGOSING_20260701_VALIDATIONFAILEDFUND_NAMEFUND_NUMBER.pdf</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">

--- a/output/BIFM_UT_Processing_Report.xlsx
+++ b/output/BIFM_UT_Processing_Report.xlsx
@@ -464,26 +464,26 @@
   <dimension ref="A1:T3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="41" customWidth="1" min="4" max="4"/>
-    <col width="41" customWidth="1" min="5" max="5"/>
-    <col width="41" customWidth="1" min="6" max="6"/>
-    <col width="41" customWidth="1" min="7" max="7"/>
-    <col width="41" customWidth="1" min="8" max="8"/>
-    <col width="41" customWidth="1" min="9" max="9"/>
-    <col width="41" customWidth="1" min="10" max="10"/>
-    <col width="41" customWidth="1" min="11" max="11"/>
-    <col width="41" customWidth="1" min="12" max="12"/>
-    <col width="41" customWidth="1" min="13" max="13"/>
-    <col width="41" customWidth="1" min="14" max="14"/>
-    <col width="41" customWidth="1" min="15" max="15"/>
-    <col width="41" customWidth="1" min="16" max="16"/>
-    <col width="41" customWidth="1" min="17" max="17"/>
-    <col width="41" customWidth="1" min="18" max="18"/>
-    <col width="41" customWidth="1" min="19" max="19"/>
-    <col width="41" customWidth="1" min="20" max="20"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="9" max="9"/>
+    <col width="45" customWidth="1" min="10" max="10"/>
+    <col width="45" customWidth="1" min="11" max="11"/>
+    <col width="45" customWidth="1" min="12" max="12"/>
+    <col width="45" customWidth="1" min="13" max="13"/>
+    <col width="45" customWidth="1" min="14" max="14"/>
+    <col width="45" customWidth="1" min="15" max="15"/>
+    <col width="45" customWidth="1" min="16" max="16"/>
+    <col width="45" customWidth="1" min="17" max="17"/>
+    <col width="45" customWidth="1" min="18" max="18"/>
+    <col width="45" customWidth="1" min="19" max="19"/>
+    <col width="45" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -519,12 +519,12 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>id_number</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>id_expiry_date</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -591,7 +591,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ONALENNA</t>
+          <t>Nnelo Taunyane</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -599,37 +599,37 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>KYC - ONALENNA.pdf, GSGF - ONALENNA BOGOSING.pdf, DIS - ONALENNA BOGOSING.pdf, DEBIT - ONALENNA BOGOSING.pdf, ADD - ONALENNA.pdf</t>
+          <t>KYC - Nnelo Taunyane.pdf, GSGF - NNELO TAUNYANE.pdf, DIS - NNELO.pdf, DEBIT - NNELO.pdf, ADD - NNELO.pdf</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>38344272</t>
+          <t>381234567</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ONALENYA BOGOSING</t>
+          <t>NNELO TAUNYANE</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ONALENYA LORATO BOGOSING</t>
+          <t>NNELO TAUNYANE</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>224922314</t>
+          <t>Ms</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>11/02/2026</t>
+          <t>11102222</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>16/11/1993</t>
+          <t>01/02/2003</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -639,47 +639,47 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>obogosinge@gmail.com</t>
+          <t>nnelo@bifm.co.bw</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>76749303</t>
+          <t>71234567</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>PLOT 40353, BLOCKS  GABS</t>
+          <t>PLOT 1234 GABORONE</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>DIPLOMAT</t>
+          <t>INTERN</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Onalenya Bogosing</t>
+          <t>NNELO TAUNYANE</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>ABSA</t>
+          <t>STANBIC</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1078631</t>
+          <t>9060001231234</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>MALL</t>
+          <t>FAIRGROUNDS</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>290167</t>
+          <t>064967</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -694,87 +694,87 @@
       <c r="C3" s="2" t="inlineStr"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — 1/1 document(s) agree</t>
+          <t>100% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — 1/1 document(s) agree</t>
+          <t>100% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — 1/1 document(s) agree</t>
+          <t>100% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — 1/1 document(s) agree</t>
+          <t>100% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — 1/1 document(s) agree</t>
+          <t>100% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — 1/1 document(s) agree</t>
+          <t>100% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — 1/1 document(s) agree</t>
+          <t>100% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — 1/1 document(s) agree</t>
+          <t>100% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — 1/1 document(s) agree</t>
+          <t>100% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — 1/1 document(s) agree</t>
+          <t>100% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — 1/1 document(s) agree</t>
+          <t>100% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — 1/1 document(s) agree</t>
+          <t>100% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — 1/1 document(s) agree</t>
+          <t>100% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — 1/1 document(s) agree</t>
+          <t>100% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — 1/1 document(s) agree</t>
+          <t>100% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — 1/1 document(s) agree</t>
+          <t>100% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — 1/1 document(s) agree</t>
+          <t>100% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
         </is>
       </c>
     </row>
@@ -792,48 +792,48 @@
   <dimension ref="A1:AP11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="45" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="33" customWidth="1" min="7" max="7"/>
-    <col width="37" customWidth="1" min="8" max="8"/>
-    <col width="35" customWidth="1" min="9" max="9"/>
-    <col width="42" customWidth="1" min="10" max="10"/>
-    <col width="29" customWidth="1" min="11" max="11"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="9" max="9"/>
+    <col width="45" customWidth="1" min="10" max="10"/>
+    <col width="45" customWidth="1" min="11" max="11"/>
     <col width="27" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="45" customWidth="1" min="14" max="14"/>
+    <col width="43" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="21" customWidth="1" min="16" max="16"/>
     <col width="21" customWidth="1" min="17" max="17"/>
     <col width="15" customWidth="1" min="18" max="18"/>
     <col width="45" customWidth="1" min="19" max="19"/>
     <col width="45" customWidth="1" min="20" max="20"/>
-    <col width="33" customWidth="1" min="21" max="21"/>
+    <col width="45" customWidth="1" min="21" max="21"/>
     <col width="45" customWidth="1" min="22" max="22"/>
     <col width="45" customWidth="1" min="23" max="23"/>
     <col width="45" customWidth="1" min="24" max="24"/>
     <col width="45" customWidth="1" min="25" max="25"/>
     <col width="45" customWidth="1" min="26" max="26"/>
     <col width="45" customWidth="1" min="27" max="27"/>
-    <col width="33" customWidth="1" min="28" max="28"/>
-    <col width="33" customWidth="1" min="29" max="29"/>
-    <col width="33" customWidth="1" min="30" max="30"/>
-    <col width="33" customWidth="1" min="31" max="31"/>
+    <col width="45" customWidth="1" min="28" max="28"/>
+    <col width="45" customWidth="1" min="29" max="29"/>
+    <col width="45" customWidth="1" min="30" max="30"/>
+    <col width="45" customWidth="1" min="31" max="31"/>
     <col width="45" customWidth="1" min="32" max="32"/>
-    <col width="29" customWidth="1" min="33" max="33"/>
-    <col width="33" customWidth="1" min="34" max="34"/>
-    <col width="29" customWidth="1" min="35" max="35"/>
-    <col width="33" customWidth="1" min="36" max="36"/>
-    <col width="33" customWidth="1" min="37" max="37"/>
-    <col width="33" customWidth="1" min="38" max="38"/>
-    <col width="33" customWidth="1" min="39" max="39"/>
-    <col width="33" customWidth="1" min="40" max="40"/>
-    <col width="33" customWidth="1" min="41" max="41"/>
-    <col width="33" customWidth="1" min="42" max="42"/>
+    <col width="45" customWidth="1" min="33" max="33"/>
+    <col width="45" customWidth="1" min="34" max="34"/>
+    <col width="45" customWidth="1" min="35" max="35"/>
+    <col width="45" customWidth="1" min="36" max="36"/>
+    <col width="45" customWidth="1" min="37" max="37"/>
+    <col width="45" customWidth="1" min="38" max="38"/>
+    <col width="45" customWidth="1" min="39" max="39"/>
+    <col width="45" customWidth="1" min="40" max="40"/>
+    <col width="45" customWidth="1" min="41" max="41"/>
+    <col width="45" customWidth="1" min="42" max="42"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -994,52 +994,52 @@
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>id_expiry_date</t>
+          <t>instruction_mode</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>instruction_mode</t>
+          <t>kyc_certified_id</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>kyc_certified_id</t>
+          <t>kyc_completeness_flag</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>kyc_completeness_flag</t>
+          <t>kyc_proof_address</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>kyc_proof_address</t>
+          <t>kyc_proof_banking</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>kyc_proof_banking</t>
+          <t>kyc_proof_source</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>kyc_proof_source</t>
+          <t>occupation</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>occupation</t>
+          <t>residential_address</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>residential_address</t>
+          <t>source_of_income</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>source_of_income</t>
+          <t>title</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
@@ -1051,7 +1051,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>GSGF - ONALENNA BOGOSING</t>
+          <t>GSGF - NNELO TAUNYANE</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -1066,17 +1066,17 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>38344272</t>
+          <t>381234567</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>ONALENYA LORATO BOGOSING</t>
+          <t>NNELO TAUNYANE</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>224922314</t>
+          <t>11102222</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr"/>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>2026-07-01T22:24:05</t>
+          <t>2026-07-02T15:23:47</t>
         </is>
       </c>
       <c r="Q2" s="3" t="inlineStr">
@@ -1127,38 +1127,38 @@
       <c r="R2" s="3" t="inlineStr"/>
       <c r="S2" s="3" t="inlineStr">
         <is>
-          <t>76749303</t>
+          <t>71234567</t>
         </is>
       </c>
       <c r="T2" s="3" t="inlineStr">
         <is>
-          <t>obogosinge@gmail.com</t>
+          <t>nnelo@bifm.co.bw</t>
         </is>
       </c>
       <c r="U2" s="3" t="inlineStr"/>
       <c r="V2" s="3" t="inlineStr">
         <is>
-          <t>Onalenya Bogosing</t>
+          <t>NNELO TAUNYANE</t>
         </is>
       </c>
       <c r="W2" s="3" t="inlineStr">
         <is>
-          <t>ABSA</t>
+          <t>STANBIC</t>
         </is>
       </c>
       <c r="X2" s="3" t="inlineStr">
         <is>
-          <t>1078631</t>
+          <t>9060001231234</t>
         </is>
       </c>
       <c r="Y2" s="3" t="inlineStr">
         <is>
-          <t>MALL</t>
+          <t>FAIRGROUNDS</t>
         </is>
       </c>
       <c r="Z2" s="3" t="inlineStr">
         <is>
-          <t>290167</t>
+          <t>064967</t>
         </is>
       </c>
       <c r="AA2" s="3" t="inlineStr">
@@ -1170,12 +1170,12 @@
       <c r="AC2" s="3" t="inlineStr"/>
       <c r="AD2" s="3" t="inlineStr"/>
       <c r="AE2" s="3" t="inlineStr"/>
-      <c r="AF2" s="3" t="inlineStr"/>
-      <c r="AG2" s="3" t="inlineStr">
+      <c r="AF2" s="3" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
+      <c r="AG2" s="3" t="inlineStr"/>
       <c r="AH2" s="3" t="inlineStr"/>
       <c r="AI2" s="3" t="inlineStr"/>
       <c r="AJ2" s="3" t="inlineStr"/>
@@ -1191,43 +1191,43 @@
       <c r="B3" s="2" t="inlineStr"/>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted</t>
+          <t>100% confidence — extracted from GSGF - NNELO TAUNYANE</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted</t>
+          <t>100% confidence — extracted from GSGF - NNELO TAUNYANE</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted</t>
+          <t>100% confidence — extracted from GSGF - NNELO TAUNYANE</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted</t>
+          <t>100% confidence — extracted from GSGF - NNELO TAUNYANE</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted</t>
+          <t>100% confidence — extracted from GSGF - NNELO TAUNYANE</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr"/>
@@ -1239,55 +1239,55 @@
       <c r="R3" s="2" t="inlineStr"/>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="U3" s="2" t="inlineStr"/>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr"/>
       <c r="AD3" s="2" t="inlineStr"/>
       <c r="AE3" s="2" t="inlineStr"/>
-      <c r="AF3" s="2" t="inlineStr"/>
-      <c r="AG3" s="2" t="inlineStr">
-        <is>
-          <t>100% confidence — extracted</t>
-        </is>
-      </c>
+      <c r="AF3" s="2" t="inlineStr">
+        <is>
+          <t>0% confidence — extracted from GSGF - NNELO TAUNYANE</t>
+        </is>
+      </c>
+      <c r="AG3" s="2" t="inlineStr"/>
       <c r="AH3" s="2" t="inlineStr"/>
       <c r="AI3" s="2" t="inlineStr"/>
       <c r="AJ3" s="2" t="inlineStr"/>
@@ -1299,180 +1299,176 @@
       <c r="AP3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>KYC - ONALENNA</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>KYC - Nnelo Taunyane</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>KYC</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>KYC (Know Your Customer)</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>ONALENYA LORATO BOGOSING</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>224922314</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>16/11/1993</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="4" t="inlineStr"/>
-      <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="4" t="inlineStr"/>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="M4" s="4" t="inlineStr">
-        <is>
-          <t>Rejected</t>
-        </is>
-      </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>Validation failed: id_expiry_date</t>
-        </is>
-      </c>
-      <c r="O4" s="4" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>381234567</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>NNELO TAUNYANE</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>11102222</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>01/02/2003</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr"/>
+      <c r="I4" s="3" t="inlineStr"/>
+      <c r="J4" s="3" t="inlineStr"/>
+      <c r="K4" s="3" t="inlineStr"/>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Captured</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr"/>
+      <c r="O4" s="3" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="P4" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-01T22:24:05</t>
-        </is>
-      </c>
-      <c r="Q4" s="4" t="inlineStr">
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-02T15:23:47</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
         <is>
           <t>marvel.ai-local-poc</t>
         </is>
       </c>
-      <c r="R4" s="4" t="inlineStr"/>
-      <c r="S4" s="4" t="inlineStr">
-        <is>
-          <t>76749303</t>
-        </is>
-      </c>
-      <c r="T4" s="4" t="inlineStr">
-        <is>
-          <t>obogosinge@gmail.com</t>
-        </is>
-      </c>
-      <c r="U4" s="4" t="inlineStr">
+      <c r="R4" s="3" t="inlineStr"/>
+      <c r="S4" s="3" t="inlineStr">
+        <is>
+          <t>71234567</t>
+        </is>
+      </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>nnelo@bifm.co.bw</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
         <is>
           <t>MOTSWANA</t>
         </is>
       </c>
-      <c r="V4" s="4" t="inlineStr">
-        <is>
-          <t>Onalenya Bogosing</t>
-        </is>
-      </c>
-      <c r="W4" s="4" t="inlineStr">
-        <is>
-          <t>ABSA</t>
-        </is>
-      </c>
-      <c r="X4" s="4" t="inlineStr">
-        <is>
-          <t>1078631</t>
-        </is>
-      </c>
-      <c r="Y4" s="4" t="inlineStr">
-        <is>
-          <t>MALL</t>
-        </is>
-      </c>
-      <c r="Z4" s="4" t="inlineStr">
-        <is>
-          <t>290167</t>
-        </is>
-      </c>
-      <c r="AA4" s="4" t="inlineStr">
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>NNELO TAUNYANE</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>STANBIC</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>9060001231234</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>FAIRGROUNDS</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>064967</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>Current</t>
         </is>
       </c>
-      <c r="AB4" s="4" t="inlineStr">
-        <is>
-          <t>Joint Signature</t>
-        </is>
-      </c>
-      <c r="AC4" s="4" t="inlineStr">
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>Individual</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
         <is>
           <t>BOTSWANA</t>
         </is>
       </c>
-      <c r="AD4" s="4" t="inlineStr">
-        <is>
-          <t>THE UNITED NATIONS</t>
-        </is>
-      </c>
-      <c r="AE4" s="4" t="inlineStr">
-        <is>
-          <t>ONALENYA BOGOSING</t>
-        </is>
-      </c>
-      <c r="AF4" s="4" t="inlineStr">
-        <is>
-          <t>11/02/2026</t>
-        </is>
-      </c>
-      <c r="AG4" s="4" t="inlineStr"/>
-      <c r="AH4" s="4" t="b">
+      <c r="AD4" s="3" t="inlineStr">
+        <is>
+          <t>BIFM UNIT TRUSTS</t>
+        </is>
+      </c>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>NNELO TAUNYANE</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr"/>
+      <c r="AG4" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="AI4" s="4" t="inlineStr">
+      <c r="AH4" s="3" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
       </c>
-      <c r="AJ4" s="4" t="b">
+      <c r="AI4" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="AK4" s="4" t="b">
+      <c r="AJ4" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="AL4" s="4" t="b">
+      <c r="AK4" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="AM4" s="4" t="inlineStr">
-        <is>
-          <t>DIPLOMAT</t>
-        </is>
-      </c>
-      <c r="AN4" s="4" t="inlineStr">
-        <is>
-          <t>PLOT 40353, BLOCKS  GABS</t>
-        </is>
-      </c>
-      <c r="AO4" s="4" t="inlineStr">
+      <c r="AL4" s="3" t="inlineStr">
+        <is>
+          <t>INTERN</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>PLOT 1234 GABORONE</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
         <is>
           <t>Salary</t>
         </is>
       </c>
-      <c r="AP4" s="4" t="inlineStr">
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>Ms</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1483,27 +1479,27 @@
       <c r="B5" s="2" t="inlineStr"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted</t>
+          <t>100% confidence — extracted from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted p.1</t>
+          <t>100% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted p.1</t>
+          <t>100% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted p.1</t>
+          <t>100% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted p.1</t>
+          <t>100% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -1519,125 +1515,125 @@
       <c r="R5" s="2" t="inlineStr"/>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted p.1</t>
+          <t>100% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted p.1</t>
+          <t>100% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted p.1</t>
+          <t>100% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted p.1</t>
+          <t>100% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted p.1</t>
+          <t>100% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted p.1</t>
+          <t>100% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted p.1</t>
+          <t>100% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted p.1</t>
+          <t>100% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted p.1</t>
+          <t>100% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted p.1</t>
+          <t>100% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted p.1</t>
+          <t>100% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted p.1</t>
+          <t>100% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
         </is>
       </c>
       <c r="AE5" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted p.1</t>
-        </is>
-      </c>
-      <c r="AF5" s="2" t="inlineStr">
-        <is>
-          <t>100% confidence — extracted p.1</t>
-        </is>
-      </c>
-      <c r="AG5" s="2" t="inlineStr"/>
+          <t>100% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
+        </is>
+      </c>
+      <c r="AF5" s="2" t="inlineStr"/>
+      <c r="AG5" s="2" t="inlineStr">
+        <is>
+          <t>100% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
+        </is>
+      </c>
       <c r="AH5" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted p.1</t>
+          <t>100% confidence — extracted from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="AI5" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted</t>
+          <t>100% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
         </is>
       </c>
       <c r="AJ5" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted p.1</t>
+          <t>100% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
         </is>
       </c>
       <c r="AK5" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted p.1</t>
+          <t>100% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
         </is>
       </c>
       <c r="AL5" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted p.1</t>
+          <t>100% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
         </is>
       </c>
       <c r="AM5" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted p.1</t>
+          <t>100% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
         </is>
       </c>
       <c r="AN5" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted p.1</t>
+          <t>100% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
         </is>
       </c>
       <c r="AO5" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted p.1</t>
+          <t>100% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
         </is>
       </c>
       <c r="AP5" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted p.1</t>
+          <t>100% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>DIS - ONALENNA BOGOSING</t>
+          <t>DIS - NNELO</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -1652,17 +1648,17 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>38344272</t>
+          <t>381234567</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>ONALENYA LORATO BOGOSING</t>
+          <t>NNELO TAUNYANE</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>224922314</t>
+          <t>11102222</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr"/>
@@ -1702,7 +1698,7 @@
       </c>
       <c r="P6" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01T22:24:05</t>
+          <t>2026-07-02T15:23:47</t>
         </is>
       </c>
       <c r="Q6" s="4" t="inlineStr">
@@ -1713,38 +1709,38 @@
       <c r="R6" s="4" t="inlineStr"/>
       <c r="S6" s="4" t="inlineStr">
         <is>
-          <t>76749303</t>
+          <t>71234567</t>
         </is>
       </c>
       <c r="T6" s="4" t="inlineStr">
         <is>
-          <t>obogosinge@gmail.com</t>
+          <t>nnelo@bifm.co.bw</t>
         </is>
       </c>
       <c r="U6" s="4" t="inlineStr"/>
       <c r="V6" s="4" t="inlineStr">
         <is>
-          <t>Onalenya Bogosing</t>
+          <t>NNELO TAUNYANE</t>
         </is>
       </c>
       <c r="W6" s="4" t="inlineStr">
         <is>
-          <t>ABSA</t>
+          <t>STANBIC</t>
         </is>
       </c>
       <c r="X6" s="4" t="inlineStr">
         <is>
-          <t>1078631</t>
+          <t>9060001231234</t>
         </is>
       </c>
       <c r="Y6" s="4" t="inlineStr">
         <is>
-          <t>MALL</t>
+          <t>FAIRGROUNDS</t>
         </is>
       </c>
       <c r="Z6" s="4" t="inlineStr">
         <is>
-          <t>290167</t>
+          <t>064967</t>
         </is>
       </c>
       <c r="AA6" s="4" t="inlineStr">
@@ -1756,12 +1752,12 @@
       <c r="AC6" s="4" t="inlineStr"/>
       <c r="AD6" s="4" t="inlineStr"/>
       <c r="AE6" s="4" t="inlineStr"/>
-      <c r="AF6" s="4" t="inlineStr"/>
-      <c r="AG6" s="4" t="inlineStr">
+      <c r="AF6" s="4" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
+      <c r="AG6" s="4" t="inlineStr"/>
       <c r="AH6" s="4" t="inlineStr"/>
       <c r="AI6" s="4" t="inlineStr"/>
       <c r="AJ6" s="4" t="inlineStr"/>
@@ -1777,39 +1773,39 @@
       <c r="B7" s="2" t="inlineStr"/>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted</t>
+          <t>100% confidence — extracted from DIS - NNELO</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr"/>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted</t>
+          <t>100% confidence — extracted from DIS - NNELO</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted</t>
+          <t>100% confidence — extracted from DIS - NNELO</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted</t>
+          <t>100% confidence — extracted from DIS - NNELO</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr"/>
@@ -1821,55 +1817,55 @@
       <c r="R7" s="2" t="inlineStr"/>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr"/>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr"/>
       <c r="AE7" s="2" t="inlineStr"/>
-      <c r="AF7" s="2" t="inlineStr"/>
-      <c r="AG7" s="2" t="inlineStr">
-        <is>
-          <t>100% confidence — extracted</t>
-        </is>
-      </c>
+      <c r="AF7" s="2" t="inlineStr">
+        <is>
+          <t>0% confidence — extracted from DIS - NNELO</t>
+        </is>
+      </c>
+      <c r="AG7" s="2" t="inlineStr"/>
       <c r="AH7" s="2" t="inlineStr"/>
       <c r="AI7" s="2" t="inlineStr"/>
       <c r="AJ7" s="2" t="inlineStr"/>
@@ -1883,7 +1879,7 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>DEBIT - ONALENNA BOGOSING</t>
+          <t>DEBIT - NNELO</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -1898,17 +1894,17 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>38344272</t>
+          <t>381234567</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>ONALENYA LORATO BOGOSING</t>
+          <t>NNELO TAUNYANE</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>224922314</t>
+          <t>11102222</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr"/>
@@ -1938,7 +1934,7 @@
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>Validation failed: instruction_type, id_expiry_date</t>
+          <t>Validation failed: instruction_type</t>
         </is>
       </c>
       <c r="O8" s="4" t="inlineStr">
@@ -1948,7 +1944,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01T22:24:05</t>
+          <t>2026-07-02T15:23:47</t>
         </is>
       </c>
       <c r="Q8" s="4" t="inlineStr">
@@ -1959,38 +1955,38 @@
       <c r="R8" s="4" t="inlineStr"/>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>76749303</t>
+          <t>71234567</t>
         </is>
       </c>
       <c r="T8" s="4" t="inlineStr">
         <is>
-          <t>obogosinge@gmail.com</t>
+          <t>nnelo@bifm.co.bw</t>
         </is>
       </c>
       <c r="U8" s="4" t="inlineStr"/>
       <c r="V8" s="4" t="inlineStr">
         <is>
-          <t>Onalenya Bogosing</t>
+          <t>NNELO TAUNYANE</t>
         </is>
       </c>
       <c r="W8" s="4" t="inlineStr">
         <is>
-          <t>ABSA</t>
+          <t>STANBIC</t>
         </is>
       </c>
       <c r="X8" s="4" t="inlineStr">
         <is>
-          <t>1078631</t>
+          <t>9060001231234</t>
         </is>
       </c>
       <c r="Y8" s="4" t="inlineStr">
         <is>
-          <t>MALL</t>
+          <t>FAIRGROUNDS</t>
         </is>
       </c>
       <c r="Z8" s="4" t="inlineStr">
         <is>
-          <t>290167</t>
+          <t>064967</t>
         </is>
       </c>
       <c r="AA8" s="4" t="inlineStr">
@@ -2002,11 +1998,7 @@
       <c r="AC8" s="4" t="inlineStr"/>
       <c r="AD8" s="4" t="inlineStr"/>
       <c r="AE8" s="4" t="inlineStr"/>
-      <c r="AF8" s="4" t="inlineStr">
-        <is>
-          <t>11/02/2026</t>
-        </is>
-      </c>
+      <c r="AF8" s="4" t="inlineStr"/>
       <c r="AG8" s="4" t="inlineStr"/>
       <c r="AH8" s="4" t="inlineStr"/>
       <c r="AI8" s="4" t="inlineStr"/>
@@ -2023,39 +2015,39 @@
       <c r="B9" s="2" t="inlineStr"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted</t>
+          <t>100% confidence — extracted from DEBIT - NNELO</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr"/>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted</t>
+          <t>100% confidence — extracted from DEBIT - NNELO</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted</t>
+          <t>100% confidence — extracted from DEBIT - NNELO</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted</t>
+          <t>100% confidence — extracted from DEBIT - NNELO</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr"/>
@@ -2067,54 +2059,50 @@
       <c r="R9" s="2" t="inlineStr"/>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr"/>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
       <c r="AE9" s="2" t="inlineStr"/>
-      <c r="AF9" s="2" t="inlineStr">
-        <is>
-          <t>85% confidence — backfilled from KYC - ONALENNA</t>
-        </is>
-      </c>
+      <c r="AF9" s="2" t="inlineStr"/>
       <c r="AG9" s="2" t="inlineStr"/>
       <c r="AH9" s="2" t="inlineStr"/>
       <c r="AI9" s="2" t="inlineStr"/>
@@ -2129,7 +2117,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>ADD - ONALENNA</t>
+          <t>ADD - NNELO</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -2144,12 +2132,12 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>38344272</t>
+          <t>381234567</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>ONALENYA LORATO BOGOSING</t>
+          <t>NNELO TAUNYANE</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr"/>
@@ -2190,7 +2178,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01T22:24:05</t>
+          <t>2026-07-02T15:23:47</t>
         </is>
       </c>
       <c r="Q10" s="4" t="inlineStr">
@@ -2201,38 +2189,38 @@
       <c r="R10" s="4" t="inlineStr"/>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>76749303</t>
+          <t>71234567</t>
         </is>
       </c>
       <c r="T10" s="4" t="inlineStr">
         <is>
-          <t>obogosinge@gmail.com</t>
+          <t>nnelo@bifm.co.bw</t>
         </is>
       </c>
       <c r="U10" s="4" t="inlineStr"/>
       <c r="V10" s="4" t="inlineStr">
         <is>
-          <t>Onalenya Bogosing</t>
+          <t>NNELO TAUNYANE</t>
         </is>
       </c>
       <c r="W10" s="4" t="inlineStr">
         <is>
-          <t>ABSA</t>
+          <t>STANBIC</t>
         </is>
       </c>
       <c r="X10" s="4" t="inlineStr">
         <is>
-          <t>1078631</t>
+          <t>9060001231234</t>
         </is>
       </c>
       <c r="Y10" s="4" t="inlineStr">
         <is>
-          <t>MALL</t>
+          <t>FAIRGROUNDS</t>
         </is>
       </c>
       <c r="Z10" s="4" t="inlineStr">
         <is>
-          <t>290167</t>
+          <t>064967</t>
         </is>
       </c>
       <c r="AA10" s="4" t="inlineStr">
@@ -2261,17 +2249,17 @@
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted</t>
+          <t>100% confidence — extracted from ADD - NNELO</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
@@ -2279,17 +2267,17 @@
       <c r="H11" s="2" t="inlineStr"/>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted</t>
+          <t>100% confidence — extracted from ADD - NNELO</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted</t>
+          <t>100% confidence — extracted from ADD - NNELO</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted</t>
+          <t>100% confidence — extracted from ADD - NNELO</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr"/>
@@ -2301,43 +2289,43 @@
       <c r="R11" s="2" t="inlineStr"/>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr"/>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - ONALENNA</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr"/>
@@ -2415,11 +2403,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="35" customWidth="1" min="5" max="5"/>
@@ -2467,12 +2455,12 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>38344272</t>
+          <t>381234567</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>KYC - ONALENNA</t>
+          <t>KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -2487,7 +2475,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>224922314</t>
+          <t>11102222</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -2504,12 +2492,12 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>38344272</t>
+          <t>381234567</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>KYC - ONALENNA</t>
+          <t>KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -2535,51 +2523,47 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>KYC - ONALENNA</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>381234567</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>KYC - Nnelo Taunyane</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>KYC</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>id_expiry_date</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>11/02/2026</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>ID expiry date is not in the future</t>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>ID expiry date not captured</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>38344272</t>
+          <t>381234567</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>KYC - ONALENNA</t>
+          <t>KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -2594,7 +2578,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>16/11/1993</t>
+          <t>01/02/2003</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -2607,12 +2591,12 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>38344272</t>
+          <t>381234567</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>KYC - ONALENNA</t>
+          <t>KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -2627,7 +2611,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>obogosinge@gmail.com</t>
+          <t>nnelo@bifm.co.bw</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -2640,12 +2624,12 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>38344272</t>
+          <t>381234567</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>KYC - ONALENNA</t>
+          <t>KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -2660,7 +2644,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>76749303</t>
+          <t>71234567</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -2673,12 +2657,12 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>38344272</t>
+          <t>381234567</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>KYC - ONALENNA</t>
+          <t>KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2693,7 +2677,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>290167</t>
+          <t>064967</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -2706,12 +2690,12 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>38344272</t>
+          <t>381234567</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>KYC - ONALENNA</t>
+          <t>KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2739,12 +2723,12 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>38344272</t>
+          <t>381234567</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>GSGF - ONALENNA BOGOSING</t>
+          <t>GSGF - NNELO TAUNYANE</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -2759,7 +2743,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>224922314</t>
+          <t>11102222</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -2776,12 +2760,12 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>38344272</t>
+          <t>381234567</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>GSGF - ONALENNA BOGOSING</t>
+          <t>GSGF - NNELO TAUNYANE</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -2809,12 +2793,12 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>38344272</t>
+          <t>381234567</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>GSGF - ONALENNA BOGOSING</t>
+          <t>GSGF - NNELO TAUNYANE</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -2829,7 +2813,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>obogosinge@gmail.com</t>
+          <t>nnelo@bifm.co.bw</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -2842,12 +2826,12 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>38344272</t>
+          <t>381234567</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>GSGF - ONALENNA BOGOSING</t>
+          <t>GSGF - NNELO TAUNYANE</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -2862,7 +2846,7 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>76749303</t>
+          <t>71234567</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -2875,12 +2859,12 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>38344272</t>
+          <t>381234567</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>GSGF - ONALENNA BOGOSING</t>
+          <t>GSGF - NNELO TAUNYANE</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -2895,7 +2879,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>290167</t>
+          <t>064967</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -2908,12 +2892,12 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>38344272</t>
+          <t>381234567</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>GSGF - ONALENNA BOGOSING</t>
+          <t>GSGF - NNELO TAUNYANE</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -2939,84 +2923,84 @@
       <c r="G15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>DIS - ONALENNA BOGOSING</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>381234567</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>GSGF - NNELO TAUNYANE</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>DIS_GSG</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>instruction_mode</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>Could not determine instruction mode - no closure tick, percentage, or withdrawal/deposit amount was found</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>381234567</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>DIS - NNELO</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>DIS</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>fund_name</t>
         </is>
       </c>
-      <c r="E16" s="4" t="n"/>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="E17" s="4" t="n"/>
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>Mandatory field missing</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>DIS - ONALENNA BOGOSING</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>id_number</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>224922314</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>Unknown ID type 'None' - cannot apply digit validation</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>38344272</t>
+          <t>381234567</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>DIS - ONALENNA BOGOSING</t>
+          <t>DIS - NNELO</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -3026,63 +3010,67 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
+          <t>id_number</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>11102222</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>Unknown ID type 'None' - cannot apply digit validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>381234567</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>DIS - NNELO</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
           <t>id_expiry_date</t>
         </is>
       </c>
-      <c r="E18" s="3" t="n"/>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>WARNING</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>ID expiry date not captured</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>DIS - ONALENNA BOGOSING</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>obogosinge@gmail.com</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>38344272</t>
+          <t>381234567</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>DIS - ONALENNA BOGOSING</t>
+          <t>DIS - NNELO</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -3092,12 +3080,12 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>contact_number</t>
+          <t>email</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>76749303</t>
+          <t>nnelo@bifm.co.bw</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -3110,12 +3098,12 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>38344272</t>
+          <t>381234567</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>DIS - ONALENNA BOGOSING</t>
+          <t>DIS - NNELO</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -3125,63 +3113,63 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
+          <t>contact_number</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>71234567</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>381234567</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>DIS - NNELO</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
           <t>branch_code</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>290167</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>064967</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>DIS - ONALENNA BOGOSING</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>fund_number</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="n"/>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>Field is blank</t>
-        </is>
-      </c>
+      <c r="G22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>38344272</t>
+          <t>381234567</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>DIS - ONALENNA BOGOSING</t>
+          <t>DIS - NNELO</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -3191,82 +3179,82 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
+          <t>fund_number</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="n"/>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>Field is blank</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>381234567</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>DIS - NNELO</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
           <t>fund_category</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>Unknown - Fund Name Not Extracted</t>
         </is>
       </c>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="F24" s="3" t="inlineStr">
         <is>
           <t>WARNING</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="G24" s="3" t="inlineStr">
         <is>
           <t>Fund category could not be determined - fund name unclear</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>DEBIT - ONALENNA BOGOSING</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>DEBIT</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>instruction_type</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="n"/>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t>Mandatory field missing</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>38344272</t>
+          <t>381234567</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>DEBIT - ONALENNA BOGOSING</t>
+          <t>DIS - NNELO</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>DEBIT</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>id_number</t>
+          <t>instruction_mode</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>224922314</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -3276,19 +3264,19 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>Unknown ID type 'None' - cannot apply digit validation</t>
+          <t>Could not determine instruction mode - no closure tick, percentage, or withdrawal/deposit amount was found</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>38344272</t>
+          <t>381234567</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>DEBIT - ONALENNA BOGOSING</t>
+          <t>DEBIT - NNELO</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -3298,100 +3286,100 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
+          <t>instruction_type</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="n"/>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>Mandatory field missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>381234567</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT - NNELO</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>id_number</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>11102222</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>Unknown ID type 'None' - cannot apply digit validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>381234567</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT - NNELO</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
           <t>id_expiry_date</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>11/02/2026</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t>ID expiry date is not in the future</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>DEBIT - ONALENNA BOGOSING</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>DEBIT</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>obogosinge@gmail.com</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>DEBIT - ONALENNA BOGOSING</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>DEBIT</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>contact_number</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>76749303</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="inlineStr"/>
+      <c r="E28" s="3" t="n"/>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>ID expiry date not captured</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>38344272</t>
+          <t>381234567</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>DEBIT - ONALENNA BOGOSING</t>
+          <t>DEBIT - NNELO</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -3401,298 +3389,298 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>nnelo@bifm.co.bw</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>381234567</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>DEBIT - NNELO</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>DEBIT</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>contact_number</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>71234567</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>381234567</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>DEBIT - NNELO</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>DEBIT</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
           <t>branch_code</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>290167</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>064967</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>DEBIT - ONALENNA BOGOSING</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="G31" s="5" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>381234567</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT - NNELO</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>DEBIT</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>fund_number</t>
         </is>
       </c>
-      <c r="E30" s="3" t="n"/>
-      <c r="F30" s="3" t="inlineStr">
+      <c r="E32" s="3" t="n"/>
+      <c r="F32" s="3" t="inlineStr">
         <is>
           <t>WARNING</t>
         </is>
       </c>
-      <c r="G30" s="3" t="inlineStr">
+      <c r="G32" s="3" t="inlineStr">
         <is>
           <t>Field is blank</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>DEBIT - ONALENNA BOGOSING</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>381234567</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT - NNELO</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>DEBIT</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>fund_category</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>Unknown - Fund Name Not Extracted</t>
         </is>
       </c>
-      <c r="F31" s="3" t="inlineStr">
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t>WARNING</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
+      <c r="G33" s="3" t="inlineStr">
         <is>
           <t>Fund category could not be determined - fund name unclear</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>ADD - ONALENNA</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>381234567</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>ADD - NNELO</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>ADD</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>fund_name</t>
         </is>
       </c>
-      <c r="E32" s="4" t="n"/>
-      <c r="F32" s="4" t="inlineStr">
+      <c r="E34" s="4" t="n"/>
+      <c r="F34" s="4" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="G32" s="4" t="inlineStr">
+      <c r="G34" s="4" t="inlineStr">
         <is>
           <t>Mandatory field missing</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>ADD - ONALENNA</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>381234567</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>ADD - NNELO</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>ADD</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>fund_number</t>
         </is>
       </c>
-      <c r="E33" s="4" t="n"/>
-      <c r="F33" s="4" t="inlineStr">
+      <c r="E35" s="4" t="n"/>
+      <c r="F35" s="4" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="G33" s="4" t="inlineStr">
+      <c r="G35" s="4" t="inlineStr">
         <is>
           <t>Mandatory field missing</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>ADD - ONALENNA</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>381234567</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>ADD - NNELO</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>ADD</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t>id_number</t>
         </is>
       </c>
-      <c r="E34" s="3" t="n"/>
-      <c r="F34" s="3" t="inlineStr">
+      <c r="E36" s="3" t="n"/>
+      <c r="F36" s="3" t="inlineStr">
         <is>
           <t>WARNING</t>
         </is>
       </c>
-      <c r="G34" s="3" t="inlineStr">
+      <c r="G36" s="3" t="inlineStr">
         <is>
           <t>ID number not captured</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>ADD - ONALENNA</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>381234567</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>ADD - NNELO</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>ADD</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>id_expiry_date</t>
         </is>
       </c>
-      <c r="E35" s="3" t="n"/>
-      <c r="F35" s="3" t="inlineStr">
+      <c r="E37" s="3" t="n"/>
+      <c r="F37" s="3" t="inlineStr">
         <is>
           <t>WARNING</t>
         </is>
       </c>
-      <c r="G35" s="3" t="inlineStr">
+      <c r="G37" s="3" t="inlineStr">
         <is>
           <t>ID expiry date not captured</t>
         </is>
       </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>ADD - ONALENNA</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>obogosinge@gmail.com</t>
-        </is>
-      </c>
-      <c r="F36" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G36" s="5" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>ADD - ONALENNA</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>contact_number</t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t>76749303</t>
-        </is>
-      </c>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G37" s="5" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>38344272</t>
+          <t>381234567</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>ADD - ONALENNA</t>
+          <t>ADD - NNELO</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -3702,86 +3690,152 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>nnelo@bifm.co.bw</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>381234567</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>ADD - NNELO</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>contact_number</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>71234567</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>381234567</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>ADD - NNELO</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
           <t>branch_code</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr">
-        <is>
-          <t>290167</t>
-        </is>
-      </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>064967</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G38" s="5" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>ADD - ONALENNA</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="G40" s="5" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>381234567</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>ADD - NNELO</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>ADD</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="D41" s="3" t="inlineStr">
         <is>
           <t>fund_number</t>
         </is>
       </c>
-      <c r="E39" s="3" t="n"/>
-      <c r="F39" s="3" t="inlineStr">
+      <c r="E41" s="3" t="n"/>
+      <c r="F41" s="3" t="inlineStr">
         <is>
           <t>WARNING</t>
         </is>
       </c>
-      <c r="G39" s="3" t="inlineStr">
+      <c r="G41" s="3" t="inlineStr">
         <is>
           <t>Field is blank</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>ADD - ONALENNA</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>381234567</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>ADD - NNELO</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>ADD</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr">
+      <c r="D42" s="3" t="inlineStr">
         <is>
           <t>fund_category</t>
         </is>
       </c>
-      <c r="E40" s="3" t="inlineStr">
+      <c r="E42" s="3" t="inlineStr">
         <is>
           <t>Unknown - Fund Name Not Extracted</t>
         </is>
       </c>
-      <c r="F40" s="3" t="inlineStr">
+      <c r="F42" s="3" t="inlineStr">
         <is>
           <t>WARNING</t>
         </is>
       </c>
-      <c r="G40" s="3" t="inlineStr">
+      <c r="G42" s="3" t="inlineStr">
         <is>
           <t>Fund category could not be determined - fund name unclear</t>
         </is>
@@ -3802,13 +3856,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="27" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="43" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
     <col width="45" customWidth="1" min="11" max="11"/>
@@ -3892,17 +3946,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-01T22:25:12</t>
+          <t>2026-07-02T15:25:01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>KYC - ONALENNA.pdf</t>
+          <t>KYC - Nnelo Taunyane.pdf</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>KYC_38344272_BOGOSING_20260701_VALIDATIONFAILEDID_EXPIRY_DATE_1.pdf</t>
+          <t>KYC_381234567_TAUNYANE_20260702.pdf</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -3915,19 +3969,15 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>WARNING</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rejected</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Validation failed: id_expiry_date</t>
-        </is>
-      </c>
+          <t>Captured</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Email</t>
@@ -3935,12 +3985,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-01T22:24:05</t>
+          <t>2026-07-02T15:23:47</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\01\NonMoneyMarket\Captured\Rejected\KYC_38344272_BOGOSING_20260701_VALIDATIONFAILEDID_EXPIRY_DATE_1.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\02\NonMoneyMarket\Captured\KYC_381234567_TAUNYANE_20260702.pdf</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -3958,17 +4008,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-01T22:25:12</t>
+          <t>2026-07-02T15:25:01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GSGF - ONALENNA BOGOSING.pdf</t>
+          <t>GSGF - NNELO TAUNYANE.pdf</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DIS_GSG_38344272_BOGOSING_20260701_1.pdf</t>
+          <t>DIS_GSG_381234567_TAUNYANE_20260702.pdf</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -3997,12 +4047,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-07-01T22:24:05</t>
+          <t>2026-07-02T15:23:47</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\01\NonMoneyMarket\Captured\DIS_GSG_38344272_BOGOSING_20260701_1.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\02\NonMoneyMarket\Captured\DIS_GSG_381234567_TAUNYANE_20260702.pdf</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -4020,17 +4070,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-01T22:25:12</t>
+          <t>2026-07-02T15:25:01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DIS - ONALENNA BOGOSING.pdf</t>
+          <t>DIS - NNELO.pdf</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DIS_38344272_BOGOSING_20260701_VALIDATIONFAILEDFUND_NAME.pdf</t>
+          <t>DIS_381234567_TAUNYANE_20260702_VALIDATIONFAILEDFUND_NAME.pdf</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -4063,12 +4113,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-07-01T22:24:05</t>
+          <t>2026-07-02T15:23:47</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\01\NonMoneyMarket\Captured\Rejected\DIS_38344272_BOGOSING_20260701_VALIDATIONFAILEDFUND_NAME.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\02\NonMoneyMarket\Captured\Rejected\DIS_381234567_TAUNYANE_20260702_VALIDATIONFAILEDFUND_NAME.pdf</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -4086,17 +4136,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-01T22:25:12</t>
+          <t>2026-07-02T15:25:01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DEBIT - ONALENNA BOGOSING.pdf</t>
+          <t>DEBIT - NNELO.pdf</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DEBIT_38344272_BOGOSING_20260701_VALIDATIONFAILEDINSTRUCTION_TYPEID_EXPIRY_DATE_1.pdf</t>
+          <t>DEBIT_381234567_TAUNYANE_20260702_VALIDATIONFAILEDINSTRUCTION_TYPE.pdf</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -4119,7 +4169,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Validation failed: instruction_type, id_expiry_date</t>
+          <t>Validation failed: instruction_type</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -4129,12 +4179,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-07-01T22:24:05</t>
+          <t>2026-07-02T15:23:47</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\01\NonMoneyMarket\Captured\Rejected\DEBIT_38344272_BOGOSING_20260701_VALIDATIONFAILEDINSTRUCTION_TYPEID_EXPIRY_DATE_1.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\02\NonMoneyMarket\Captured\Rejected\DEBIT_381234567_TAUNYANE_20260702_VALIDATIONFAILEDINSTRUCTION_TYPE.pdf</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -4152,17 +4202,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-01T22:25:12</t>
+          <t>2026-07-02T15:25:01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ADD - ONALENNA.pdf</t>
+          <t>ADD - NNELO.pdf</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ADD_38344272_BOGOSING_20260701_VALIDATIONFAILEDFUND_NAMEFUND_NUMBER.pdf</t>
+          <t>ADD_381234567_TAUNYANE_20260702_VALIDATIONFAILEDFUND_NAMEFUND_NUMBER.pdf</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -4195,12 +4245,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-07-01T22:24:05</t>
+          <t>2026-07-02T15:23:47</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\01\NonMoneyMarket\Captured\Rejected\ADD_38344272_BOGOSING_20260701_VALIDATIONFAILEDFUND_NAMEFUND_NUMBER.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\02\NonMoneyMarket\Captured\Rejected\ADD_381234567_TAUNYANE_20260702_VALIDATIONFAILEDFUND_NAMEFUND_NUMBER.pdf</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">

--- a/output/BIFM_UT_Processing_Report.xlsx
+++ b/output/BIFM_UT_Processing_Report.xlsx
@@ -694,87 +694,87 @@
       <c r="C3" s="2" t="inlineStr"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
+          <t>98% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
+          <t>98% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
+          <t>98% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
+          <t>98% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
+          <t>98% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
+          <t>98% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
+          <t>98% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
+          <t>98% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
+          <t>98% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
+          <t>98% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
+          <t>98% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
+          <t>98% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
+          <t>98% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
+          <t>98% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
+          <t>98% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
+          <t>98% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
+          <t>98% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>2026-07-02T15:23:47</t>
+          <t>2026-07-02T16:37:07</t>
         </is>
       </c>
       <c r="Q2" s="3" t="inlineStr">
@@ -1191,43 +1191,43 @@
       <c r="B3" s="2" t="inlineStr"/>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted from GSGF - NNELO TAUNYANE</t>
+          <t>98% confidence — extracted from GSGF - NNELO TAUNYANE</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted from GSGF - NNELO TAUNYANE</t>
+          <t>98% confidence — extracted from GSGF - NNELO TAUNYANE</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted from GSGF - NNELO TAUNYANE</t>
+          <t>98% confidence — extracted from GSGF - NNELO TAUNYANE</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted from GSGF - NNELO TAUNYANE</t>
+          <t>98% confidence — extracted from GSGF - NNELO TAUNYANE</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted from GSGF - NNELO TAUNYANE</t>
+          <t>98% confidence — extracted from GSGF - NNELO TAUNYANE</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr"/>
@@ -1239,43 +1239,43 @@
       <c r="R3" s="2" t="inlineStr"/>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
         </is>
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
         </is>
       </c>
       <c r="U3" s="2" t="inlineStr"/>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
         </is>
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr"/>
@@ -1284,7 +1284,7 @@
       <c r="AE3" s="2" t="inlineStr"/>
       <c r="AF3" s="2" t="inlineStr">
         <is>
-          <t>0% confidence — extracted from GSGF - NNELO TAUNYANE</t>
+          <t>0% confidence — extracted from GSGF - NNELO TAUNYANE — ⚠ recommend recheck</t>
         </is>
       </c>
       <c r="AG3" s="2" t="inlineStr"/>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>2026-07-02T15:23:47</t>
+          <t>2026-07-02T16:37:07</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -1479,27 +1479,27 @@
       <c r="B5" s="2" t="inlineStr"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted from KYC - Nnelo Taunyane</t>
+          <t>98% confidence — extracted from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
+          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
+          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
+          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
+          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -1515,118 +1515,118 @@
       <c r="R5" s="2" t="inlineStr"/>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
+          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
+          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
+          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
+          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
+          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
+          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
+          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
+          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
+          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
+          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
+          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
+          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
         </is>
       </c>
       <c r="AE5" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
+          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
         </is>
       </c>
       <c r="AF5" s="2" t="inlineStr"/>
       <c r="AG5" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
+          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
         </is>
       </c>
       <c r="AH5" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted from KYC - Nnelo Taunyane</t>
+          <t>98% confidence — extracted from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="AI5" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
+          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
         </is>
       </c>
       <c r="AJ5" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
+          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
         </is>
       </c>
       <c r="AK5" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
+          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
         </is>
       </c>
       <c r="AL5" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
+          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
         </is>
       </c>
       <c r="AM5" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
+          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
         </is>
       </c>
       <c r="AN5" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
+          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
         </is>
       </c>
       <c r="AO5" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
+          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
         </is>
       </c>
       <c r="AP5" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
+          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
         </is>
       </c>
     </row>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="P6" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02T15:23:47</t>
+          <t>2026-07-02T16:37:07</t>
         </is>
       </c>
       <c r="Q6" s="4" t="inlineStr">
@@ -1773,39 +1773,39 @@
       <c r="B7" s="2" t="inlineStr"/>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted from DIS - NNELO</t>
+          <t>98% confidence — extracted from DIS - NNELO</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr"/>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted from DIS - NNELO</t>
+          <t>98% confidence — extracted from DIS - NNELO</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted from DIS - NNELO</t>
+          <t>98% confidence — extracted from DIS - NNELO</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted from DIS - NNELO</t>
+          <t>98% confidence — extracted from DIS - NNELO</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr"/>
@@ -1817,43 +1817,43 @@
       <c r="R7" s="2" t="inlineStr"/>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr"/>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
@@ -1862,7 +1862,7 @@
       <c r="AE7" s="2" t="inlineStr"/>
       <c r="AF7" s="2" t="inlineStr">
         <is>
-          <t>0% confidence — extracted from DIS - NNELO</t>
+          <t>0% confidence — extracted from DIS - NNELO — ⚠ recommend recheck</t>
         </is>
       </c>
       <c r="AG7" s="2" t="inlineStr"/>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02T15:23:47</t>
+          <t>2026-07-02T16:37:07</t>
         </is>
       </c>
       <c r="Q8" s="4" t="inlineStr">
@@ -2015,39 +2015,39 @@
       <c r="B9" s="2" t="inlineStr"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted from DEBIT - NNELO</t>
+          <t>98% confidence — extracted from DEBIT - NNELO</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr"/>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted from DEBIT - NNELO</t>
+          <t>98% confidence — extracted from DEBIT - NNELO</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted from DEBIT - NNELO</t>
+          <t>98% confidence — extracted from DEBIT - NNELO</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted from DEBIT - NNELO</t>
+          <t>98% confidence — extracted from DEBIT - NNELO</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr"/>
@@ -2059,43 +2059,43 @@
       <c r="R9" s="2" t="inlineStr"/>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr"/>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02T15:23:47</t>
+          <t>2026-07-02T16:37:07</t>
         </is>
       </c>
       <c r="Q10" s="4" t="inlineStr">
@@ -2249,17 +2249,17 @@
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted from ADD - NNELO</t>
+          <t>98% confidence — extracted from ADD - NNELO</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
@@ -2267,17 +2267,17 @@
       <c r="H11" s="2" t="inlineStr"/>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted from ADD - NNELO</t>
+          <t>98% confidence — extracted from ADD - NNELO</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted from ADD - NNELO</t>
+          <t>98% confidence — extracted from ADD - NNELO</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>100% confidence — extracted from ADD - NNELO</t>
+          <t>98% confidence — extracted from ADD - NNELO</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr"/>
@@ -2289,43 +2289,43 @@
       <c r="R11" s="2" t="inlineStr"/>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr"/>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr"/>
@@ -2403,7 +2403,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2453,107 +2453,103 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>381234567</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>381234567</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>KYC - Nnelo Taunyane</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>KYC</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>id_number</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>11102222</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>gender</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="n"/>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Gender derivation not applicable for this ID type</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>381234567</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>KYC - Nnelo Taunyane</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>KYC</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>id_expiry_date</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>WARNING</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>Unknown ID type 'None' - cannot apply digit validation</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>381234567</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>ID expiry date not captured</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>381234567</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>KYC - Nnelo Taunyane</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>KYC</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>gender</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="n"/>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>date_of_birth</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>01/02/2003</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>Gender derivation not applicable for this ID type</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>381234567</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>KYC - Nnelo Taunyane</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>KYC</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>id_expiry_date</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="n"/>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>ID expiry date not captured</t>
-        </is>
-      </c>
+      <c r="G4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -2573,12 +2569,12 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>date_of_birth</t>
+          <t>email</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>01/02/2003</t>
+          <t>nnelo@bifm.co.bw</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -2606,12 +2602,12 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>contact_number</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>nnelo@bifm.co.bw</t>
+          <t>71234567</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -2639,12 +2635,12 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>contact_number</t>
+          <t>branch_code</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>71234567</t>
+          <t>064967</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -2672,12 +2668,12 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>branch_code</t>
+          <t>kyc_completeness_flag</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>064967</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -2688,107 +2684,103 @@
       <c r="G8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>381234567</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>KYC - Nnelo Taunyane</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>KYC</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>kyc_completeness_flag</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Complete</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>381234567</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>GSGF - NNELO TAUNYANE</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>DIS_GSG</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>id_expiry_date</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>ID expiry date not captured</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>381234567</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>GSGF - NNELO TAUNYANE</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>DIS_GSG</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>nnelo@bifm.co.bw</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>381234567</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>381234567</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>GSGF - NNELO TAUNYANE</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>DIS_GSG</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>id_number</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>11102222</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>Unknown ID type 'None' - cannot apply digit validation</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>381234567</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>GSGF - NNELO TAUNYANE</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>DIS_GSG</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>id_expiry_date</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="n"/>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>ID expiry date not captured</t>
-        </is>
-      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>contact_number</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>71234567</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -2808,12 +2800,12 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>branch_code</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>nnelo@bifm.co.bw</t>
+          <t>064967</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -2841,12 +2833,12 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>contact_number</t>
+          <t>fund_category</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>71234567</t>
+          <t>Non-Money Market (GSGF)</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -2857,70 +2849,74 @@
       <c r="G13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>381234567</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>381234567</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>GSGF - NNELO TAUNYANE</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>DIS_GSG</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>branch_code</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>064967</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr"/>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>instruction_mode</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>Could not determine instruction mode - no closure tick, percentage, or withdrawal/deposit amount was found</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>381234567</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>GSGF - NNELO TAUNYANE</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>DIS_GSG</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>fund_category</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>Non-Money Market (GSGF)</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr"/>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>381234567</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>DIS - NNELO</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>fund_name</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="n"/>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>Mandatory field missing</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -2930,267 +2926,267 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>GSGF - NNELO TAUNYANE</t>
+          <t>DIS - NNELO</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>DIS_GSG</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
+          <t>id_expiry_date</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n"/>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>ID expiry date not captured</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>381234567</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>DIS - NNELO</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>nnelo@bifm.co.bw</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>381234567</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>DIS - NNELO</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>contact_number</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>71234567</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>381234567</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>DIS - NNELO</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>branch_code</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>064967</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>381234567</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>DIS - NNELO</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>fund_number</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n"/>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>Field is blank</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>381234567</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>DIS - NNELO</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>fund_category</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Unknown - Fund Name Not Extracted</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>Fund category could not be determined - fund name unclear</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>381234567</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>DIS - NNELO</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
           <t>instruction_mode</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>WARNING</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t>Could not determine instruction mode - no closure tick, percentage, or withdrawal/deposit amount was found</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>381234567</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>DIS - NNELO</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>fund_name</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="n"/>
-      <c r="F17" s="4" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>381234567</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>DEBIT - NNELO</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>DEBIT</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>instruction_type</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="n"/>
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>Mandatory field missing</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>381234567</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>DIS - NNELO</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>id_number</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>11102222</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>Unknown ID type 'None' - cannot apply digit validation</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>381234567</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>DIS - NNELO</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>id_expiry_date</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="n"/>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>ID expiry date not captured</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>381234567</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>DIS - NNELO</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>nnelo@bifm.co.bw</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>381234567</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>DIS - NNELO</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>contact_number</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>71234567</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>381234567</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>DIS - NNELO</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>branch_code</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>064967</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>381234567</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>DIS - NNELO</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>fund_number</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="n"/>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>Field is blank</t>
         </is>
       </c>
     </row>
@@ -3202,24 +3198,20 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>DIS - NNELO</t>
+          <t>DEBIT - NNELO</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>DEBIT</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>fund_category</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>Unknown - Fund Name Not Extracted</t>
-        </is>
-      </c>
+          <t>id_expiry_date</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="n"/>
       <c r="F24" s="3" t="inlineStr">
         <is>
           <t>WARNING</t>
@@ -3227,116 +3219,108 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Fund category could not be determined - fund name unclear</t>
+          <t>ID expiry date not captured</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>381234567</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>DIS - NNELO</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>instruction_mode</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>Could not determine instruction mode - no closure tick, percentage, or withdrawal/deposit amount was found</t>
-        </is>
-      </c>
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>381234567</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>DEBIT - NNELO</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>DEBIT</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>nnelo@bifm.co.bw</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>381234567</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>381234567</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>DEBIT - NNELO</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>DEBIT</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>instruction_type</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="n"/>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t>Mandatory field missing</t>
-        </is>
-      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>contact_number</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>71234567</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>381234567</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>381234567</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>DEBIT - NNELO</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>DEBIT</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>id_number</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>11102222</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>Unknown ID type 'None' - cannot apply digit validation</t>
-        </is>
-      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>branch_code</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>064967</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -3356,7 +3340,7 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>id_expiry_date</t>
+          <t>fund_number</t>
         </is>
       </c>
       <c r="E28" s="3" t="n"/>
@@ -3367,108 +3351,112 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>ID expiry date not captured</t>
+          <t>Field is blank</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>381234567</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>381234567</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>DEBIT - NNELO</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>DEBIT</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>nnelo@bifm.co.bw</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr"/>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>fund_category</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Unknown - Fund Name Not Extracted</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>Fund category could not be determined - fund name unclear</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>381234567</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>DEBIT - NNELO</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>DEBIT</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>contact_number</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>71234567</t>
-        </is>
-      </c>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr"/>
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>381234567</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>ADD - NNELO</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>fund_name</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="n"/>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>Mandatory field missing</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>381234567</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>DEBIT - NNELO</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>DEBIT</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>branch_code</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>064967</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr"/>
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>381234567</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>ADD - NNELO</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>fund_number</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="n"/>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>Mandatory field missing</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -3478,17 +3466,17 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>DEBIT - NNELO</t>
+          <t>ADD - NNELO</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>DEBIT</t>
+          <t>ADD</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>fund_number</t>
+          <t>id_expiry_date</t>
         </is>
       </c>
       <c r="E32" s="3" t="n"/>
@@ -3499,112 +3487,108 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>Field is blank</t>
+          <t>ID expiry date not captured</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>381234567</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>DEBIT - NNELO</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>DEBIT</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>fund_category</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>Unknown - Fund Name Not Extracted</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>Fund category could not be determined - fund name unclear</t>
-        </is>
-      </c>
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>381234567</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>ADD - NNELO</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>nnelo@bifm.co.bw</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>381234567</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>381234567</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>ADD - NNELO</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>ADD</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>fund_name</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="n"/>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G34" s="4" t="inlineStr">
-        <is>
-          <t>Mandatory field missing</t>
-        </is>
-      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>contact_number</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>71234567</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>381234567</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>381234567</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>ADD - NNELO</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>ADD</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>fund_number</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="n"/>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G35" s="4" t="inlineStr">
-        <is>
-          <t>Mandatory field missing</t>
-        </is>
-      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>branch_code</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>064967</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
@@ -3624,7 +3608,7 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>id_number</t>
+          <t>fund_number</t>
         </is>
       </c>
       <c r="E36" s="3" t="n"/>
@@ -3635,7 +3619,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>ID number not captured</t>
+          <t>Field is blank</t>
         </is>
       </c>
     </row>
@@ -3657,185 +3641,20 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>id_expiry_date</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="n"/>
+          <t>fund_category</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Unknown - Fund Name Not Extracted</t>
+        </is>
+      </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
           <t>WARNING</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t>ID expiry date not captured</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>381234567</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>ADD - NNELO</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="E38" s="5" t="inlineStr">
-        <is>
-          <t>nnelo@bifm.co.bw</t>
-        </is>
-      </c>
-      <c r="F38" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G38" s="5" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>381234567</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>ADD - NNELO</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="inlineStr">
-        <is>
-          <t>contact_number</t>
-        </is>
-      </c>
-      <c r="E39" s="5" t="inlineStr">
-        <is>
-          <t>71234567</t>
-        </is>
-      </c>
-      <c r="F39" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G39" s="5" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>381234567</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>ADD - NNELO</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="inlineStr">
-        <is>
-          <t>branch_code</t>
-        </is>
-      </c>
-      <c r="E40" s="5" t="inlineStr">
-        <is>
-          <t>064967</t>
-        </is>
-      </c>
-      <c r="F40" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G40" s="5" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>381234567</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>ADD - NNELO</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>fund_number</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="n"/>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t>Field is blank</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>381234567</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>ADD - NNELO</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>fund_category</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>Unknown - Fund Name Not Extracted</t>
-        </is>
-      </c>
-      <c r="F42" s="3" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G42" s="3" t="inlineStr">
         <is>
           <t>Fund category could not be determined - fund name unclear</t>
         </is>
@@ -3946,7 +3765,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-02T15:25:01</t>
+          <t>2026-07-02T16:38:17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3956,7 +3775,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>KYC_381234567_TAUNYANE_20260702.pdf</t>
+          <t>KYC_381234567_TAUNYANE_20260702_1.pdf</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -3965,7 +3784,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3985,12 +3804,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-02T15:23:47</t>
+          <t>2026-07-02T16:37:07</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\02\NonMoneyMarket\Captured\KYC_381234567_TAUNYANE_20260702.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\02\NonMoneyMarket\Captured\KYC_381234567_TAUNYANE_20260702_1.pdf</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -4008,7 +3827,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-02T15:25:01</t>
+          <t>2026-07-02T16:38:17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -4018,7 +3837,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DIS_GSG_381234567_TAUNYANE_20260702.pdf</t>
+          <t>DIS_GSG_381234567_TAUNYANE_20260702_1.pdf</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -4027,7 +3846,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -4047,12 +3866,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-07-02T15:23:47</t>
+          <t>2026-07-02T16:37:07</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\02\NonMoneyMarket\Captured\DIS_GSG_381234567_TAUNYANE_20260702.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\02\NonMoneyMarket\Captured\DIS_GSG_381234567_TAUNYANE_20260702_1.pdf</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -4070,7 +3889,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-02T15:25:01</t>
+          <t>2026-07-02T16:38:17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -4080,7 +3899,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DIS_381234567_TAUNYANE_20260702_VALIDATIONFAILEDFUND_NAME.pdf</t>
+          <t>DIS_381234567_TAUNYANE_20260702_VALIDATIONFAILEDFUND_NAME_1.pdf</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -4089,7 +3908,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -4113,12 +3932,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-07-02T15:23:47</t>
+          <t>2026-07-02T16:37:07</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\02\NonMoneyMarket\Captured\Rejected\DIS_381234567_TAUNYANE_20260702_VALIDATIONFAILEDFUND_NAME.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\02\NonMoneyMarket\Captured\Rejected\DIS_381234567_TAUNYANE_20260702_VALIDATIONFAILEDFUND_NAME_1.pdf</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -4136,7 +3955,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-02T15:25:01</t>
+          <t>2026-07-02T16:38:17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -4146,7 +3965,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DEBIT_381234567_TAUNYANE_20260702_VALIDATIONFAILEDINSTRUCTION_TYPE.pdf</t>
+          <t>DEBIT_381234567_TAUNYANE_20260702_VALIDATIONFAILEDINSTRUCTION_TYPE_1.pdf</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -4155,7 +3974,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -4179,12 +3998,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-07-02T15:23:47</t>
+          <t>2026-07-02T16:37:07</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\02\NonMoneyMarket\Captured\Rejected\DEBIT_381234567_TAUNYANE_20260702_VALIDATIONFAILEDINSTRUCTION_TYPE.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\02\NonMoneyMarket\Captured\Rejected\DEBIT_381234567_TAUNYANE_20260702_VALIDATIONFAILEDINSTRUCTION_TYPE_1.pdf</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -4202,7 +4021,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-02T15:25:01</t>
+          <t>2026-07-02T16:38:17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -4212,7 +4031,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ADD_381234567_TAUNYANE_20260702_VALIDATIONFAILEDFUND_NAMEFUND_NUMBER.pdf</t>
+          <t>ADD_381234567_TAUNYANE_20260702_VALIDATIONFAILEDFUND_NAMEFUND_NUMBER_1.pdf</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -4221,7 +4040,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -4245,12 +4064,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-07-02T15:23:47</t>
+          <t>2026-07-02T16:37:07</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\02\NonMoneyMarket\Captured\Rejected\ADD_381234567_TAUNYANE_20260702_VALIDATIONFAILEDFUND_NAMEFUND_NUMBER.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\02\NonMoneyMarket\Captured\Rejected\ADD_381234567_TAUNYANE_20260702_VALIDATIONFAILEDFUND_NAMEFUND_NUMBER_1.pdf</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">

--- a/output/BIFM_UT_Processing_Report.xlsx
+++ b/output/BIFM_UT_Processing_Report.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>NNELO TAUNYANE</t>
+          <t>NNelo Taunyane</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>NNELO TAUNYANE</t>
+          <t>NNelo Taunyane</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>2026-07-02T16:37:07</t>
+          <t>2026-07-02T17:01:41</t>
         </is>
       </c>
       <c r="Q2" s="3" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>NNELO TAUNYANE</t>
+          <t>NNelo Taunyane</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>2026-07-02T16:37:07</t>
+          <t>2026-07-02T17:01:41</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>NNELO TAUNYANE</t>
+          <t>NNelo Taunyane</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="P6" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02T16:37:07</t>
+          <t>2026-07-02T17:01:41</t>
         </is>
       </c>
       <c r="Q6" s="4" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>NNELO TAUNYANE</t>
+          <t>NNelo Taunyane</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02T16:37:07</t>
+          <t>2026-07-02T17:01:41</t>
         </is>
       </c>
       <c r="Q8" s="4" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>NNELO TAUNYANE</t>
+          <t>NNelo Taunyane</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr"/>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02T16:37:07</t>
+          <t>2026-07-02T17:01:41</t>
         </is>
       </c>
       <c r="Q10" s="4" t="inlineStr">
@@ -2403,7 +2403,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2684,37 +2684,37 @@
       <c r="G8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>381234567</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>GSGF - NNELO TAUNYANE</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>DIS_GSG</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>id_expiry_date</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n"/>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>ID expiry date not captured</t>
-        </is>
-      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>nnelo@bifm.co.bw</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -2734,12 +2734,12 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>contact_number</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>nnelo@bifm.co.bw</t>
+          <t>71234567</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -2767,12 +2767,12 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>contact_number</t>
+          <t>branch_code</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>71234567</t>
+          <t>064967</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -2800,12 +2800,12 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>branch_code</t>
+          <t>fund_category</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>064967</t>
+          <t>Non-Money Market (GSGF)</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -2816,140 +2816,140 @@
       <c r="G12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>381234567</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>GSGF - NNELO TAUNYANE</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>DIS_GSG</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>fund_category</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>Non-Money Market (GSGF)</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>instruction_mode</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Could not determine instruction mode - no closure tick, percentage, or withdrawal/deposit amount was found</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>381234567</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>DIS - NNELO</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>fund_name</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>Mandatory field missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>381234567</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>DIS - NNELO</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>nnelo@bifm.co.bw</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>381234567</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>GSGF - NNELO TAUNYANE</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>DIS_GSG</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>instruction_mode</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>Could not determine instruction mode - no closure tick, percentage, or withdrawal/deposit amount was found</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>381234567</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>DIS - NNELO</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>DIS</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>fund_name</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="n"/>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>Mandatory field missing</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>381234567</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>DIS - NNELO</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>id_expiry_date</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="n"/>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>ID expiry date not captured</t>
-        </is>
-      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>contact_number</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>71234567</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -2969,12 +2969,12 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>branch_code</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>nnelo@bifm.co.bw</t>
+          <t>064967</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -2985,70 +2985,74 @@
       <c r="G17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>381234567</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>DIS - NNELO</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>DIS</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>contact_number</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>71234567</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr"/>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>fund_number</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>Field is blank</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>381234567</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>DIS - NNELO</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>DIS</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>branch_code</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>064967</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr"/>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>fund_category</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Unknown - Fund Name Not Extracted</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>Fund category could not be determined - fund name unclear</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -3068,395 +3072,391 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
+          <t>instruction_mode</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>Could not determine instruction mode - no closure tick, percentage, or withdrawal/deposit amount was found</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>381234567</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>DEBIT - NNELO</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>DEBIT</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>instruction_type</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="n"/>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>Mandatory field missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>381234567</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>DEBIT - NNELO</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>DEBIT</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>nnelo@bifm.co.bw</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>381234567</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>DEBIT - NNELO</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>DEBIT</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>contact_number</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>71234567</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>381234567</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>DEBIT - NNELO</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>DEBIT</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>branch_code</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>064967</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>381234567</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT - NNELO</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
           <t>fund_number</t>
         </is>
       </c>
-      <c r="E20" s="3" t="n"/>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="E25" s="3" t="n"/>
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>WARNING</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="G25" s="3" t="inlineStr">
         <is>
           <t>Field is blank</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>381234567</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>DIS - NNELO</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT - NNELO</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>fund_category</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>Unknown - Fund Name Not Extracted</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="F26" s="3" t="inlineStr">
         <is>
           <t>WARNING</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="G26" s="3" t="inlineStr">
         <is>
           <t>Fund category could not be determined - fund name unclear</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>381234567</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>DIS - NNELO</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>instruction_mode</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>Could not determine instruction mode - no closure tick, percentage, or withdrawal/deposit amount was found</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>ADD - NNELO</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>fund_name</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="n"/>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>Mandatory field missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>381234567</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>DEBIT - NNELO</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>DEBIT</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>instruction_type</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="n"/>
-      <c r="F23" s="4" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>ADD - NNELO</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>fund_number</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="G28" s="4" t="inlineStr">
         <is>
           <t>Mandatory field missing</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>381234567</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>DEBIT - NNELO</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>DEBIT</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>id_expiry_date</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="n"/>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>ID expiry date not captured</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>ADD - NNELO</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>nnelo@bifm.co.bw</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>381234567</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>DEBIT - NNELO</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>DEBIT</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>nnelo@bifm.co.bw</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>ADD - NNELO</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>contact_number</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>71234567</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="G30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>381234567</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>DEBIT - NNELO</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>DEBIT</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>contact_number</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>71234567</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>ADD - NNELO</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>branch_code</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>064967</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>381234567</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>DEBIT - NNELO</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>DEBIT</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>branch_code</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>064967</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>381234567</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>DEBIT - NNELO</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>DEBIT</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>fund_number</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="n"/>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>Field is blank</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>381234567</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>DEBIT - NNELO</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>DEBIT</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>fund_category</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>Unknown - Fund Name Not Extracted</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>Fund category could not be determined - fund name unclear</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>381234567</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>ADD - NNELO</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>fund_name</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="n"/>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G30" s="4" t="inlineStr">
-        <is>
-          <t>Mandatory field missing</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>381234567</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>ADD - NNELO</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>fund_number</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="n"/>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t>Mandatory field missing</t>
-        </is>
-      </c>
+      <c r="G31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>id_expiry_date</t>
+          <t>fund_number</t>
         </is>
       </c>
       <c r="E32" s="3" t="n"/>
@@ -3487,174 +3487,42 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>ID expiry date not captured</t>
+          <t>Field is blank</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>381234567</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>ADD - NNELO</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>ADD</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>nnelo@bifm.co.bw</t>
-        </is>
-      </c>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>381234567</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>ADD - NNELO</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>contact_number</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>71234567</t>
-        </is>
-      </c>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>381234567</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>ADD - NNELO</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>branch_code</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>064967</t>
-        </is>
-      </c>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G35" s="5" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>381234567</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>ADD - NNELO</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>fund_number</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="n"/>
-      <c r="F36" s="3" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>fund_category</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Unknown - Fund Name Not Extracted</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t>WARNING</t>
         </is>
       </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t>Field is blank</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>381234567</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>ADD - NNELO</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>fund_category</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>Unknown - Fund Name Not Extracted</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G37" s="3" t="inlineStr">
+      <c r="G33" s="3" t="inlineStr">
         <is>
           <t>Fund category could not be determined - fund name unclear</t>
         </is>
@@ -3765,7 +3633,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-02T16:38:17</t>
+          <t>2026-07-02T17:02:48</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3775,7 +3643,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>KYC_381234567_TAUNYANE_20260702_1.pdf</t>
+          <t>KYC_381234567_TAUNYANE_20260702_1_2.pdf</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -3804,12 +3672,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-02T16:37:07</t>
+          <t>2026-07-02T17:01:41</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\02\NonMoneyMarket\Captured\KYC_381234567_TAUNYANE_20260702_1.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\02\NonMoneyMarket\Captured\KYC_381234567_TAUNYANE_20260702_1_2.pdf</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -3827,7 +3695,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-02T16:38:17</t>
+          <t>2026-07-02T17:02:48</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3837,7 +3705,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DIS_GSG_381234567_TAUNYANE_20260702_1.pdf</t>
+          <t>DIS_GSG_381234567_TAUNYANE_20260702_1_2.pdf</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -3866,12 +3734,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-07-02T16:37:07</t>
+          <t>2026-07-02T17:01:41</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\02\NonMoneyMarket\Captured\DIS_GSG_381234567_TAUNYANE_20260702_1.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\02\NonMoneyMarket\Captured\DIS_GSG_381234567_TAUNYANE_20260702_1_2.pdf</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -3889,7 +3757,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-02T16:38:17</t>
+          <t>2026-07-02T17:02:48</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3899,7 +3767,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DIS_381234567_TAUNYANE_20260702_VALIDATIONFAILEDFUND_NAME_1.pdf</t>
+          <t>DIS_381234567_TAUNYANE_20260702_VALIDATIONFAILEDFUND_NAME_1_2.pdf</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -3932,12 +3800,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-07-02T16:37:07</t>
+          <t>2026-07-02T17:01:41</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\02\NonMoneyMarket\Captured\Rejected\DIS_381234567_TAUNYANE_20260702_VALIDATIONFAILEDFUND_NAME_1.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\02\NonMoneyMarket\Captured\Rejected\DIS_381234567_TAUNYANE_20260702_VALIDATIONFAILEDFUND_NAME_1_2.pdf</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -3955,7 +3823,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-02T16:38:17</t>
+          <t>2026-07-02T17:02:48</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3965,7 +3833,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DEBIT_381234567_TAUNYANE_20260702_VALIDATIONFAILEDINSTRUCTION_TYPE_1.pdf</t>
+          <t>DEBIT_381234567_TAUNYANE_20260702_VALIDATIONFAILEDINSTRUCTION_TYPE_1_2.pdf</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -3998,12 +3866,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-07-02T16:37:07</t>
+          <t>2026-07-02T17:01:41</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\02\NonMoneyMarket\Captured\Rejected\DEBIT_381234567_TAUNYANE_20260702_VALIDATIONFAILEDINSTRUCTION_TYPE_1.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\02\NonMoneyMarket\Captured\Rejected\DEBIT_381234567_TAUNYANE_20260702_VALIDATIONFAILEDINSTRUCTION_TYPE_1_2.pdf</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -4021,7 +3889,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-02T16:38:17</t>
+          <t>2026-07-02T17:02:48</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -4031,7 +3899,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ADD_381234567_TAUNYANE_20260702_VALIDATIONFAILEDFUND_NAMEFUND_NUMBER_1.pdf</t>
+          <t>ADD_381234567_TAUNYANE_20260702_VALIDATIONFAILEDFUND_NAMEFUND_NUMBER_1_2.pdf</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -4064,12 +3932,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-07-02T16:37:07</t>
+          <t>2026-07-02T17:01:41</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\02\NonMoneyMarket\Captured\Rejected\ADD_381234567_TAUNYANE_20260702_VALIDATIONFAILEDFUND_NAMEFUND_NUMBER_1.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\02\NonMoneyMarket\Captured\Rejected\ADD_381234567_TAUNYANE_20260702_VALIDATIONFAILEDFUND_NAMEFUND_NUMBER_1_2.pdf</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">

--- a/output/BIFM_UT_Processing_Report.xlsx
+++ b/output/BIFM_UT_Processing_Report.xlsx
@@ -1116,7 +1116,7 @@
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>2026-07-02T17:01:41</t>
+          <t>2026-07-02T17:10:12</t>
         </is>
       </c>
       <c r="Q2" s="3" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>2026-07-02T17:01:41</t>
+          <t>2026-07-02T17:10:12</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="P6" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02T17:01:41</t>
+          <t>2026-07-02T17:10:12</t>
         </is>
       </c>
       <c r="Q6" s="4" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02T17:01:41</t>
+          <t>2026-07-02T17:10:12</t>
         </is>
       </c>
       <c r="Q8" s="4" t="inlineStr">
@@ -2178,7 +2178,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02T17:01:41</t>
+          <t>2026-07-02T17:10:12</t>
         </is>
       </c>
       <c r="Q10" s="4" t="inlineStr">
@@ -3633,7 +3633,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:02:48</t>
+          <t>2026-07-02T17:11:20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>KYC_381234567_TAUNYANE_20260702_1_2.pdf</t>
+          <t>KYC_381234567_TAUNYANE_20260702_1_2_3.pdf</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:01:41</t>
+          <t>2026-07-02T17:10:12</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\02\NonMoneyMarket\Captured\KYC_381234567_TAUNYANE_20260702_1_2.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\02\NonMoneyMarket\Captured\KYC_381234567_TAUNYANE_20260702_1_2_3.pdf</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -3695,7 +3695,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-02T17:02:48</t>
+          <t>2026-07-02T17:11:20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DIS_GSG_381234567_TAUNYANE_20260702_1_2.pdf</t>
+          <t>DIS_GSG_381234567_TAUNYANE_20260702_1_2_3.pdf</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-07-02T17:01:41</t>
+          <t>2026-07-02T17:10:12</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\02\NonMoneyMarket\Captured\DIS_GSG_381234567_TAUNYANE_20260702_1_2.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\02\NonMoneyMarket\Captured\DIS_GSG_381234567_TAUNYANE_20260702_1_2_3.pdf</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -3757,7 +3757,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-02T17:02:48</t>
+          <t>2026-07-02T17:11:20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DIS_381234567_TAUNYANE_20260702_VALIDATIONFAILEDFUND_NAME_1_2.pdf</t>
+          <t>DIS_381234567_TAUNYANE_20260702_VALIDATIONFAILEDFUND_NAME_1_2_3.pdf</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -3776,7 +3776,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-07-02T17:01:41</t>
+          <t>2026-07-02T17:10:12</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\02\NonMoneyMarket\Captured\Rejected\DIS_381234567_TAUNYANE_20260702_VALIDATIONFAILEDFUND_NAME_1_2.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\02\NonMoneyMarket\Captured\Rejected\DIS_381234567_TAUNYANE_20260702_VALIDATIONFAILEDFUND_NAME_1_2_3.pdf</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -3823,7 +3823,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-02T17:02:48</t>
+          <t>2026-07-02T17:11:20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3833,7 +3833,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DEBIT_381234567_TAUNYANE_20260702_VALIDATIONFAILEDINSTRUCTION_TYPE_1_2.pdf</t>
+          <t>DEBIT_381234567_TAUNYANE_20260702_VALIDATIONFAILEDINSTRUCTION_TYPE_1_2_3.pdf</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -3866,12 +3866,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-07-02T17:01:41</t>
+          <t>2026-07-02T17:10:12</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\02\NonMoneyMarket\Captured\Rejected\DEBIT_381234567_TAUNYANE_20260702_VALIDATIONFAILEDINSTRUCTION_TYPE_1_2.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\02\NonMoneyMarket\Captured\Rejected\DEBIT_381234567_TAUNYANE_20260702_VALIDATIONFAILEDINSTRUCTION_TYPE_1_2_3.pdf</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -3889,7 +3889,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-02T17:02:48</t>
+          <t>2026-07-02T17:11:20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ADD_381234567_TAUNYANE_20260702_VALIDATIONFAILEDFUND_NAMEFUND_NUMBER_1_2.pdf</t>
+          <t>ADD_381234567_TAUNYANE_20260702_VALIDATIONFAILEDFUND_NAMEFUND_NUMBER_1_2_3.pdf</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-07-02T17:01:41</t>
+          <t>2026-07-02T17:10:12</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\02\NonMoneyMarket\Captured\Rejected\ADD_381234567_TAUNYANE_20260702_VALIDATIONFAILEDFUND_NAMEFUND_NUMBER_1_2.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\02\NonMoneyMarket\Captured\Rejected\ADD_381234567_TAUNYANE_20260702_VALIDATIONFAILEDFUND_NAMEFUND_NUMBER_1_2_3.pdf</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">

--- a/output/BIFM_UT_Processing_Report.xlsx
+++ b/output/BIFM_UT_Processing_Report.xlsx
@@ -39,7 +39,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -66,12 +66,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
         <bgColor rgb="00C6EFCE"/>
       </patternFill>
@@ -89,13 +83,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -694,87 +687,87 @@
       <c r="C3" s="2" t="inlineStr"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
+          <t>98% confidence — majority vote: 4/5 documents agree on this value (differs on: GSGF - NNELO TAUNYANE) — value taken from KYC - Nnelo Taunyane</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
           <t>98% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>98% confidence — 5/5 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>98% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>90% confidence — NO MAJORITY — 2-way tie across 4 documents, no value has more support than another (sources: DEBIT - NNELO, DIS - NNELO, GSGF - NNELO TAUNYANE, KYC - Nnelo Taunyane) — best guess shown from KYC - Nnelo Taunyane, needs manual review before relying on this value — value taken from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>98% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>98% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>98% confidence — majority vote: 3/5 documents agree on this value (differs on: ADD - NNELO, DEBIT - NNELO) — value taken from KYC - Nnelo Taunyane</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>98% confidence — 5/5 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>98% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>98% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>98% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>98% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>98% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>98% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>98% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
-        </is>
-      </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>98% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
+          <t>98% confidence — 2/2 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>98% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
+          <t>98% confidence — 3/3 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>98% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
+          <t>90% confidence — NO MAJORITY — 3-way tie across 3 documents, no value has more support than another (sources: DIS - NNELO, GSGF - NNELO TAUNYANE, KYC - Nnelo Taunyane) — best guess shown from KYC - Nnelo Taunyane, needs manual review before relying on this value — value taken from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
-          <t>98% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
+          <t>98% confidence — 3/3 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>98% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
+          <t>98% confidence — 3/3 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
-          <t>98% confidence — 1/1 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
+          <t>98% confidence — 3/3 document(s) agree — value taken from KYC - Nnelo Taunyane</t>
         </is>
       </c>
     </row>
@@ -789,7 +782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP11"/>
+  <dimension ref="A1:BB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -803,14 +796,14 @@
     <col width="45" customWidth="1" min="9" max="9"/>
     <col width="45" customWidth="1" min="10" max="10"/>
     <col width="45" customWidth="1" min="11" max="11"/>
-    <col width="27" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="43" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="21" customWidth="1" min="16" max="16"/>
+    <col width="45" customWidth="1" min="12" max="12"/>
+    <col width="27" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
     <col width="21" customWidth="1" min="17" max="17"/>
-    <col width="15" customWidth="1" min="18" max="18"/>
-    <col width="45" customWidth="1" min="19" max="19"/>
+    <col width="21" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
     <col width="45" customWidth="1" min="20" max="20"/>
     <col width="45" customWidth="1" min="21" max="21"/>
     <col width="45" customWidth="1" min="22" max="22"/>
@@ -834,6 +827,18 @@
     <col width="45" customWidth="1" min="40" max="40"/>
     <col width="45" customWidth="1" min="41" max="41"/>
     <col width="45" customWidth="1" min="42" max="42"/>
+    <col width="45" customWidth="1" min="43" max="43"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="45" max="45"/>
+    <col width="45" customWidth="1" min="46" max="46"/>
+    <col width="45" customWidth="1" min="47" max="47"/>
+    <col width="45" customWidth="1" min="48" max="48"/>
+    <col width="45" customWidth="1" min="49" max="49"/>
+    <col width="45" customWidth="1" min="50" max="50"/>
+    <col width="45" customWidth="1" min="51" max="51"/>
+    <col width="45" customWidth="1" min="52" max="52"/>
+    <col width="45" customWidth="1" min="53" max="53"/>
+    <col width="45" customWidth="1" min="54" max="54"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -879,170 +884,230 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>fund_number</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>fund_category</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>processing_cutoff</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>fund_category_priority</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>overall_validation_status</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>instruction_status</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>rejection_reason</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>channel</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>upload_date</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>captured_by</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>authorized_by</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>contact_number</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>citizenship</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>bank_account_name</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>bank_name</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>account_number</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>branch_name</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>branch_code</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>account_type_banking</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>account_category</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>account_closure</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>change_amount</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>commencement_date</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>country_of_birth</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>disinvestment_amount</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>employer</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>entity_name</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>income_distribution</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>instruction_mode</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>instruction_type</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>kyc_certified_id</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>kyc_completeness_flag</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>kyc_proof_address</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>kyc_proof_banking</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>kyc_proof_source</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>lump_sum_debit_amount</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>occupation</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>payment_method</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>residential_address</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>source_of_contribution</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>source_of_funds</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>source_of_income</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>sub_instruction_type</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>us_ssn</t>
         </is>
@@ -1051,17 +1116,17 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>GSGF - NNELO TAUNYANE</t>
+          <t>DIS - NNELO</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>DIS_GSG</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Disinvestment Form (GSGF)</t>
+          <t>Disinvestment Form (Standard)</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -1076,242 +1141,286 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>11102222</t>
+          <t>111102222</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr"/>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>BIFM Global Sustainable Growth Fund</t>
+          <t>Bifm Pula Money Market Fund</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>Non-Money Market (GSGF)</t>
+          <t>9876543</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>Quarterly - 7th of last month of quarter</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
+          <t>Money Market</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>1:00 PM</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>WARNING</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>Captured</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr"/>
-      <c r="O2" s="3" t="inlineStr">
+      <c r="O2" s="3" t="inlineStr"/>
+      <c r="P2" s="3" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-02T17:10:12</t>
-        </is>
-      </c>
       <c r="Q2" s="3" t="inlineStr">
         <is>
+          <t>2026-07-02T17:16:15</t>
+        </is>
+      </c>
+      <c r="R2" s="3" t="inlineStr">
+        <is>
           <t>marvel.ai-local-poc</t>
         </is>
       </c>
-      <c r="R2" s="3" t="inlineStr"/>
-      <c r="S2" s="3" t="inlineStr">
+      <c r="S2" s="3" t="inlineStr"/>
+      <c r="T2" s="3" t="inlineStr">
         <is>
           <t>71234567</t>
         </is>
       </c>
-      <c r="T2" s="3" t="inlineStr">
+      <c r="U2" s="3" t="inlineStr">
         <is>
           <t>nnelo@bifm.co.bw</t>
         </is>
       </c>
-      <c r="U2" s="3" t="inlineStr"/>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>NNELO TAUNYANE</t>
-        </is>
-      </c>
+      <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" s="3" t="inlineStr">
         <is>
-          <t>STANBIC</t>
+          <t>NNelo Taunyane</t>
         </is>
       </c>
       <c r="X2" s="3" t="inlineStr">
         <is>
-          <t>9060001231234</t>
+          <t>Stanbic</t>
         </is>
       </c>
       <c r="Y2" s="3" t="inlineStr">
         <is>
-          <t>FAIRGROUNDS</t>
+          <t>9066001231243</t>
         </is>
       </c>
       <c r="Z2" s="3" t="inlineStr">
         <is>
+          <t>Fairgrounds</t>
+        </is>
+      </c>
+      <c r="AA2" s="3" t="inlineStr">
+        <is>
           <t>064967</t>
         </is>
       </c>
-      <c r="AA2" s="3" t="inlineStr">
+      <c r="AB2" s="3" t="inlineStr">
         <is>
           <t>Current</t>
         </is>
       </c>
-      <c r="AB2" s="3" t="inlineStr"/>
       <c r="AC2" s="3" t="inlineStr"/>
-      <c r="AD2" s="3" t="inlineStr"/>
+      <c r="AD2" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="AE2" s="3" t="inlineStr"/>
-      <c r="AF2" s="3" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
-      <c r="AH2" s="3" t="inlineStr"/>
+      <c r="AH2" s="3" t="n">
+        <v>1000</v>
+      </c>
       <c r="AI2" s="3" t="inlineStr"/>
       <c r="AJ2" s="3" t="inlineStr"/>
       <c r="AK2" s="3" t="inlineStr"/>
-      <c r="AL2" s="3" t="inlineStr"/>
+      <c r="AL2" s="3" t="inlineStr">
+        <is>
+          <t>Partial Withdrawal</t>
+        </is>
+      </c>
       <c r="AM2" s="3" t="inlineStr"/>
       <c r="AN2" s="3" t="inlineStr"/>
       <c r="AO2" s="3" t="inlineStr"/>
       <c r="AP2" s="3" t="inlineStr"/>
+      <c r="AQ2" s="3" t="inlineStr"/>
+      <c r="AR2" s="3" t="inlineStr"/>
+      <c r="AS2" s="3" t="inlineStr"/>
+      <c r="AT2" s="3" t="inlineStr"/>
+      <c r="AU2" s="3" t="inlineStr"/>
+      <c r="AV2" s="3" t="inlineStr"/>
+      <c r="AW2" s="3" t="inlineStr"/>
+      <c r="AX2" s="3" t="inlineStr"/>
+      <c r="AY2" s="3" t="inlineStr"/>
+      <c r="AZ2" s="3" t="inlineStr"/>
+      <c r="BA2" s="3" t="inlineStr"/>
+      <c r="BB2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr"/>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>98% confidence — extracted from GSGF - NNELO TAUNYANE</t>
+          <t>98% confidence — extracted from DIS - NNELO</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
+          <t>98% confidence — extracted from DIS - NNELO, p.2</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
+          <t>98% confidence — extracted from DIS - NNELO, p.2</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
+          <t>98% confidence — extracted from DIS - NNELO, p.2</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>98% confidence — extracted from GSGF - NNELO TAUNYANE</t>
+          <t>98% confidence — extracted from DIS - NNELO, p.2</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>98% confidence — extracted from GSGF - NNELO TAUNYANE</t>
+          <t>98% confidence — extracted from DIS - NNELO, p.2</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>98% confidence — extracted from GSGF - NNELO TAUNYANE</t>
+          <t>98% confidence — extracted from DIS - NNELO</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>98% confidence — extracted from GSGF - NNELO TAUNYANE</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
+          <t>98% confidence — extracted from DIS - NNELO</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>98% confidence — extracted from DIS - NNELO</t>
+        </is>
+      </c>
       <c r="M3" s="2" t="inlineStr"/>
       <c r="N3" s="2" t="inlineStr"/>
       <c r="O3" s="2" t="inlineStr"/>
       <c r="P3" s="2" t="inlineStr"/>
       <c r="Q3" s="2" t="inlineStr"/>
       <c r="R3" s="2" t="inlineStr"/>
-      <c r="S3" s="2" t="inlineStr">
-        <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
-        </is>
-      </c>
+      <c r="S3" s="2" t="inlineStr"/>
       <c r="T3" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
-        </is>
-      </c>
-      <c r="U3" s="2" t="inlineStr"/>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
-        </is>
-      </c>
+          <t>98% confidence — extracted from DIS - NNELO, p.2</t>
+        </is>
+      </c>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t>98% confidence — extracted from DIS - NNELO, p.2</t>
+        </is>
+      </c>
+      <c r="V3" s="2" t="inlineStr"/>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
+          <t>98% confidence — extracted from DIS - NNELO, p.2</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
+          <t>98% confidence — extracted from DIS - NNELO, p.2</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
+          <t>98% confidence — extracted from DIS - NNELO, p.2</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
+          <t>98% confidence — extracted from DIS - NNELO, p.2</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+          <t>98% confidence — extracted from DIS - NNELO, p.2</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>98% confidence — extracted from DIS - NNELO, p.2</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr"/>
-      <c r="AD3" s="2" t="inlineStr"/>
+      <c r="AD3" s="2" t="inlineStr">
+        <is>
+          <t>98% confidence — extracted from DIS - NNELO, p.2</t>
+        </is>
+      </c>
       <c r="AE3" s="2" t="inlineStr"/>
-      <c r="AF3" s="2" t="inlineStr">
-        <is>
-          <t>0% confidence — extracted from GSGF - NNELO TAUNYANE — ⚠ recommend recheck</t>
-        </is>
-      </c>
+      <c r="AF3" s="2" t="inlineStr"/>
       <c r="AG3" s="2" t="inlineStr"/>
-      <c r="AH3" s="2" t="inlineStr"/>
+      <c r="AH3" s="2" t="inlineStr">
+        <is>
+          <t>98% confidence — extracted from DIS - NNELO, p.2</t>
+        </is>
+      </c>
       <c r="AI3" s="2" t="inlineStr"/>
       <c r="AJ3" s="2" t="inlineStr"/>
       <c r="AK3" s="2" t="inlineStr"/>
-      <c r="AL3" s="2" t="inlineStr"/>
+      <c r="AL3" s="2" t="inlineStr">
+        <is>
+          <t>98% confidence — extracted from DIS - NNELO</t>
+        </is>
+      </c>
       <c r="AM3" s="2" t="inlineStr"/>
       <c r="AN3" s="2" t="inlineStr"/>
       <c r="AO3" s="2" t="inlineStr"/>
       <c r="AP3" s="2" t="inlineStr"/>
+      <c r="AQ3" s="2" t="inlineStr"/>
+      <c r="AR3" s="2" t="inlineStr"/>
+      <c r="AS3" s="2" t="inlineStr"/>
+      <c r="AT3" s="2" t="inlineStr"/>
+      <c r="AU3" s="2" t="inlineStr"/>
+      <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" s="2" t="inlineStr"/>
+      <c r="AX3" s="2" t="inlineStr"/>
+      <c r="AY3" s="2" t="inlineStr"/>
+      <c r="AZ3" s="2" t="inlineStr"/>
+      <c r="BA3" s="2" t="inlineStr"/>
+      <c r="BB3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>KYC - Nnelo Taunyane</t>
+          <t>DEBIT - NNELO</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>KYC</t>
+          <t>DEBIT</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>KYC (Know Your Customer)</t>
+          <t>Debit Order Form</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -1321,7 +1430,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>NNelo Taunyane</t>
+          <t>NNELO TAUNYANE</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -1329,957 +1438,1077 @@
           <t>11102222</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>01/02/2003</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
-      <c r="J4" s="3" t="inlineStr"/>
-      <c r="K4" s="3" t="inlineStr"/>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Bifm Pula Money Market Fund</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>9876543</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Money Market</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>1:00 PM</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>WARNING</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>Captured</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr"/>
-      <c r="O4" s="3" t="inlineStr">
+      <c r="O4" s="3" t="inlineStr"/>
+      <c r="P4" s="3" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="P4" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-02T17:10:12</t>
-        </is>
-      </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
+          <t>2026-07-02T17:16:15</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
           <t>marvel.ai-local-poc</t>
         </is>
       </c>
-      <c r="R4" s="3" t="inlineStr"/>
-      <c r="S4" s="3" t="inlineStr">
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr">
         <is>
           <t>71234567</t>
         </is>
       </c>
-      <c r="T4" s="3" t="inlineStr">
-        <is>
-          <t>nnelo@bifm.co.bw</t>
-        </is>
-      </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t>MOTSWANA</t>
-        </is>
-      </c>
-      <c r="V4" s="3" t="inlineStr">
+          <t>taunyane@bifm.co.bw</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr"/>
+      <c r="W4" s="3" t="inlineStr">
         <is>
           <t>NNELO TAUNYANE</t>
         </is>
       </c>
-      <c r="W4" s="3" t="inlineStr">
+      <c r="X4" s="3" t="inlineStr">
         <is>
           <t>STANBIC</t>
         </is>
       </c>
-      <c r="X4" s="3" t="inlineStr">
-        <is>
-          <t>9060001231234</t>
-        </is>
-      </c>
-      <c r="Y4" s="3" t="inlineStr">
+      <c r="Y4" s="3" t="inlineStr"/>
+      <c r="Z4" s="3" t="inlineStr">
         <is>
           <t>FAIRGROUNDS</t>
         </is>
       </c>
-      <c r="Z4" s="3" t="inlineStr">
+      <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>064967</t>
         </is>
       </c>
-      <c r="AA4" s="3" t="inlineStr">
+      <c r="AB4" s="3" t="inlineStr">
         <is>
           <t>Current</t>
         </is>
       </c>
-      <c r="AB4" s="3" t="inlineStr">
-        <is>
-          <t>Individual</t>
-        </is>
-      </c>
-      <c r="AC4" s="3" t="inlineStr">
-        <is>
-          <t>BOTSWANA</t>
-        </is>
-      </c>
-      <c r="AD4" s="3" t="inlineStr">
-        <is>
-          <t>BIFM UNIT TRUSTS</t>
-        </is>
-      </c>
+      <c r="AC4" s="3" t="inlineStr"/>
+      <c r="AD4" s="3" t="inlineStr"/>
       <c r="AE4" s="3" t="inlineStr">
         <is>
-          <t>NNELO TAUNYANE</t>
-        </is>
-      </c>
-      <c r="AF4" s="3" t="inlineStr"/>
-      <c r="AG4" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH4" s="3" t="inlineStr">
-        <is>
-          <t>Complete</t>
-        </is>
-      </c>
-      <c r="AI4" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ4" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK4" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL4" s="3" t="inlineStr">
-        <is>
-          <t>INTERN</t>
-        </is>
-      </c>
+          <t>1000-00</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr">
+        <is>
+          <t>M 03 Y 2026</t>
+        </is>
+      </c>
+      <c r="AG4" s="3" t="inlineStr"/>
+      <c r="AH4" s="3" t="inlineStr"/>
+      <c r="AI4" s="3" t="inlineStr"/>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" s="3" t="inlineStr"/>
       <c r="AM4" s="3" t="inlineStr">
         <is>
-          <t>PLOT 1234 GABORONE</t>
-        </is>
-      </c>
-      <c r="AN4" s="3" t="inlineStr">
+          <t>Change existing debit order</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr"/>
+      <c r="AO4" s="3" t="inlineStr"/>
+      <c r="AP4" s="3" t="inlineStr"/>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr"/>
+      <c r="AS4" s="3" t="inlineStr"/>
+      <c r="AT4" s="3" t="inlineStr"/>
+      <c r="AU4" s="3" t="inlineStr"/>
+      <c r="AV4" s="3" t="inlineStr"/>
+      <c r="AW4" s="3" t="inlineStr">
         <is>
           <t>Salary</t>
         </is>
       </c>
-      <c r="AO4" s="3" t="inlineStr">
-        <is>
-          <t>Ms</t>
-        </is>
-      </c>
-      <c r="AP4" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="AX4" s="3" t="inlineStr"/>
+      <c r="AY4" s="3" t="inlineStr"/>
+      <c r="AZ4" s="3" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="BA4" s="3" t="inlineStr"/>
+      <c r="BB4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>98% confidence — extracted from KYC - Nnelo Taunyane</t>
+          <t>98% confidence — extracted from DEBIT - NNELO</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
+          <t>98% confidence — extracted from DEBIT - NNELO, p.2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
+          <t>98% confidence — extracted from DEBIT - NNELO, p.2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr"/>
+          <t>98% confidence — extracted from DEBIT - NNELO, p.2</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>98% confidence — extracted from DEBIT - NNELO, p.2</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>98% confidence — extracted from DEBIT - NNELO, p.2</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>98% confidence — extracted from DEBIT - NNELO</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>98% confidence — extracted from DEBIT - NNELO</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>98% confidence — extracted from DEBIT - NNELO</t>
+        </is>
+      </c>
       <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr"/>
       <c r="O5" s="2" t="inlineStr"/>
       <c r="P5" s="2" t="inlineStr"/>
       <c r="Q5" s="2" t="inlineStr"/>
       <c r="R5" s="2" t="inlineStr"/>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
-        </is>
-      </c>
+      <c r="S5" s="2" t="inlineStr"/>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
+          <t>98% confidence — extracted from DEBIT - NNELO, p.2</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
-        </is>
-      </c>
+          <t>98% confidence — extracted from DEBIT - NNELO, p.2</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr"/>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
-        </is>
-      </c>
-      <c r="Y5" s="2" t="inlineStr">
-        <is>
-          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
-        </is>
-      </c>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
+        </is>
+      </c>
+      <c r="Y5" s="2" t="inlineStr"/>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
-        </is>
-      </c>
-      <c r="AC5" s="2" t="inlineStr">
-        <is>
-          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
-        </is>
-      </c>
-      <c r="AD5" s="2" t="inlineStr">
-        <is>
-          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
-        </is>
-      </c>
+          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
+        </is>
+      </c>
+      <c r="AC5" s="2" t="inlineStr"/>
+      <c r="AD5" s="2" t="inlineStr"/>
       <c r="AE5" s="2" t="inlineStr">
         <is>
-          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
-        </is>
-      </c>
-      <c r="AF5" s="2" t="inlineStr"/>
-      <c r="AG5" s="2" t="inlineStr">
-        <is>
-          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
-        </is>
-      </c>
-      <c r="AH5" s="2" t="inlineStr">
-        <is>
-          <t>98% confidence — extracted from KYC - Nnelo Taunyane</t>
-        </is>
-      </c>
-      <c r="AI5" s="2" t="inlineStr">
-        <is>
-          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
-        </is>
-      </c>
-      <c r="AJ5" s="2" t="inlineStr">
-        <is>
-          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
-        </is>
-      </c>
-      <c r="AK5" s="2" t="inlineStr">
-        <is>
-          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
-        </is>
-      </c>
-      <c r="AL5" s="2" t="inlineStr">
-        <is>
-          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
-        </is>
-      </c>
+          <t>80% confidence — extracted from DEBIT - NNELO, p.2 — ⚠ recommend recheck</t>
+        </is>
+      </c>
+      <c r="AF5" s="2" t="inlineStr">
+        <is>
+          <t>80% confidence — extracted from DEBIT - NNELO, p.2 — ⚠ recommend recheck</t>
+        </is>
+      </c>
+      <c r="AG5" s="2" t="inlineStr"/>
+      <c r="AH5" s="2" t="inlineStr"/>
+      <c r="AI5" s="2" t="inlineStr"/>
+      <c r="AJ5" s="2" t="inlineStr"/>
+      <c r="AK5" s="2" t="inlineStr"/>
+      <c r="AL5" s="2" t="inlineStr"/>
       <c r="AM5" s="2" t="inlineStr">
         <is>
-          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
-        </is>
-      </c>
-      <c r="AN5" s="2" t="inlineStr">
-        <is>
-          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
-        </is>
-      </c>
-      <c r="AO5" s="2" t="inlineStr">
-        <is>
-          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
-        </is>
-      </c>
-      <c r="AP5" s="2" t="inlineStr">
-        <is>
-          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
-        </is>
-      </c>
+          <t>98% confidence — extracted from DEBIT - NNELO, p.2</t>
+        </is>
+      </c>
+      <c r="AN5" s="2" t="inlineStr"/>
+      <c r="AO5" s="2" t="inlineStr"/>
+      <c r="AP5" s="2" t="inlineStr"/>
+      <c r="AQ5" s="2" t="inlineStr"/>
+      <c r="AR5" s="2" t="inlineStr"/>
+      <c r="AS5" s="2" t="inlineStr"/>
+      <c r="AT5" s="2" t="inlineStr"/>
+      <c r="AU5" s="2" t="inlineStr"/>
+      <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" s="2" t="inlineStr">
+        <is>
+          <t>98% confidence — extracted from DEBIT - NNELO, p.2</t>
+        </is>
+      </c>
+      <c r="AX5" s="2" t="inlineStr"/>
+      <c r="AY5" s="2" t="inlineStr"/>
+      <c r="AZ5" s="2" t="inlineStr">
+        <is>
+          <t>98% confidence — extracted from DEBIT - NNELO</t>
+        </is>
+      </c>
+      <c r="BA5" s="2" t="inlineStr"/>
+      <c r="BB5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>DIS - NNELO</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Disinvestment Form (Standard)</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>ADD - NNELO</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Additional Investment Form</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>381234567</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>NNelo Taunyane</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>11102222</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr"/>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>Unknown - Fund Name Not Extracted</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="n">
-        <v>99</v>
-      </c>
-      <c r="L6" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="M6" s="4" t="inlineStr">
-        <is>
-          <t>Rejected</t>
-        </is>
-      </c>
-      <c r="N6" s="4" t="inlineStr">
-        <is>
-          <t>Validation failed: fund_name</t>
-        </is>
-      </c>
-      <c r="O6" s="4" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>NNELO TAUNYANE</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Bifm Pula Money Market Fund</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>1876545</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>Money Market</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>1:00 PM</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>Captured</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr"/>
+      <c r="P6" s="3" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="P6" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-02T17:10:12</t>
-        </is>
-      </c>
-      <c r="Q6" s="4" t="inlineStr">
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-02T17:16:15</t>
+        </is>
+      </c>
+      <c r="R6" s="3" t="inlineStr">
         <is>
           <t>marvel.ai-local-poc</t>
         </is>
       </c>
-      <c r="R6" s="4" t="inlineStr"/>
-      <c r="S6" s="4" t="inlineStr">
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr">
         <is>
           <t>71234567</t>
         </is>
       </c>
-      <c r="T6" s="4" t="inlineStr">
-        <is>
-          <t>nnelo@bifm.co.bw</t>
-        </is>
-      </c>
-      <c r="U6" s="4" t="inlineStr"/>
-      <c r="V6" s="4" t="inlineStr">
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>nneelo@bifm.co.bw</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr"/>
+      <c r="W6" s="3" t="inlineStr">
         <is>
           <t>NNELO TAUNYANE</t>
         </is>
       </c>
-      <c r="W6" s="4" t="inlineStr">
+      <c r="X6" s="3" t="inlineStr">
         <is>
           <t>STANBIC</t>
         </is>
       </c>
-      <c r="X6" s="4" t="inlineStr">
-        <is>
-          <t>9060001231234</t>
-        </is>
-      </c>
-      <c r="Y6" s="4" t="inlineStr">
+      <c r="Y6" s="3" t="inlineStr"/>
+      <c r="Z6" s="3" t="inlineStr">
         <is>
           <t>FAIRGROUNDS</t>
         </is>
       </c>
-      <c r="Z6" s="4" t="inlineStr">
+      <c r="AA6" s="3" t="inlineStr">
         <is>
           <t>064967</t>
         </is>
       </c>
-      <c r="AA6" s="4" t="inlineStr">
+      <c r="AB6" s="3" t="inlineStr">
         <is>
           <t>Current</t>
         </is>
       </c>
-      <c r="AB6" s="4" t="inlineStr"/>
-      <c r="AC6" s="4" t="inlineStr"/>
-      <c r="AD6" s="4" t="inlineStr"/>
-      <c r="AE6" s="4" t="inlineStr"/>
-      <c r="AF6" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="AG6" s="4" t="inlineStr"/>
-      <c r="AH6" s="4" t="inlineStr"/>
-      <c r="AI6" s="4" t="inlineStr"/>
-      <c r="AJ6" s="4" t="inlineStr"/>
-      <c r="AK6" s="4" t="inlineStr"/>
-      <c r="AL6" s="4" t="inlineStr"/>
-      <c r="AM6" s="4" t="inlineStr"/>
-      <c r="AN6" s="4" t="inlineStr"/>
-      <c r="AO6" s="4" t="inlineStr"/>
-      <c r="AP6" s="4" t="inlineStr"/>
+      <c r="AC6" s="3" t="inlineStr"/>
+      <c r="AD6" s="3" t="inlineStr"/>
+      <c r="AE6" s="3" t="inlineStr"/>
+      <c r="AF6" s="3" t="inlineStr"/>
+      <c r="AG6" s="3" t="inlineStr"/>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr"/>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr">
+        <is>
+          <t>Reinvest</t>
+        </is>
+      </c>
+      <c r="AL6" s="3" t="inlineStr"/>
+      <c r="AM6" s="3" t="inlineStr"/>
+      <c r="AN6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr"/>
+      <c r="AP6" s="3" t="inlineStr"/>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr"/>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>1000-00</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr"/>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Investor's bank account</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr"/>
+      <c r="AW6" s="3" t="inlineStr"/>
+      <c r="AX6" s="3" t="inlineStr">
+        <is>
+          <t>Salary</t>
+        </is>
+      </c>
+      <c r="AY6" s="3" t="inlineStr"/>
+      <c r="AZ6" s="3" t="inlineStr"/>
+      <c r="BA6" s="3" t="inlineStr"/>
+      <c r="BB6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr"/>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>98% confidence — extracted from DIS - NNELO</t>
+          <t>98% confidence — extracted from ADD - NNELO</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
+          <t>98% confidence — extracted from ADD - NNELO, p.2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
-        </is>
-      </c>
+          <t>98% confidence — extracted from ADD - NNELO, p.2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>98% confidence — extracted from ADD - NNELO, p.2</t>
+        </is>
+      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>98% confidence — extracted from DIS - NNELO</t>
+          <t>98% confidence — extracted from ADD - NNELO, p.2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>98% confidence — extracted from DIS - NNELO</t>
+          <t>98% confidence — extracted from ADD - NNELO</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>98% confidence — extracted from DIS - NNELO</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr"/>
+          <t>98% confidence — extracted from ADD - NNELO</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>98% confidence — extracted from ADD - NNELO</t>
+        </is>
+      </c>
       <c r="M7" s="2" t="inlineStr"/>
       <c r="N7" s="2" t="inlineStr"/>
       <c r="O7" s="2" t="inlineStr"/>
       <c r="P7" s="2" t="inlineStr"/>
       <c r="Q7" s="2" t="inlineStr"/>
       <c r="R7" s="2" t="inlineStr"/>
-      <c r="S7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr"/>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>98% confidence — extracted from ADD - NNELO, p.2</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>98% confidence — extracted from ADD - NNELO, p.2</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr"/>
+      <c r="W7" s="2" t="inlineStr">
         <is>
           <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
         </is>
       </c>
-      <c r="T7" s="2" t="inlineStr">
+      <c r="X7" s="2" t="inlineStr">
         <is>
           <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
         </is>
       </c>
-      <c r="U7" s="2" t="inlineStr"/>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="Y7" s="2" t="inlineStr"/>
+      <c r="Z7" s="2" t="inlineStr">
         <is>
           <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
         </is>
       </c>
-      <c r="W7" s="2" t="inlineStr">
+      <c r="AA7" s="2" t="inlineStr">
         <is>
           <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
         </is>
       </c>
-      <c r="X7" s="2" t="inlineStr">
+      <c r="AB7" s="2" t="inlineStr">
         <is>
           <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
         </is>
       </c>
-      <c r="Y7" s="2" t="inlineStr">
-        <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
-        </is>
-      </c>
-      <c r="Z7" s="2" t="inlineStr">
-        <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
-        </is>
-      </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr"/>
       <c r="AE7" s="2" t="inlineStr"/>
-      <c r="AF7" s="2" t="inlineStr">
-        <is>
-          <t>0% confidence — extracted from DIS - NNELO — ⚠ recommend recheck</t>
-        </is>
-      </c>
+      <c r="AF7" s="2" t="inlineStr"/>
       <c r="AG7" s="2" t="inlineStr"/>
       <c r="AH7" s="2" t="inlineStr"/>
       <c r="AI7" s="2" t="inlineStr"/>
       <c r="AJ7" s="2" t="inlineStr"/>
-      <c r="AK7" s="2" t="inlineStr"/>
+      <c r="AK7" s="2" t="inlineStr">
+        <is>
+          <t>98% confidence — extracted from ADD - NNELO, p.2</t>
+        </is>
+      </c>
       <c r="AL7" s="2" t="inlineStr"/>
       <c r="AM7" s="2" t="inlineStr"/>
       <c r="AN7" s="2" t="inlineStr"/>
       <c r="AO7" s="2" t="inlineStr"/>
       <c r="AP7" s="2" t="inlineStr"/>
+      <c r="AQ7" s="2" t="inlineStr"/>
+      <c r="AR7" s="2" t="inlineStr"/>
+      <c r="AS7" s="2" t="inlineStr">
+        <is>
+          <t>98% confidence — extracted from ADD - NNELO, p.2</t>
+        </is>
+      </c>
+      <c r="AT7" s="2" t="inlineStr"/>
+      <c r="AU7" s="2" t="inlineStr">
+        <is>
+          <t>98% confidence — extracted from ADD - NNELO, p.2</t>
+        </is>
+      </c>
+      <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" s="2" t="inlineStr"/>
+      <c r="AX7" s="2" t="inlineStr">
+        <is>
+          <t>98% confidence — extracted from ADD - NNELO, p.2</t>
+        </is>
+      </c>
+      <c r="AY7" s="2" t="inlineStr"/>
+      <c r="AZ7" s="2" t="inlineStr"/>
+      <c r="BA7" s="2" t="inlineStr"/>
+      <c r="BB7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>DEBIT - NNELO</t>
+          <t>GSGF - NNELO TAUNYANE</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>DEBIT</t>
+          <t>DIS_GSG</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Debit Order Form</t>
+          <t>Disinvestment Form (GSGF)</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>381234567</t>
+          <t>381234321</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>NNelo Taunyane</t>
+          <t>NNELO TAUNYANE</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>11102222</t>
+          <t>111102222</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr"/>
-      <c r="H8" s="4" t="inlineStr"/>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>Unknown - Fund Name Not Extracted</t>
-        </is>
-      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>BIFM Global Sustainable Growth Fund</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="K8" s="4" t="n">
-        <v>99</v>
-      </c>
-      <c r="L8" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
+          <t>Non-Money Market (GSGF)</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>Quarterly - 7th of last month of quarter</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>3</v>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>Validation failed: instruction_type</t>
-        </is>
-      </c>
-      <c r="O8" s="4" t="inlineStr">
+          <t>Captured</t>
+        </is>
+      </c>
+      <c r="O8" s="4" t="inlineStr"/>
+      <c r="P8" s="4" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="P8" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-02T17:10:12</t>
-        </is>
-      </c>
       <c r="Q8" s="4" t="inlineStr">
         <is>
+          <t>2026-07-02T17:16:15</t>
+        </is>
+      </c>
+      <c r="R8" s="4" t="inlineStr">
+        <is>
           <t>marvel.ai-local-poc</t>
         </is>
       </c>
-      <c r="R8" s="4" t="inlineStr"/>
-      <c r="S8" s="4" t="inlineStr">
+      <c r="S8" s="4" t="inlineStr"/>
+      <c r="T8" s="4" t="inlineStr">
         <is>
           <t>71234567</t>
         </is>
       </c>
-      <c r="T8" s="4" t="inlineStr">
+      <c r="U8" s="4" t="inlineStr">
         <is>
           <t>nnelo@bifm.co.bw</t>
         </is>
       </c>
-      <c r="U8" s="4" t="inlineStr"/>
-      <c r="V8" s="4" t="inlineStr">
+      <c r="V8" s="4" t="inlineStr"/>
+      <c r="W8" s="4" t="inlineStr">
         <is>
           <t>NNELO TAUNYANE</t>
         </is>
       </c>
-      <c r="W8" s="4" t="inlineStr">
+      <c r="X8" s="4" t="inlineStr">
         <is>
           <t>STANBIC</t>
         </is>
       </c>
-      <c r="X8" s="4" t="inlineStr">
-        <is>
-          <t>9060001231234</t>
-        </is>
-      </c>
       <c r="Y8" s="4" t="inlineStr">
         <is>
+          <t>906000123124</t>
+        </is>
+      </c>
+      <c r="Z8" s="4" t="inlineStr">
+        <is>
           <t>FAIRGROUNDS</t>
         </is>
       </c>
-      <c r="Z8" s="4" t="inlineStr">
+      <c r="AA8" s="4" t="inlineStr">
         <is>
           <t>064967</t>
         </is>
       </c>
-      <c r="AA8" s="4" t="inlineStr">
+      <c r="AB8" s="4" t="inlineStr">
         <is>
           <t>Current</t>
         </is>
       </c>
-      <c r="AB8" s="4" t="inlineStr"/>
       <c r="AC8" s="4" t="inlineStr"/>
-      <c r="AD8" s="4" t="inlineStr"/>
+      <c r="AD8" s="4" t="b">
+        <v>0</v>
+      </c>
       <c r="AE8" s="4" t="inlineStr"/>
       <c r="AF8" s="4" t="inlineStr"/>
       <c r="AG8" s="4" t="inlineStr"/>
-      <c r="AH8" s="4" t="inlineStr"/>
+      <c r="AH8" s="4" t="n">
+        <v>5000</v>
+      </c>
       <c r="AI8" s="4" t="inlineStr"/>
       <c r="AJ8" s="4" t="inlineStr"/>
       <c r="AK8" s="4" t="inlineStr"/>
-      <c r="AL8" s="4" t="inlineStr"/>
+      <c r="AL8" s="4" t="inlineStr">
+        <is>
+          <t>Partial Withdrawal</t>
+        </is>
+      </c>
       <c r="AM8" s="4" t="inlineStr"/>
       <c r="AN8" s="4" t="inlineStr"/>
       <c r="AO8" s="4" t="inlineStr"/>
       <c r="AP8" s="4" t="inlineStr"/>
+      <c r="AQ8" s="4" t="inlineStr"/>
+      <c r="AR8" s="4" t="inlineStr"/>
+      <c r="AS8" s="4" t="inlineStr"/>
+      <c r="AT8" s="4" t="inlineStr"/>
+      <c r="AU8" s="4" t="inlineStr"/>
+      <c r="AV8" s="4" t="inlineStr"/>
+      <c r="AW8" s="4" t="inlineStr"/>
+      <c r="AX8" s="4" t="inlineStr"/>
+      <c r="AY8" s="4" t="inlineStr"/>
+      <c r="AZ8" s="4" t="inlineStr"/>
+      <c r="BA8" s="4" t="inlineStr"/>
+      <c r="BB8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>98% confidence — extracted from DEBIT - NNELO</t>
+          <t>98% confidence — extracted from GSGF - NNELO TAUNYANE</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
+          <t>98% confidence — extracted from GSGF - NNELO TAUNYANE, p.2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
+          <t>98% confidence — extracted from GSGF - NNELO TAUNYANE, p.2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
+          <t>98% confidence — extracted from GSGF - NNELO TAUNYANE, p.2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr"/>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>98% confidence — extracted from DEBIT - NNELO</t>
-        </is>
-      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>98% confidence — extracted from GSGF - NNELO TAUNYANE</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>98% confidence — extracted from DEBIT - NNELO</t>
+          <t>98% confidence — extracted from GSGF - NNELO TAUNYANE</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>98% confidence — extracted from DEBIT - NNELO</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr"/>
+          <t>98% confidence — extracted from GSGF - NNELO TAUNYANE</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>98% confidence — extracted from GSGF - NNELO TAUNYANE</t>
+        </is>
+      </c>
       <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr"/>
       <c r="O9" s="2" t="inlineStr"/>
       <c r="P9" s="2" t="inlineStr"/>
       <c r="Q9" s="2" t="inlineStr"/>
       <c r="R9" s="2" t="inlineStr"/>
-      <c r="S9" s="2" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr"/>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>98% confidence — extracted from GSGF - NNELO TAUNYANE, p.2</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>98% confidence — extracted from GSGF - NNELO TAUNYANE, p.2</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr"/>
+      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
         </is>
       </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr"/>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
-        <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
-        </is>
-      </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
+          <t>98% confidence — extracted from GSGF - NNELO TAUNYANE, p.2</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
+          <t>98% confidence — extracted from GSGF - NNELO TAUNYANE, p.2</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
+          <t>98% confidence — extracted from GSGF - NNELO TAUNYANE, p.2</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+          <t>98% confidence — extracted from GSGF - NNELO TAUNYANE, p.2</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>98% confidence — extracted from GSGF - NNELO TAUNYANE, p.2</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr"/>
-      <c r="AD9" s="2" t="inlineStr"/>
+      <c r="AD9" s="2" t="inlineStr">
+        <is>
+          <t>98% confidence — extracted from GSGF - NNELO TAUNYANE, p.2</t>
+        </is>
+      </c>
       <c r="AE9" s="2" t="inlineStr"/>
       <c r="AF9" s="2" t="inlineStr"/>
       <c r="AG9" s="2" t="inlineStr"/>
-      <c r="AH9" s="2" t="inlineStr"/>
+      <c r="AH9" s="2" t="inlineStr">
+        <is>
+          <t>98% confidence — extracted from GSGF - NNELO TAUNYANE, p.2</t>
+        </is>
+      </c>
       <c r="AI9" s="2" t="inlineStr"/>
       <c r="AJ9" s="2" t="inlineStr"/>
       <c r="AK9" s="2" t="inlineStr"/>
-      <c r="AL9" s="2" t="inlineStr"/>
+      <c r="AL9" s="2" t="inlineStr">
+        <is>
+          <t>98% confidence — extracted from GSGF - NNELO TAUNYANE</t>
+        </is>
+      </c>
       <c r="AM9" s="2" t="inlineStr"/>
       <c r="AN9" s="2" t="inlineStr"/>
       <c r="AO9" s="2" t="inlineStr"/>
       <c r="AP9" s="2" t="inlineStr"/>
+      <c r="AQ9" s="2" t="inlineStr"/>
+      <c r="AR9" s="2" t="inlineStr"/>
+      <c r="AS9" s="2" t="inlineStr"/>
+      <c r="AT9" s="2" t="inlineStr"/>
+      <c r="AU9" s="2" t="inlineStr"/>
+      <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" s="2" t="inlineStr"/>
+      <c r="AX9" s="2" t="inlineStr"/>
+      <c r="AY9" s="2" t="inlineStr"/>
+      <c r="AZ9" s="2" t="inlineStr"/>
+      <c r="BA9" s="2" t="inlineStr"/>
+      <c r="BB9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>ADD - NNELO</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Additional Investment Form</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>KYC - Nnelo Taunyane</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>KYC</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>KYC (Know Your Customer)</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>381234567</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>NNelo Taunyane</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr"/>
-      <c r="G10" s="4" t="inlineStr"/>
-      <c r="H10" s="4" t="inlineStr"/>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>Unknown - Fund Name Not Extracted</t>
-        </is>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="n">
-        <v>99</v>
-      </c>
-      <c r="L10" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="M10" s="4" t="inlineStr">
-        <is>
-          <t>Rejected</t>
-        </is>
-      </c>
-      <c r="N10" s="4" t="inlineStr">
-        <is>
-          <t>Validation failed: fund_name, fund_number</t>
-        </is>
-      </c>
-      <c r="O10" s="4" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>11102222</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>01/02/2003</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr"/>
+      <c r="I10" s="3" t="inlineStr"/>
+      <c r="J10" s="3" t="inlineStr"/>
+      <c r="K10" s="3" t="inlineStr"/>
+      <c r="L10" s="3" t="inlineStr"/>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Captured</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr"/>
+      <c r="P10" s="3" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="P10" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-02T17:10:12</t>
-        </is>
-      </c>
-      <c r="Q10" s="4" t="inlineStr">
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-02T17:16:15</t>
+        </is>
+      </c>
+      <c r="R10" s="3" t="inlineStr">
         <is>
           <t>marvel.ai-local-poc</t>
         </is>
       </c>
-      <c r="R10" s="4" t="inlineStr"/>
-      <c r="S10" s="4" t="inlineStr">
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr">
         <is>
           <t>71234567</t>
         </is>
       </c>
-      <c r="T10" s="4" t="inlineStr">
+      <c r="U10" s="3" t="inlineStr">
         <is>
           <t>nnelo@bifm.co.bw</t>
         </is>
       </c>
-      <c r="U10" s="4" t="inlineStr"/>
-      <c r="V10" s="4" t="inlineStr">
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>MOTSWANA</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
         <is>
           <t>NNELO TAUNYANE</t>
         </is>
       </c>
-      <c r="W10" s="4" t="inlineStr">
+      <c r="X10" s="3" t="inlineStr">
         <is>
           <t>STANBIC</t>
         </is>
       </c>
-      <c r="X10" s="4" t="inlineStr">
+      <c r="Y10" s="3" t="inlineStr">
         <is>
           <t>9060001231234</t>
         </is>
       </c>
-      <c r="Y10" s="4" t="inlineStr">
+      <c r="Z10" s="3" t="inlineStr">
         <is>
           <t>FAIRGROUNDS</t>
         </is>
       </c>
-      <c r="Z10" s="4" t="inlineStr">
+      <c r="AA10" s="3" t="inlineStr">
         <is>
           <t>064967</t>
         </is>
       </c>
-      <c r="AA10" s="4" t="inlineStr">
+      <c r="AB10" s="3" t="inlineStr">
         <is>
           <t>Current</t>
         </is>
       </c>
-      <c r="AB10" s="4" t="inlineStr"/>
-      <c r="AC10" s="4" t="inlineStr"/>
-      <c r="AD10" s="4" t="inlineStr"/>
-      <c r="AE10" s="4" t="inlineStr"/>
-      <c r="AF10" s="4" t="inlineStr"/>
-      <c r="AG10" s="4" t="inlineStr"/>
-      <c r="AH10" s="4" t="inlineStr"/>
-      <c r="AI10" s="4" t="inlineStr"/>
-      <c r="AJ10" s="4" t="inlineStr"/>
-      <c r="AK10" s="4" t="inlineStr"/>
-      <c r="AL10" s="4" t="inlineStr"/>
-      <c r="AM10" s="4" t="inlineStr"/>
-      <c r="AN10" s="4" t="inlineStr"/>
-      <c r="AO10" s="4" t="inlineStr"/>
-      <c r="AP10" s="4" t="inlineStr"/>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>Individual</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr"/>
+      <c r="AE10" s="3" t="inlineStr"/>
+      <c r="AF10" s="3" t="inlineStr"/>
+      <c r="AG10" s="3" t="inlineStr">
+        <is>
+          <t>BOTSWANA</t>
+        </is>
+      </c>
+      <c r="AH10" s="3" t="inlineStr"/>
+      <c r="AI10" s="3" t="inlineStr">
+        <is>
+          <t>BIFM UNIT TRUSTS</t>
+        </is>
+      </c>
+      <c r="AJ10" s="3" t="inlineStr">
+        <is>
+          <t>NNELO TAUNYANE</t>
+        </is>
+      </c>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr"/>
+      <c r="AM10" s="3" t="inlineStr"/>
+      <c r="AN10" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AP10" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ10" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AR10" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AS10" s="3" t="inlineStr"/>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>INTERN</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr"/>
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
+          <t>PLOT 1234 GABORONE</t>
+        </is>
+      </c>
+      <c r="AW10" s="3" t="inlineStr"/>
+      <c r="AX10" s="3" t="inlineStr"/>
+      <c r="AY10" s="3" t="inlineStr">
+        <is>
+          <t>Salary</t>
+        </is>
+      </c>
+      <c r="AZ10" s="3" t="inlineStr"/>
+      <c r="BA10" s="3" t="inlineStr">
+        <is>
+          <t>Ms</t>
+        </is>
+      </c>
+      <c r="BB10" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>98% confidence — extracted from ADD - NNELO</t>
+          <t>98% confidence — extracted from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
+          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr"/>
-      <c r="G11" s="2" t="inlineStr"/>
+          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
+        </is>
+      </c>
       <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98% confidence — extracted from ADD - NNELO</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>98% confidence — extracted from ADD - NNELO</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>98% confidence — extracted from ADD - NNELO</t>
-        </is>
-      </c>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr"/>
       <c r="N11" s="2" t="inlineStr"/>
@@ -2287,62 +2516,134 @@
       <c r="P11" s="2" t="inlineStr"/>
       <c r="Q11" s="2" t="inlineStr"/>
       <c r="R11" s="2" t="inlineStr"/>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
-        </is>
-      </c>
+      <c r="S11" s="2" t="inlineStr"/>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr"/>
+          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
+        </is>
+      </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
+          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
+          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
+          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
+          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
+          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>85% confidence — backfilled from KYC - Nnelo Taunyane — ⚠ recommend recheck</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
-      <c r="AC11" s="2" t="inlineStr"/>
+          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
+        </is>
+      </c>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
+        </is>
+      </c>
       <c r="AD11" s="2" t="inlineStr"/>
       <c r="AE11" s="2" t="inlineStr"/>
       <c r="AF11" s="2" t="inlineStr"/>
-      <c r="AG11" s="2" t="inlineStr"/>
+      <c r="AG11" s="2" t="inlineStr">
+        <is>
+          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
+        </is>
+      </c>
       <c r="AH11" s="2" t="inlineStr"/>
-      <c r="AI11" s="2" t="inlineStr"/>
-      <c r="AJ11" s="2" t="inlineStr"/>
+      <c r="AI11" s="2" t="inlineStr">
+        <is>
+          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
+        </is>
+      </c>
+      <c r="AJ11" s="2" t="inlineStr">
+        <is>
+          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
+        </is>
+      </c>
       <c r="AK11" s="2" t="inlineStr"/>
       <c r="AL11" s="2" t="inlineStr"/>
       <c r="AM11" s="2" t="inlineStr"/>
-      <c r="AN11" s="2" t="inlineStr"/>
-      <c r="AO11" s="2" t="inlineStr"/>
-      <c r="AP11" s="2" t="inlineStr"/>
+      <c r="AN11" s="2" t="inlineStr">
+        <is>
+          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
+        </is>
+      </c>
+      <c r="AO11" s="2" t="inlineStr">
+        <is>
+          <t>98% confidence — extracted from KYC - Nnelo Taunyane</t>
+        </is>
+      </c>
+      <c r="AP11" s="2" t="inlineStr">
+        <is>
+          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
+        </is>
+      </c>
+      <c r="AQ11" s="2" t="inlineStr">
+        <is>
+          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
+        </is>
+      </c>
+      <c r="AR11" s="2" t="inlineStr">
+        <is>
+          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
+        </is>
+      </c>
+      <c r="AS11" s="2" t="inlineStr"/>
+      <c r="AT11" s="2" t="inlineStr">
+        <is>
+          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
+        </is>
+      </c>
+      <c r="AU11" s="2" t="inlineStr"/>
+      <c r="AV11" s="2" t="inlineStr">
+        <is>
+          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
+        </is>
+      </c>
+      <c r="AW11" s="2" t="inlineStr"/>
+      <c r="AX11" s="2" t="inlineStr"/>
+      <c r="AY11" s="2" t="inlineStr">
+        <is>
+          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
+        </is>
+      </c>
+      <c r="AZ11" s="2" t="inlineStr"/>
+      <c r="BA11" s="2" t="inlineStr">
+        <is>
+          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
+        </is>
+      </c>
+      <c r="BB11" s="2" t="inlineStr">
+        <is>
+          <t>98% confidence — extracted from KYC - Nnelo Taunyane, p.1</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2403,14 +2704,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
   </cols>
@@ -2453,33 +2754,33 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>381234567</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>KYC - Nnelo Taunyane</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>KYC</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>gender</t>
         </is>
       </c>
-      <c r="E2" s="5" t="n"/>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="E2" s="4" t="n"/>
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Gender derivation not applicable for this ID type</t>
         </is>
@@ -2519,338 +2820,334 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>381234567</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>KYC - Nnelo Taunyane</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>KYC</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>date_of_birth</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>01/02/2003</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>381234567</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>KYC - Nnelo Taunyane</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>KYC</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>nnelo@bifm.co.bw</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr"/>
+      <c r="G5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>381234567</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>KYC - Nnelo Taunyane</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>KYC</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>contact_number</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>71234567</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>381234567</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>KYC - Nnelo Taunyane</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>KYC</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>branch_code</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>064967</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr"/>
+      <c r="G7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>381234567</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>KYC - Nnelo Taunyane</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>KYC</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>kyc_completeness_flag</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr"/>
+      <c r="G8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>381234567</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>381234321</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>GSGF - NNELO TAUNYANE</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>DIS_GSG</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>nnelo@bifm.co.bw</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr"/>
+      <c r="G9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>381234567</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>381234321</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>GSGF - NNELO TAUNYANE</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>DIS_GSG</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>contact_number</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>71234567</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr"/>
+      <c r="G10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>381234567</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>381234321</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>GSGF - NNELO TAUNYANE</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>DIS_GSG</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>branch_code</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>064967</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr"/>
+      <c r="G11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>381234567</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>381234321</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>GSGF - NNELO TAUNYANE</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>DIS_GSG</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>fund_category</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>Non-Money Market (GSGF)</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr"/>
+      <c r="G12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>381234567</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>381234321</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>GSGF - NNELO TAUNYANE</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>DIS_GSG</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>instruction_mode</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>Could not determine instruction mode - no closure tick, percentage, or withdrawal/deposit amount was found</t>
-        </is>
-      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Partial Withdrawal</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -2870,226 +3167,222 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>fund_name</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="n"/>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>nnelo@bifm.co.bw</t>
+        </is>
+      </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>Mandatory field missing</t>
-        </is>
-      </c>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>381234567</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>DIS - NNELO</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>DIS</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>contact_number</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>71234567</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>381234567</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>DIS - NNELO</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>branch_code</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>064967</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>381234567</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>DIS - NNELO</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>fund_number</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>9876543</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>Expected 8 or 9 digits, got 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>381234567</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>DIS - NNELO</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>fund_category</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Money Market</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>381234567</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>DIS - NNELO</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>instruction_mode</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Partial Withdrawal</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>381234567</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>DEBIT - NNELO</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>DEBIT</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>nnelo@bifm.co.bw</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>taunyane@bifm.co.bw</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>381234567</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>DIS - NNELO</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>contact_number</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>71234567</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>381234567</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>DIS - NNELO</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>branch_code</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>064967</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>381234567</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>DIS - NNELO</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>fund_number</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="n"/>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>Field is blank</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>381234567</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>DIS - NNELO</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>fund_category</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>Unknown - Fund Name Not Extracted</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>Fund category could not be determined - fund name unclear</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>381234567</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>DIS - NNELO</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>instruction_mode</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>Could not determine instruction mode - no closure tick, percentage, or withdrawal/deposit amount was found</t>
-        </is>
-      </c>
+      <c r="G20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -3109,189 +3402,189 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>instruction_type</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="n"/>
+          <t>contact_number</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>71234567</t>
+        </is>
+      </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>Mandatory field missing</t>
-        </is>
-      </c>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>381234567</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>DEBIT - NNELO</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>DEBIT</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>branch_code</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>064967</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>381234567</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT - NNELO</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>fund_number</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>9876543</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>Expected 8 or 9 digits, got 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>381234567</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>DEBIT - NNELO</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>DEBIT</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>fund_category</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Money Market</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>381234567</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>ADD - NNELO</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>nnelo@bifm.co.bw</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>nneelo@bifm.co.bw</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>381234567</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>DEBIT - NNELO</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>DEBIT</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>ADD - NNELO</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>contact_number</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>71234567</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>381234567</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>DEBIT - NNELO</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>DEBIT</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>branch_code</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>064967</t>
-        </is>
-      </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>381234567</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>DEBIT - NNELO</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>DEBIT</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>fund_number</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="n"/>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>Field is blank</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>381234567</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>DEBIT - NNELO</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>DEBIT</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>fund_category</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>Unknown - Fund Name Not Extracted</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>Fund category could not be determined - fund name unclear</t>
-        </is>
-      </c>
+      <c r="G26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -3311,222 +3604,90 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>fund_name</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="n"/>
+          <t>branch_code</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>064967</t>
+        </is>
+      </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t>Mandatory field missing</t>
-        </is>
-      </c>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>381234567</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>ADD - NNELO</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>ADD</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>fund_number</t>
         </is>
       </c>
-      <c r="E28" s="4" t="n"/>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G28" s="4" t="inlineStr">
-        <is>
-          <t>Mandatory field missing</t>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>1876545</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>Expected 8 or 9 digits, got 7</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>381234567</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>ADD - NNELO</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>ADD</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>nnelo@bifm.co.bw</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>fund_category</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Money Market</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>381234567</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>ADD - NNELO</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>contact_number</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>71234567</t>
-        </is>
-      </c>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>381234567</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>ADD - NNELO</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>branch_code</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>064967</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>381234567</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>ADD - NNELO</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>fund_number</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="n"/>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>Field is blank</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>381234567</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>ADD - NNELO</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>fund_category</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>Unknown - Fund Name Not Extracted</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>Fund category could not be determined - fund name unclear</t>
-        </is>
-      </c>
+      <c r="G29" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3549,7 +3710,7 @@
     <col width="27" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="43" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
     <col width="45" customWidth="1" min="11" max="11"/>
@@ -3633,7 +3794,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:11:20</t>
+          <t>2026-07-02T17:18:22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3643,7 +3804,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>KYC_381234567_TAUNYANE_20260702_1_2_3.pdf</t>
+          <t>KYC_381234567_TAUNYANE_20260702_1_2_3_4.pdf</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -3672,12 +3833,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:10:12</t>
+          <t>2026-07-02T17:16:15</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\02\NonMoneyMarket\Captured\KYC_381234567_TAUNYANE_20260702_1_2_3.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\02\NonMoneyMarket\Captured\KYC_381234567_TAUNYANE_20260702_1_2_3_4.pdf</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -3695,7 +3856,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-02T17:11:20</t>
+          <t>2026-07-02T17:18:22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3705,7 +3866,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DIS_GSG_381234567_TAUNYANE_20260702_1_2_3.pdf</t>
+          <t>DIS_GSG_381234321_TAUNYANE_20260702.pdf</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -3718,7 +3879,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>WARNING</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3734,12 +3895,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-07-02T17:10:12</t>
+          <t>2026-07-02T17:16:15</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\02\NonMoneyMarket\Captured\DIS_GSG_381234567_TAUNYANE_20260702_1_2_3.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\02\NonMoneyMarket\Captured\DIS_GSG_381234321_TAUNYANE_20260702.pdf</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -3757,7 +3918,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-02T17:11:20</t>
+          <t>2026-07-02T17:18:22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3767,7 +3928,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DIS_381234567_TAUNYANE_20260702_VALIDATIONFAILEDFUND_NAME_1_2_3.pdf</t>
+          <t>DIS_381234567_TAUNYANE_20260702.pdf</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -3776,23 +3937,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>WARNING</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rejected</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Validation failed: fund_name</t>
-        </is>
-      </c>
+          <t>Captured</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Email</t>
@@ -3800,12 +3957,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-07-02T17:10:12</t>
+          <t>2026-07-02T17:16:15</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\02\NonMoneyMarket\Captured\Rejected\DIS_381234567_TAUNYANE_20260702_VALIDATIONFAILEDFUND_NAME_1_2_3.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\02\MoneyMarket\Captured\DIS_381234567_TAUNYANE_20260702.pdf</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -3823,7 +3980,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-02T17:11:20</t>
+          <t>2026-07-02T17:18:22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3833,7 +3990,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DEBIT_381234567_TAUNYANE_20260702_VALIDATIONFAILEDINSTRUCTION_TYPE_1_2_3.pdf</t>
+          <t>DEBIT_381234567_TAUNYANE_20260702.pdf</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -3846,19 +4003,15 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>WARNING</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rejected</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Validation failed: instruction_type</t>
-        </is>
-      </c>
+          <t>Captured</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Email</t>
@@ -3866,12 +4019,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-07-02T17:10:12</t>
+          <t>2026-07-02T17:16:15</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\02\NonMoneyMarket\Captured\Rejected\DEBIT_381234567_TAUNYANE_20260702_VALIDATIONFAILEDINSTRUCTION_TYPE_1_2_3.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\02\MoneyMarket\Captured\DEBIT_381234567_TAUNYANE_20260702.pdf</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -3889,7 +4042,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-02T17:11:20</t>
+          <t>2026-07-02T17:18:22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3899,7 +4052,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ADD_381234567_TAUNYANE_20260702_VALIDATIONFAILEDFUND_NAMEFUND_NUMBER_1_2_3.pdf</t>
+          <t>ADD_381234567_TAUNYANE_20260702.pdf</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -3912,19 +4065,15 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>WARNING</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rejected</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Validation failed: fund_name, fund_number</t>
-        </is>
-      </c>
+          <t>Captured</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Email</t>
@@ -3932,12 +4081,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-07-02T17:10:12</t>
+          <t>2026-07-02T17:16:15</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\02\NonMoneyMarket\Captured\Rejected\ADD_381234567_TAUNYANE_20260702_VALIDATIONFAILEDFUND_NAMEFUND_NUMBER_1_2_3.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\02\MoneyMarket\Captured\ADD_381234567_TAUNYANE_20260702.pdf</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">

--- a/output/BIFM_UT_Processing_Report.xlsx
+++ b/output/BIFM_UT_Processing_Report.xlsx
@@ -60,14 +60,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-        <bgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -607,7 +607,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>NNelo Taunyane</t>
+          <t>NNELO TAUNYANE</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>98% confidence — majority vote: 3/5 documents agree on this value (differs on: ADD - NNELO, DEBIT - NNELO) — value taken from KYC - Nnelo Taunyane</t>
+          <t>98% confidence — majority vote: 4/5 documents agree on this value (differs on: DEBIT - NNELO) — value taken from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>WARNING</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="Q2" s="3" t="inlineStr">
         <is>
-          <t>2026-07-02T17:16:15</t>
+          <t>2026-07-02T17:24:42</t>
         </is>
       </c>
       <c r="R2" s="3" t="inlineStr">
@@ -1243,8 +1243,10 @@
       <c r="AE2" s="3" t="inlineStr"/>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
-      <c r="AH2" s="3" t="n">
-        <v>1000</v>
+      <c r="AH2" s="3" t="inlineStr">
+        <is>
+          <t>1000.00</t>
+        </is>
       </c>
       <c r="AI2" s="3" t="inlineStr"/>
       <c r="AJ2" s="3" t="inlineStr"/>
@@ -1464,7 +1466,7 @@
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>WARNING</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -1480,7 +1482,7 @@
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>2026-07-02T17:16:15</t>
+          <t>2026-07-02T17:24:42</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
@@ -1535,7 +1537,7 @@
       </c>
       <c r="AF4" s="3" t="inlineStr">
         <is>
-          <t>M 03 Y 2026</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="AG4" s="3" t="inlineStr"/>
@@ -1675,7 +1677,7 @@
       </c>
       <c r="AF5" s="2" t="inlineStr">
         <is>
-          <t>80% confidence — extracted from DEBIT - NNELO, p.2 — ⚠ recommend recheck</t>
+          <t>98% confidence — extracted from DEBIT - NNELO, p.2</t>
         </is>
       </c>
       <c r="AG5" s="2" t="inlineStr"/>
@@ -1766,7 +1768,7 @@
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>WARNING</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
@@ -1782,7 +1784,7 @@
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>2026-07-02T17:16:15</t>
+          <t>2026-07-02T17:24:42</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
@@ -1798,7 +1800,7 @@
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t>nneelo@bifm.co.bw</t>
+          <t>nnelo@bifm.co.bw</t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr"/>
@@ -2004,158 +2006,158 @@
       <c r="BB7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>GSGF - NNELO TAUNYANE</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>DIS_GSG</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Disinvestment Form (GSGF)</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>381234321</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>NNELO TAUNYANE</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>111102222</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr"/>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>BIFM Global Sustainable Growth Fund</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr"/>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="I8" s="3" t="inlineStr"/>
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>Non-Money Market (GSGF)</t>
         </is>
       </c>
-      <c r="K8" s="4" t="inlineStr">
+      <c r="K8" s="3" t="inlineStr">
         <is>
           <t>Quarterly - 7th of last month of quarter</t>
         </is>
       </c>
-      <c r="L8" s="4" t="n">
+      <c r="L8" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="M8" s="4" t="inlineStr">
+      <c r="M8" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="N8" s="4" t="inlineStr">
+      <c r="N8" s="3" t="inlineStr">
         <is>
           <t>Captured</t>
         </is>
       </c>
-      <c r="O8" s="4" t="inlineStr"/>
-      <c r="P8" s="4" t="inlineStr">
+      <c r="O8" s="3" t="inlineStr"/>
+      <c r="P8" s="3" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="Q8" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-02T17:16:15</t>
-        </is>
-      </c>
-      <c r="R8" s="4" t="inlineStr">
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-02T17:24:42</t>
+        </is>
+      </c>
+      <c r="R8" s="3" t="inlineStr">
         <is>
           <t>marvel.ai-local-poc</t>
         </is>
       </c>
-      <c r="S8" s="4" t="inlineStr"/>
-      <c r="T8" s="4" t="inlineStr">
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr">
         <is>
           <t>71234567</t>
         </is>
       </c>
-      <c r="U8" s="4" t="inlineStr">
+      <c r="U8" s="3" t="inlineStr">
         <is>
           <t>nnelo@bifm.co.bw</t>
         </is>
       </c>
-      <c r="V8" s="4" t="inlineStr"/>
-      <c r="W8" s="4" t="inlineStr">
+      <c r="V8" s="3" t="inlineStr"/>
+      <c r="W8" s="3" t="inlineStr">
         <is>
           <t>NNELO TAUNYANE</t>
         </is>
       </c>
-      <c r="X8" s="4" t="inlineStr">
+      <c r="X8" s="3" t="inlineStr">
         <is>
           <t>STANBIC</t>
         </is>
       </c>
-      <c r="Y8" s="4" t="inlineStr">
+      <c r="Y8" s="3" t="inlineStr">
         <is>
           <t>906000123124</t>
         </is>
       </c>
-      <c r="Z8" s="4" t="inlineStr">
+      <c r="Z8" s="3" t="inlineStr">
         <is>
           <t>FAIRGROUNDS</t>
         </is>
       </c>
-      <c r="AA8" s="4" t="inlineStr">
+      <c r="AA8" s="3" t="inlineStr">
         <is>
           <t>064967</t>
         </is>
       </c>
-      <c r="AB8" s="4" t="inlineStr">
+      <c r="AB8" s="3" t="inlineStr">
         <is>
           <t>Current</t>
         </is>
       </c>
-      <c r="AC8" s="4" t="inlineStr"/>
-      <c r="AD8" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" s="4" t="inlineStr"/>
-      <c r="AF8" s="4" t="inlineStr"/>
-      <c r="AG8" s="4" t="inlineStr"/>
-      <c r="AH8" s="4" t="n">
+      <c r="AC8" s="3" t="inlineStr"/>
+      <c r="AD8" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE8" s="3" t="inlineStr"/>
+      <c r="AF8" s="3" t="inlineStr"/>
+      <c r="AG8" s="3" t="inlineStr"/>
+      <c r="AH8" s="3" t="n">
         <v>5000</v>
       </c>
-      <c r="AI8" s="4" t="inlineStr"/>
-      <c r="AJ8" s="4" t="inlineStr"/>
-      <c r="AK8" s="4" t="inlineStr"/>
-      <c r="AL8" s="4" t="inlineStr">
-        <is>
-          <t>Partial Withdrawal</t>
-        </is>
-      </c>
-      <c r="AM8" s="4" t="inlineStr"/>
-      <c r="AN8" s="4" t="inlineStr"/>
-      <c r="AO8" s="4" t="inlineStr"/>
-      <c r="AP8" s="4" t="inlineStr"/>
-      <c r="AQ8" s="4" t="inlineStr"/>
-      <c r="AR8" s="4" t="inlineStr"/>
-      <c r="AS8" s="4" t="inlineStr"/>
-      <c r="AT8" s="4" t="inlineStr"/>
-      <c r="AU8" s="4" t="inlineStr"/>
-      <c r="AV8" s="4" t="inlineStr"/>
-      <c r="AW8" s="4" t="inlineStr"/>
-      <c r="AX8" s="4" t="inlineStr"/>
-      <c r="AY8" s="4" t="inlineStr"/>
-      <c r="AZ8" s="4" t="inlineStr"/>
-      <c r="BA8" s="4" t="inlineStr"/>
-      <c r="BB8" s="4" t="inlineStr"/>
+      <c r="AI8" s="3" t="inlineStr"/>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr">
+        <is>
+          <t>Full Closure</t>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr"/>
+      <c r="AN8" s="3" t="inlineStr"/>
+      <c r="AO8" s="3" t="inlineStr"/>
+      <c r="AP8" s="3" t="inlineStr"/>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr"/>
+      <c r="AS8" s="3" t="inlineStr"/>
+      <c r="AT8" s="3" t="inlineStr"/>
+      <c r="AU8" s="3" t="inlineStr"/>
+      <c r="AV8" s="3" t="inlineStr"/>
+      <c r="AW8" s="3" t="inlineStr"/>
+      <c r="AX8" s="3" t="inlineStr"/>
+      <c r="AY8" s="3" t="inlineStr"/>
+      <c r="AZ8" s="3" t="inlineStr"/>
+      <c r="BA8" s="3" t="inlineStr"/>
+      <c r="BB8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr"/>
@@ -2290,188 +2292,188 @@
       <c r="BB9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>KYC - Nnelo Taunyane</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>KYC</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>KYC (Know Your Customer)</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>381234567</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>NNelo Taunyane</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>NNELO TAUNYANE</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>11102222</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>01/02/2003</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="3" t="inlineStr"/>
-      <c r="J10" s="3" t="inlineStr"/>
-      <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="3" t="inlineStr"/>
-      <c r="M10" s="3" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr"/>
+      <c r="I10" s="4" t="inlineStr"/>
+      <c r="J10" s="4" t="inlineStr"/>
+      <c r="K10" s="4" t="inlineStr"/>
+      <c r="L10" s="4" t="inlineStr"/>
+      <c r="M10" s="4" t="inlineStr">
         <is>
           <t>WARNING</t>
         </is>
       </c>
-      <c r="N10" s="3" t="inlineStr">
+      <c r="N10" s="4" t="inlineStr">
         <is>
           <t>Captured</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr"/>
-      <c r="P10" s="3" t="inlineStr">
+      <c r="O10" s="4" t="inlineStr"/>
+      <c r="P10" s="4" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="Q10" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-02T17:16:15</t>
-        </is>
-      </c>
-      <c r="R10" s="3" t="inlineStr">
+      <c r="Q10" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02T17:24:42</t>
+        </is>
+      </c>
+      <c r="R10" s="4" t="inlineStr">
         <is>
           <t>marvel.ai-local-poc</t>
         </is>
       </c>
-      <c r="S10" s="3" t="inlineStr"/>
-      <c r="T10" s="3" t="inlineStr">
+      <c r="S10" s="4" t="inlineStr"/>
+      <c r="T10" s="4" t="inlineStr">
         <is>
           <t>71234567</t>
         </is>
       </c>
-      <c r="U10" s="3" t="inlineStr">
+      <c r="U10" s="4" t="inlineStr">
         <is>
           <t>nnelo@bifm.co.bw</t>
         </is>
       </c>
-      <c r="V10" s="3" t="inlineStr">
+      <c r="V10" s="4" t="inlineStr">
         <is>
           <t>MOTSWANA</t>
         </is>
       </c>
-      <c r="W10" s="3" t="inlineStr">
+      <c r="W10" s="4" t="inlineStr">
         <is>
           <t>NNELO TAUNYANE</t>
         </is>
       </c>
-      <c r="X10" s="3" t="inlineStr">
+      <c r="X10" s="4" t="inlineStr">
         <is>
           <t>STANBIC</t>
         </is>
       </c>
-      <c r="Y10" s="3" t="inlineStr">
+      <c r="Y10" s="4" t="inlineStr">
         <is>
           <t>9060001231234</t>
         </is>
       </c>
-      <c r="Z10" s="3" t="inlineStr">
+      <c r="Z10" s="4" t="inlineStr">
         <is>
           <t>FAIRGROUNDS</t>
         </is>
       </c>
-      <c r="AA10" s="3" t="inlineStr">
+      <c r="AA10" s="4" t="inlineStr">
         <is>
           <t>064967</t>
         </is>
       </c>
-      <c r="AB10" s="3" t="inlineStr">
+      <c r="AB10" s="4" t="inlineStr">
         <is>
           <t>Current</t>
         </is>
       </c>
-      <c r="AC10" s="3" t="inlineStr">
+      <c r="AC10" s="4" t="inlineStr">
         <is>
           <t>Individual</t>
         </is>
       </c>
-      <c r="AD10" s="3" t="inlineStr"/>
-      <c r="AE10" s="3" t="inlineStr"/>
-      <c r="AF10" s="3" t="inlineStr"/>
-      <c r="AG10" s="3" t="inlineStr">
+      <c r="AD10" s="4" t="inlineStr"/>
+      <c r="AE10" s="4" t="inlineStr"/>
+      <c r="AF10" s="4" t="inlineStr"/>
+      <c r="AG10" s="4" t="inlineStr">
         <is>
           <t>BOTSWANA</t>
         </is>
       </c>
-      <c r="AH10" s="3" t="inlineStr"/>
-      <c r="AI10" s="3" t="inlineStr">
+      <c r="AH10" s="4" t="inlineStr"/>
+      <c r="AI10" s="4" t="inlineStr">
         <is>
           <t>BIFM UNIT TRUSTS</t>
         </is>
       </c>
-      <c r="AJ10" s="3" t="inlineStr">
+      <c r="AJ10" s="4" t="inlineStr">
         <is>
           <t>NNELO TAUNYANE</t>
         </is>
       </c>
-      <c r="AK10" s="3" t="inlineStr"/>
-      <c r="AL10" s="3" t="inlineStr"/>
-      <c r="AM10" s="3" t="inlineStr"/>
-      <c r="AN10" s="3" t="b">
+      <c r="AK10" s="4" t="inlineStr"/>
+      <c r="AL10" s="4" t="inlineStr"/>
+      <c r="AM10" s="4" t="inlineStr"/>
+      <c r="AN10" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="AO10" s="3" t="inlineStr">
+      <c r="AO10" s="4" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
       </c>
-      <c r="AP10" s="3" t="b">
+      <c r="AP10" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="AQ10" s="3" t="b">
+      <c r="AQ10" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="AR10" s="3" t="b">
+      <c r="AR10" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="AS10" s="3" t="inlineStr"/>
-      <c r="AT10" s="3" t="inlineStr">
+      <c r="AS10" s="4" t="inlineStr"/>
+      <c r="AT10" s="4" t="inlineStr">
         <is>
           <t>INTERN</t>
         </is>
       </c>
-      <c r="AU10" s="3" t="inlineStr"/>
-      <c r="AV10" s="3" t="inlineStr">
+      <c r="AU10" s="4" t="inlineStr"/>
+      <c r="AV10" s="4" t="inlineStr">
         <is>
           <t>PLOT 1234 GABORONE</t>
         </is>
       </c>
-      <c r="AW10" s="3" t="inlineStr"/>
-      <c r="AX10" s="3" t="inlineStr"/>
-      <c r="AY10" s="3" t="inlineStr">
+      <c r="AW10" s="4" t="inlineStr"/>
+      <c r="AX10" s="4" t="inlineStr"/>
+      <c r="AY10" s="4" t="inlineStr">
         <is>
           <t>Salary</t>
         </is>
       </c>
-      <c r="AZ10" s="3" t="inlineStr"/>
-      <c r="BA10" s="3" t="inlineStr">
+      <c r="AZ10" s="4" t="inlineStr"/>
+      <c r="BA10" s="4" t="inlineStr">
         <is>
           <t>Ms</t>
         </is>
       </c>
-      <c r="BB10" s="3" t="inlineStr">
+      <c r="BB10" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2754,499 +2756,499 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>381234567</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>KYC - Nnelo Taunyane</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>KYC</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>gender</t>
         </is>
       </c>
-      <c r="E2" s="4" t="n"/>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Gender derivation not applicable for this ID type</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>381234567</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>KYC - Nnelo Taunyane</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>KYC</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>id_expiry_date</t>
         </is>
       </c>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="E3" s="4" t="n"/>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>WARNING</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>ID expiry date not captured</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>381234567</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>KYC - Nnelo Taunyane</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>KYC</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>date_of_birth</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>01/02/2003</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr"/>
+      <c r="G4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>381234567</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>KYC - Nnelo Taunyane</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>KYC</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>nnelo@bifm.co.bw</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>381234567</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>KYC - Nnelo Taunyane</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>KYC</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>contact_number</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>71234567</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>381234567</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>KYC - Nnelo Taunyane</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>KYC</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>branch_code</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>064967</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>381234567</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>KYC - Nnelo Taunyane</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>KYC</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>kyc_completeness_flag</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>381234321</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>GSGF - NNELO TAUNYANE</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>DIS_GSG</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>nnelo@bifm.co.bw</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>381234321</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>GSGF - NNELO TAUNYANE</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>DIS_GSG</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>contact_number</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>71234567</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr"/>
+      <c r="G10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>381234321</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>GSGF - NNELO TAUNYANE</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>DIS_GSG</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>branch_code</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>064967</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr"/>
+      <c r="G11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>381234321</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>GSGF - NNELO TAUNYANE</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>DIS_GSG</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>fund_category</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>Non-Money Market (GSGF)</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr"/>
+      <c r="G12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>381234321</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>GSGF - NNELO TAUNYANE</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>DIS_GSG</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>instruction_mode</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>Partial Withdrawal</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Full Closure</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr"/>
+      <c r="G13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>381234567</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>DIS - NNELO</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>DIS</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>nnelo@bifm.co.bw</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr"/>
+      <c r="G14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>381234567</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>DIS - NNELO</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>DIS</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>contact_number</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>71234567</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr"/>
+      <c r="G15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>381234567</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>DIS - NNELO</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>DIS</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>branch_code</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>064967</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr"/>
+      <c r="G16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -3276,179 +3278,175 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>Expected 8 or 9 digits, got 7</t>
-        </is>
-      </c>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>381234567</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>DIS - NNELO</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>DIS</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>fund_category</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>Money Market</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr"/>
+      <c r="G18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>381234567</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>DIS - NNELO</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>DIS</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>instruction_mode</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>Partial Withdrawal</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr"/>
+      <c r="G19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>381234567</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>DEBIT - NNELO</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>DEBIT</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>taunyane@bifm.co.bw</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr"/>
+      <c r="G20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>381234567</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>DEBIT - NNELO</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>DEBIT</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>contact_number</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>71234567</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr"/>
+      <c r="G21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>381234567</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>DEBIT - NNELO</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>DEBIT</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>branch_code</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>064967</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr"/>
+      <c r="G22" s="3" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -3478,146 +3476,142 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>Expected 8 or 9 digits, got 7</t>
-        </is>
-      </c>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>381234567</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>DEBIT - NNELO</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>DEBIT</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>fund_category</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>Money Market</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="F24" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr"/>
+      <c r="G24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>381234567</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>ADD - NNELO</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>ADD</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>nneelo@bifm.co.bw</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>nnelo@bifm.co.bw</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>381234567</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>ADD - NNELO</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>ADD</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>contact_number</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>71234567</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="F26" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G26" s="4" t="inlineStr"/>
+      <c r="G26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>381234567</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>ADD - NNELO</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>ADD</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>branch_code</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>064967</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G27" s="4" t="inlineStr"/>
+      <c r="G27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -3647,47 +3641,43 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>Expected 8 or 9 digits, got 7</t>
-        </is>
-      </c>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>381234567</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>ADD - NNELO</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>ADD</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>fund_category</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>Money Market</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr">
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G29" s="4" t="inlineStr"/>
+      <c r="G29" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3794,7 +3784,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:18:22</t>
+          <t>2026-07-02T17:26:48</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3804,7 +3794,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>KYC_381234567_TAUNYANE_20260702_1_2_3_4.pdf</t>
+          <t>KYC_381234567_TAUNYANE_20260702_1_2_3_4_5.pdf</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -3833,12 +3823,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:16:15</t>
+          <t>2026-07-02T17:24:42</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\02\NonMoneyMarket\Captured\KYC_381234567_TAUNYANE_20260702_1_2_3_4.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\02\NonMoneyMarket\Captured\KYC_381234567_TAUNYANE_20260702_1_2_3_4_5.pdf</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -3856,7 +3846,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-02T17:18:22</t>
+          <t>2026-07-02T17:26:48</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3866,7 +3856,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DIS_GSG_381234321_TAUNYANE_20260702.pdf</t>
+          <t>DIS_GSG_381234321_TAUNYANE_20260702_1.pdf</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -3895,12 +3885,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-07-02T17:16:15</t>
+          <t>2026-07-02T17:24:42</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\02\NonMoneyMarket\Captured\DIS_GSG_381234321_TAUNYANE_20260702.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\02\NonMoneyMarket\Captured\DIS_GSG_381234321_TAUNYANE_20260702_1.pdf</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -3918,7 +3908,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-02T17:18:22</t>
+          <t>2026-07-02T17:26:48</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3928,7 +3918,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DIS_381234567_TAUNYANE_20260702.pdf</t>
+          <t>DIS_381234567_TAUNYANE_20260702_1.pdf</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -3941,7 +3931,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>WARNING</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3957,12 +3947,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-07-02T17:16:15</t>
+          <t>2026-07-02T17:24:42</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\02\MoneyMarket\Captured\DIS_381234567_TAUNYANE_20260702.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\02\MoneyMarket\Captured\DIS_381234567_TAUNYANE_20260702_1.pdf</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -3980,7 +3970,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-02T17:18:22</t>
+          <t>2026-07-02T17:26:48</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3990,7 +3980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DEBIT_381234567_TAUNYANE_20260702.pdf</t>
+          <t>DEBIT_381234567_TAUNYANE_20260702_1.pdf</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -4003,7 +3993,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>WARNING</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -4019,12 +4009,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-07-02T17:16:15</t>
+          <t>2026-07-02T17:24:42</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\02\MoneyMarket\Captured\DEBIT_381234567_TAUNYANE_20260702.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\02\MoneyMarket\Captured\DEBIT_381234567_TAUNYANE_20260702_1.pdf</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -4042,7 +4032,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-02T17:18:22</t>
+          <t>2026-07-02T17:26:48</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -4052,7 +4042,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ADD_381234567_TAUNYANE_20260702.pdf</t>
+          <t>ADD_381234567_TAUNYANE_20260702_1.pdf</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -4065,7 +4055,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>WARNING</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -4081,12 +4071,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-07-02T17:16:15</t>
+          <t>2026-07-02T17:24:42</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\02\MoneyMarket\Captured\ADD_381234567_TAUNYANE_20260702.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\02\MoneyMarket\Captured\ADD_381234567_TAUNYANE_20260702_1.pdf</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">

--- a/output/BIFM_UT_Processing_Report.xlsx
+++ b/output/BIFM_UT_Processing_Report.xlsx
@@ -722,7 +722,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>98% confidence — majority vote: 4/5 documents agree on this value (differs on: DEBIT - NNELO) — value taken from KYC - Nnelo Taunyane</t>
+          <t>98% confidence — majority vote: 3/5 documents agree on this value (differs on: ADD - NNELO, DEBIT - NNELO) — value taken from KYC - Nnelo Taunyane</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="Q2" s="3" t="inlineStr">
         <is>
-          <t>2026-07-02T17:24:42</t>
+          <t>2026-07-03T09:50:59</t>
         </is>
       </c>
       <c r="R2" s="3" t="inlineStr">
@@ -1243,10 +1243,8 @@
       <c r="AE2" s="3" t="inlineStr"/>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
-      <c r="AH2" s="3" t="inlineStr">
-        <is>
-          <t>1000.00</t>
-        </is>
+      <c r="AH2" s="3" t="n">
+        <v>1000</v>
       </c>
       <c r="AI2" s="3" t="inlineStr"/>
       <c r="AJ2" s="3" t="inlineStr"/>
@@ -1482,7 +1480,7 @@
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>2026-07-02T17:24:42</t>
+          <t>2026-07-03T09:50:59</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
@@ -1537,7 +1535,7 @@
       </c>
       <c r="AF4" s="3" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>M 03 Y 2026</t>
         </is>
       </c>
       <c r="AG4" s="3" t="inlineStr"/>
@@ -1677,7 +1675,7 @@
       </c>
       <c r="AF5" s="2" t="inlineStr">
         <is>
-          <t>98% confidence — extracted from DEBIT - NNELO, p.2</t>
+          <t>80% confidence — extracted from DEBIT - NNELO, p.2 — ⚠ recommend recheck</t>
         </is>
       </c>
       <c r="AG5" s="2" t="inlineStr"/>
@@ -1784,7 +1782,7 @@
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>2026-07-02T17:24:42</t>
+          <t>2026-07-03T09:50:59</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
@@ -1800,7 +1798,7 @@
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t>nnelo@bifm.co.bw</t>
+          <t>nneelo@bifm.co.bw</t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr"/>
@@ -2074,7 +2072,7 @@
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>2026-07-02T17:24:42</t>
+          <t>2026-07-03T09:50:59</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
@@ -2350,7 +2348,7 @@
       </c>
       <c r="Q10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02T17:24:42</t>
+          <t>2026-07-03T09:50:58</t>
         </is>
       </c>
       <c r="R10" s="4" t="inlineStr">
@@ -3537,7 +3535,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>nnelo@bifm.co.bw</t>
+          <t>nneelo@bifm.co.bw</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -3695,7 +3693,7 @@
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="41" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="27" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
@@ -3784,7 +3782,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:26:48</t>
+          <t>2026-07-03T09:58:44</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3794,7 +3792,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>KYC_381234567_TAUNYANE_20260702_1_2_3_4_5.pdf</t>
+          <t>KYC_381234567_TAUNYANE_20260703.pdf</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -3823,12 +3821,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:24:42</t>
+          <t>2026-07-03T09:50:58</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\02\NonMoneyMarket\Captured\KYC_381234567_TAUNYANE_20260702_1_2_3_4_5.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\03\NonMoneyMarket\Captured\KYC_381234567_TAUNYANE_20260703.pdf</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -3846,7 +3844,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-02T17:26:48</t>
+          <t>2026-07-03T09:58:44</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3856,7 +3854,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DIS_GSG_381234321_TAUNYANE_20260702_1.pdf</t>
+          <t>DIS_GSG_381234321_TAUNYANE_20260703.pdf</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -3885,12 +3883,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-07-02T17:24:42</t>
+          <t>2026-07-03T09:50:59</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\02\NonMoneyMarket\Captured\DIS_GSG_381234321_TAUNYANE_20260702_1.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\03\NonMoneyMarket\Captured\DIS_GSG_381234321_TAUNYANE_20260703.pdf</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -3908,7 +3906,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-02T17:26:48</t>
+          <t>2026-07-03T09:58:44</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3918,7 +3916,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DIS_381234567_TAUNYANE_20260702_1.pdf</t>
+          <t>DIS_381234567_TAUNYANE_20260703.pdf</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -3947,12 +3945,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-07-02T17:24:42</t>
+          <t>2026-07-03T09:50:59</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\02\MoneyMarket\Captured\DIS_381234567_TAUNYANE_20260702_1.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\03\MoneyMarket\Captured\DIS_381234567_TAUNYANE_20260703.pdf</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -3970,7 +3968,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-02T17:26:48</t>
+          <t>2026-07-03T09:58:44</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3980,7 +3978,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DEBIT_381234567_TAUNYANE_20260702_1.pdf</t>
+          <t>DEBIT_381234567_TAUNYANE_20260703.pdf</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -4009,12 +4007,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-07-02T17:24:42</t>
+          <t>2026-07-03T09:50:59</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\02\MoneyMarket\Captured\DEBIT_381234567_TAUNYANE_20260702_1.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\03\MoneyMarket\Captured\DEBIT_381234567_TAUNYANE_20260703.pdf</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -4032,7 +4030,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-02T17:26:48</t>
+          <t>2026-07-03T09:58:44</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -4042,7 +4040,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ADD_381234567_TAUNYANE_20260702_1.pdf</t>
+          <t>ADD_381234567_TAUNYANE_20260703.pdf</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -4071,12 +4069,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-07-02T17:24:42</t>
+          <t>2026-07-03T09:50:59</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\02\MoneyMarket\Captured\ADD_381234567_TAUNYANE_20260702_1.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\03\MoneyMarket\Captured\ADD_381234567_TAUNYANE_20260703.pdf</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">

--- a/output/BIFM_UT_Processing_Report.xlsx
+++ b/output/BIFM_UT_Processing_Report.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>NNELO TAUNYANE</t>
+          <t>NNelo Taunyane</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="Q2" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03T09:50:59</t>
+          <t>2026-07-03T12:13:00</t>
         </is>
       </c>
       <c r="R2" s="3" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="Y2" s="3" t="inlineStr">
         <is>
-          <t>9066001231243</t>
+          <t>906001231243</t>
         </is>
       </c>
       <c r="Z2" s="3" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03T09:50:59</t>
+          <t>2026-07-03T12:13:00</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03T09:50:59</t>
+          <t>2026-07-03T12:13:00</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t>nneelo@bifm.co.bw</t>
+          <t>nneio@bifm.co.bw</t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr"/>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>98% confidence — extracted from ADD - NNELO, p.2</t>
+          <t>90% confidence — extracted from ADD - NNELO, p.2</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr"/>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03T09:50:59</t>
+          <t>2026-07-03T12:13:00</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>NNELO TAUNYANE</t>
+          <t>NNelo Taunyane</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="Q10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-03T09:50:58</t>
+          <t>2026-07-03T12:13:00</t>
         </is>
       </c>
       <c r="R10" s="4" t="inlineStr">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>nneelo@bifm.co.bw</t>
+          <t>nneio@bifm.co.bw</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -3693,7 +3693,7 @@
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="43" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="27" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
@@ -3782,7 +3782,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-03T09:58:44</t>
+          <t>2026-07-03T12:15:08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3792,7 +3792,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>KYC_381234567_TAUNYANE_20260703.pdf</t>
+          <t>KYC_381234567_TAUNYANE_20260703_1.pdf</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-03T09:50:58</t>
+          <t>2026-07-03T12:13:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\03\NonMoneyMarket\Captured\KYC_381234567_TAUNYANE_20260703.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\03\NonMoneyMarket\Captured\KYC_381234567_TAUNYANE_20260703_1.pdf</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -3844,7 +3844,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-03T09:58:44</t>
+          <t>2026-07-03T12:15:08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DIS_GSG_381234321_TAUNYANE_20260703.pdf</t>
+          <t>DIS_GSG_381234321_TAUNYANE_20260703_1.pdf</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-07-03T09:50:59</t>
+          <t>2026-07-03T12:13:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\03\NonMoneyMarket\Captured\DIS_GSG_381234321_TAUNYANE_20260703.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\03\NonMoneyMarket\Captured\DIS_GSG_381234321_TAUNYANE_20260703_1.pdf</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -3906,7 +3906,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-03T09:58:44</t>
+          <t>2026-07-03T12:15:08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DIS_381234567_TAUNYANE_20260703.pdf</t>
+          <t>DIS_381234567_TAUNYANE_20260703_1.pdf</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-07-03T09:50:59</t>
+          <t>2026-07-03T12:13:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\03\MoneyMarket\Captured\DIS_381234567_TAUNYANE_20260703.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\03\MoneyMarket\Captured\DIS_381234567_TAUNYANE_20260703_1.pdf</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -3968,7 +3968,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-03T09:58:44</t>
+          <t>2026-07-03T12:15:08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DEBIT_381234567_TAUNYANE_20260703.pdf</t>
+          <t>DEBIT_381234567_TAUNYANE_20260703_1.pdf</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-07-03T09:50:59</t>
+          <t>2026-07-03T12:13:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\03\MoneyMarket\Captured\DEBIT_381234567_TAUNYANE_20260703.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\03\MoneyMarket\Captured\DEBIT_381234567_TAUNYANE_20260703_1.pdf</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -4030,7 +4030,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-03T09:58:44</t>
+          <t>2026-07-03T12:15:08</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ADD_381234567_TAUNYANE_20260703.pdf</t>
+          <t>ADD_381234567_TAUNYANE_20260703_1.pdf</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-07-03T09:50:59</t>
+          <t>2026-07-03T12:13:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\03\MoneyMarket\Captured\ADD_381234567_TAUNYANE_20260703.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\2026\07-July\03\MoneyMarket\Captured\ADD_381234567_TAUNYANE_20260703_1.pdf</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">

--- a/output/BIFM_UT_Processing_Report.xlsx
+++ b/output/BIFM_UT_Processing_Report.xlsx
@@ -57,14 +57,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-        <bgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:V2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -466,7 +466,7 @@
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
@@ -476,12 +476,13 @@
     <col width="26" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="37" customWidth="1" min="15" max="15"/>
-    <col width="19" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="16" customWidth="1" min="18" max="18"/>
-    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="19" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
     <col width="13" customWidth="1" min="20" max="20"/>
-    <col width="22" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="22" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -562,30 +563,35 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>fund_number</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>bank_account_name</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>bank_name</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>account_number</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>branch_name</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>branch_code</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>account_type_banking</t>
         </is>
@@ -617,7 +623,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ONALENYA LORATO BOGOSING</t>
+          <t>Onalenna Bogosing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -667,30 +673,35 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Onalenya Bogosiny</t>
+          <t>1674982</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
+          <t>Onalenna Bogosing</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
           <t>ABSA</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>1078631</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>MALL</t>
-        </is>
-      </c>
       <c r="T2" t="inlineStr">
         <is>
+          <t>Maun</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
           <t>290167</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Current</t>
         </is>
@@ -707,7 +718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO6"/>
+  <dimension ref="A1:BD6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -718,39 +729,54 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="37" customWidth="1" min="8" max="8"/>
-    <col width="35" customWidth="1" min="9" max="9"/>
-    <col width="42" customWidth="1" min="10" max="10"/>
-    <col width="27" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="45" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="21" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="35" customWidth="1" min="10" max="10"/>
+    <col width="42" customWidth="1" min="11" max="11"/>
+    <col width="27" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
     <col width="21" customWidth="1" min="16" max="16"/>
-    <col width="15" customWidth="1" min="17" max="17"/>
-    <col width="16" customWidth="1" min="18" max="18"/>
-    <col width="22" customWidth="1" min="19" max="19"/>
-    <col width="13" customWidth="1" min="20" max="20"/>
-    <col width="18" customWidth="1" min="21" max="21"/>
-    <col width="16" customWidth="1" min="22" max="22"/>
-    <col width="22" customWidth="1" min="23" max="23"/>
-    <col width="19" customWidth="1" min="24" max="24"/>
-    <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="13" customWidth="1" min="26" max="26"/>
-    <col width="13" customWidth="1" min="27" max="27"/>
-    <col width="18" customWidth="1" min="28" max="28"/>
-    <col width="20" customWidth="1" min="29" max="29"/>
-    <col width="19" customWidth="1" min="30" max="30"/>
-    <col width="16" customWidth="1" min="31" max="31"/>
+    <col width="21" customWidth="1" min="17" max="17"/>
+    <col width="15" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
+    <col width="23" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="18" customWidth="1" min="22" max="22"/>
+    <col width="17" customWidth="1" min="23" max="23"/>
+    <col width="16" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="25" max="25"/>
+    <col width="19" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="13" customWidth="1" min="28" max="28"/>
+    <col width="13" customWidth="1" min="29" max="29"/>
+    <col width="15" customWidth="1" min="30" max="30"/>
+    <col width="19" customWidth="1" min="31" max="31"/>
     <col width="18" customWidth="1" min="32" max="32"/>
-    <col width="18" customWidth="1" min="33" max="33"/>
-    <col width="23" customWidth="1" min="34" max="34"/>
+    <col width="22" customWidth="1" min="33" max="33"/>
+    <col width="20" customWidth="1" min="34" max="34"/>
     <col width="19" customWidth="1" min="35" max="35"/>
-    <col width="19" customWidth="1" min="36" max="36"/>
-    <col width="18" customWidth="1" min="37" max="37"/>
-    <col width="12" customWidth="1" min="38" max="38"/>
-    <col width="26" customWidth="1" min="39" max="39"/>
-    <col width="18" customWidth="1" min="40" max="40"/>
-    <col width="12" customWidth="1" min="41" max="41"/>
+    <col width="17" customWidth="1" min="36" max="36"/>
+    <col width="24" customWidth="1" min="37" max="37"/>
+    <col width="16" customWidth="1" min="38" max="38"/>
+    <col width="21" customWidth="1" min="39" max="39"/>
+    <col width="20" customWidth="1" min="40" max="40"/>
+    <col width="29" customWidth="1" min="41" max="41"/>
+    <col width="18" customWidth="1" min="42" max="42"/>
+    <col width="23" customWidth="1" min="43" max="43"/>
+    <col width="19" customWidth="1" min="44" max="44"/>
+    <col width="19" customWidth="1" min="45" max="45"/>
+    <col width="18" customWidth="1" min="46" max="46"/>
+    <col width="23" customWidth="1" min="47" max="47"/>
+    <col width="25" customWidth="1" min="48" max="48"/>
+    <col width="12" customWidth="1" min="49" max="49"/>
+    <col width="25" customWidth="1" min="50" max="50"/>
+    <col width="26" customWidth="1" min="51" max="51"/>
+    <col width="24" customWidth="1" min="52" max="52"/>
+    <col width="17" customWidth="1" min="53" max="53"/>
+    <col width="18" customWidth="1" min="54" max="54"/>
+    <col width="22" customWidth="1" min="55" max="55"/>
+    <col width="12" customWidth="1" min="56" max="56"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -796,165 +822,240 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>fund_number</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>fund_category</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>processing_cutoff</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>overall_validation_status</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>instruction_status</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>rejection_reason</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>channel</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>upload_date</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>captured_by</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>authorized_by</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>contact_number</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>citizenship</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>account_category</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>account_closure</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>account_number</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>account_type_banking</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>bank_account_name</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>bank_name</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>branch_code</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>branch_name</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>change_amount</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>commencement_date</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>country_of_birth</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>disinvestment_amount</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>employer</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>entity_name</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>escalation_rate</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>fund_category_priority</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>id_expiry_date</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>income_distribution</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>instruction_mode</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>instruction_type</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>kyc_certified_id</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>kyc_completeness_flag</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>kyc_proof_address</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>kyc_proof_banking</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>kyc_proof_source</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>lump_sum_debit_amount</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>lump_sum_deposit_amount</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>occupation</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>payment_method</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>residential_address</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>source_of_contribution</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>source_of_funds</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>source_of_income</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>sub_instruction_type</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>us_ssn</t>
         </is>
@@ -999,141 +1100,156 @@
       <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>Rejected</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>Validation failed: id_expiry_date</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-07T17:58:29</t>
-        </is>
-      </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
+          <t>2026-07-08T10:33:03</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
           <t>marvel.ai-local-poc</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr">
+      <c r="R2" s="2" t="inlineStr"/>
+      <c r="S2" s="2" t="inlineStr">
         <is>
           <t>76749303</t>
         </is>
       </c>
-      <c r="S2" s="2" t="inlineStr">
+      <c r="T2" s="2" t="inlineStr">
         <is>
           <t>obogosinge@gmail.com</t>
         </is>
       </c>
-      <c r="T2" s="2" t="inlineStr">
+      <c r="U2" s="2" t="inlineStr">
         <is>
           <t>MOTSWANA</t>
         </is>
       </c>
-      <c r="U2" s="2" t="inlineStr">
+      <c r="V2" s="2" t="inlineStr">
         <is>
           <t>Joint Signature</t>
         </is>
       </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="W2" s="2" t="inlineStr"/>
+      <c r="X2" s="2" t="inlineStr">
         <is>
           <t>1078631</t>
         </is>
       </c>
-      <c r="W2" s="2" t="inlineStr">
+      <c r="Y2" s="2" t="inlineStr">
         <is>
           <t>Current</t>
         </is>
       </c>
-      <c r="X2" s="2" t="inlineStr">
+      <c r="Z2" s="2" t="inlineStr">
         <is>
           <t>Onalenya Bogosiny</t>
         </is>
       </c>
-      <c r="Y2" s="2" t="inlineStr">
+      <c r="AA2" s="2" t="inlineStr">
         <is>
           <t>ABSA</t>
         </is>
       </c>
-      <c r="Z2" s="2" t="inlineStr">
+      <c r="AB2" s="2" t="inlineStr">
         <is>
           <t>290167</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
+      <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>MALL</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
+      <c r="AD2" s="2" t="inlineStr"/>
+      <c r="AE2" s="2" t="inlineStr"/>
+      <c r="AF2" s="2" t="inlineStr">
         <is>
           <t>BOTSWANA</t>
         </is>
       </c>
-      <c r="AC2" s="2" t="inlineStr">
+      <c r="AG2" s="2" t="inlineStr"/>
+      <c r="AH2" s="2" t="inlineStr">
         <is>
           <t>THE UNITED NATIONS</t>
         </is>
       </c>
-      <c r="AD2" s="2" t="inlineStr">
+      <c r="AI2" s="2" t="inlineStr">
         <is>
           <t>ONALENYA BOGOSING</t>
         </is>
       </c>
-      <c r="AE2" s="2" t="inlineStr">
+      <c r="AJ2" s="2" t="inlineStr"/>
+      <c r="AK2" s="2" t="inlineStr"/>
+      <c r="AL2" s="2" t="inlineStr">
         <is>
           <t>11/02/2026</t>
         </is>
       </c>
-      <c r="AF2" s="2" t="inlineStr"/>
-      <c r="AG2" s="2" t="b">
+      <c r="AM2" s="2" t="inlineStr"/>
+      <c r="AN2" s="2" t="inlineStr"/>
+      <c r="AO2" s="2" t="inlineStr"/>
+      <c r="AP2" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AH2" s="2" t="inlineStr">
+      <c r="AQ2" s="2" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
       </c>
-      <c r="AI2" s="2" t="b">
+      <c r="AR2" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AJ2" s="2" t="b">
+      <c r="AS2" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AK2" s="2" t="b">
+      <c r="AT2" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AL2" s="2" t="inlineStr">
+      <c r="AU2" s="2" t="inlineStr"/>
+      <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" s="2" t="inlineStr">
         <is>
           <t>DIPLOMAT</t>
         </is>
       </c>
-      <c r="AM2" s="2" t="inlineStr">
+      <c r="AX2" s="2" t="inlineStr"/>
+      <c r="AY2" s="2" t="inlineStr">
         <is>
           <t>PLOT 40353, BLOCKS  GABS</t>
         </is>
       </c>
-      <c r="AN2" s="2" t="inlineStr">
+      <c r="AZ2" s="2" t="inlineStr"/>
+      <c r="BA2" s="2" t="inlineStr"/>
+      <c r="BB2" s="2" t="inlineStr">
         <is>
           <t>Salary</t>
         </is>
       </c>
-      <c r="AO2" s="2" t="inlineStr">
+      <c r="BC2" s="2" t="inlineStr"/>
+      <c r="BD2" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1157,17 +1273,17 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>38344272</t>
+          <t>388144272</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>ONALENYA LORATO BOGOSING</t>
+          <t>Onalenna Bogosing</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>224922314</t>
+          <t>224922316</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
@@ -1176,238 +1292,284 @@
           <t>BIFM Global Sustainable Growth Fund</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>Non-Money Market (GSGF)</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>Quarterly - 7th of last month of quarter</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
           <t>Captured</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr"/>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr"/>
+      <c r="O3" s="3" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-07T17:58:29</t>
-        </is>
-      </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
+          <t>2026-07-08T10:33:03</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr">
+        <is>
           <t>marvel.ai-local-poc</t>
         </is>
       </c>
-      <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr">
-        <is>
-          <t>76749303</t>
-        </is>
-      </c>
+      <c r="R3" s="3" t="inlineStr"/>
       <c r="S3" s="3" t="inlineStr">
         <is>
-          <t>obogosinge@gmail.com</t>
-        </is>
-      </c>
-      <c r="T3" s="3" t="inlineStr"/>
+          <t>26749363</t>
+        </is>
+      </c>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>bogosing@gmail.com</t>
+        </is>
+      </c>
       <c r="U3" s="3" t="inlineStr"/>
-      <c r="V3" s="3" t="inlineStr">
-        <is>
-          <t>1078631</t>
-        </is>
-      </c>
-      <c r="W3" s="3" t="inlineStr">
+      <c r="V3" s="3" t="inlineStr"/>
+      <c r="W3" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>4072341</t>
+        </is>
+      </c>
+      <c r="Y3" s="3" t="inlineStr">
         <is>
           <t>Current</t>
         </is>
       </c>
-      <c r="X3" s="3" t="inlineStr">
-        <is>
-          <t>Onalenya Bogosiny</t>
-        </is>
-      </c>
-      <c r="Y3" s="3" t="inlineStr">
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>Onalenna Bogosing</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr">
         <is>
           <t>ABSA</t>
         </is>
       </c>
-      <c r="Z3" s="3" t="inlineStr">
+      <c r="AB3" s="3" t="inlineStr">
         <is>
           <t>290167</t>
         </is>
       </c>
-      <c r="AA3" s="3" t="inlineStr">
-        <is>
-          <t>MALL</t>
-        </is>
-      </c>
-      <c r="AB3" s="3" t="inlineStr"/>
-      <c r="AC3" s="3" t="inlineStr"/>
+      <c r="AC3" s="3" t="inlineStr">
+        <is>
+          <t>Maun</t>
+        </is>
+      </c>
       <c r="AD3" s="3" t="inlineStr"/>
       <c r="AE3" s="3" t="inlineStr"/>
-      <c r="AF3" s="3" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="AG3" s="3" t="inlineStr"/>
+      <c r="AF3" s="3" t="inlineStr"/>
+      <c r="AG3" s="3" t="n">
+        <v>40000</v>
+      </c>
       <c r="AH3" s="3" t="inlineStr"/>
       <c r="AI3" s="3" t="inlineStr"/>
       <c r="AJ3" s="3" t="inlineStr"/>
-      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="n">
+        <v>3</v>
+      </c>
       <c r="AL3" s="3" t="inlineStr"/>
       <c r="AM3" s="3" t="inlineStr"/>
-      <c r="AN3" s="3" t="inlineStr"/>
+      <c r="AN3" s="3" t="inlineStr">
+        <is>
+          <t>Partial Withdrawal</t>
+        </is>
+      </c>
       <c r="AO3" s="3" t="inlineStr"/>
+      <c r="AP3" s="3" t="inlineStr"/>
+      <c r="AQ3" s="3" t="inlineStr"/>
+      <c r="AR3" s="3" t="inlineStr"/>
+      <c r="AS3" s="3" t="inlineStr"/>
+      <c r="AT3" s="3" t="inlineStr"/>
+      <c r="AU3" s="3" t="inlineStr"/>
+      <c r="AV3" s="3" t="inlineStr"/>
+      <c r="AW3" s="3" t="inlineStr"/>
+      <c r="AX3" s="3" t="inlineStr"/>
+      <c r="AY3" s="3" t="inlineStr"/>
+      <c r="AZ3" s="3" t="inlineStr"/>
+      <c r="BA3" s="3" t="inlineStr"/>
+      <c r="BB3" s="3" t="inlineStr"/>
+      <c r="BC3" s="3" t="inlineStr"/>
+      <c r="BD3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>DIS - ONALENNA BOGOSING</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>DIS</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>Disinvestment Form (Standard)</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>ONALENYA LORATO BOGOSING</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>224922314</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr"/>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>3831 44272</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Onalenna Bogosing</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>222922316</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>BIFM Global Sustainable Growth Fund</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>1674982</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>Unknown - Fund Name Not Extracted</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr">
         <is>
           <t>WARNING</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="M4" s="4" t="inlineStr">
         <is>
           <t>Captured</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr"/>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="N4" s="4" t="inlineStr"/>
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-07T17:58:29</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="inlineStr">
+      <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-08T10:33:03</t>
+        </is>
+      </c>
+      <c r="Q4" s="4" t="inlineStr">
         <is>
           <t>marvel.ai-local-poc</t>
         </is>
       </c>
-      <c r="Q4" s="3" t="inlineStr"/>
-      <c r="R4" s="3" t="inlineStr">
+      <c r="R4" s="4" t="inlineStr"/>
+      <c r="S4" s="4" t="inlineStr">
         <is>
           <t>76749303</t>
         </is>
       </c>
-      <c r="S4" s="3" t="inlineStr">
+      <c r="T4" s="4" t="inlineStr">
         <is>
           <t>obogosinge@gmail.com</t>
         </is>
       </c>
-      <c r="T4" s="3" t="inlineStr"/>
-      <c r="U4" s="3" t="inlineStr"/>
-      <c r="V4" s="3" t="inlineStr">
-        <is>
-          <t>1078631</t>
-        </is>
-      </c>
-      <c r="W4" s="3" t="inlineStr">
+      <c r="U4" s="4" t="inlineStr"/>
+      <c r="V4" s="4" t="inlineStr"/>
+      <c r="W4" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="X4" s="4" t="inlineStr">
+        <is>
+          <t>1033921</t>
+        </is>
+      </c>
+      <c r="Y4" s="4" t="inlineStr">
         <is>
           <t>Current</t>
         </is>
       </c>
-      <c r="X4" s="3" t="inlineStr">
-        <is>
-          <t>Onalenya Bogosiny</t>
-        </is>
-      </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>ABSA</t>
-        </is>
-      </c>
-      <c r="Z4" s="3" t="inlineStr">
+      <c r="Z4" s="4" t="inlineStr">
+        <is>
+          <t>Onalenna Bogosing</t>
+        </is>
+      </c>
+      <c r="AA4" s="4" t="inlineStr">
+        <is>
+          <t>NBSA</t>
+        </is>
+      </c>
+      <c r="AB4" s="4" t="inlineStr">
         <is>
           <t>290167</t>
         </is>
       </c>
-      <c r="AA4" s="3" t="inlineStr">
-        <is>
-          <t>MALL</t>
-        </is>
-      </c>
-      <c r="AB4" s="3" t="inlineStr"/>
-      <c r="AC4" s="3" t="inlineStr"/>
-      <c r="AD4" s="3" t="inlineStr"/>
-      <c r="AE4" s="3" t="inlineStr"/>
-      <c r="AF4" s="3" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="AG4" s="3" t="inlineStr"/>
-      <c r="AH4" s="3" t="inlineStr"/>
-      <c r="AI4" s="3" t="inlineStr"/>
-      <c r="AJ4" s="3" t="inlineStr"/>
-      <c r="AK4" s="3" t="inlineStr"/>
-      <c r="AL4" s="3" t="inlineStr"/>
-      <c r="AM4" s="3" t="inlineStr"/>
-      <c r="AN4" s="3" t="inlineStr"/>
-      <c r="AO4" s="3" t="inlineStr"/>
+      <c r="AC4" s="4" t="inlineStr">
+        <is>
+          <t>Maun</t>
+        </is>
+      </c>
+      <c r="AD4" s="4" t="inlineStr"/>
+      <c r="AE4" s="4" t="inlineStr"/>
+      <c r="AF4" s="4" t="inlineStr"/>
+      <c r="AG4" s="4" t="n">
+        <v>200000</v>
+      </c>
+      <c r="AH4" s="4" t="inlineStr"/>
+      <c r="AI4" s="4" t="inlineStr"/>
+      <c r="AJ4" s="4" t="inlineStr"/>
+      <c r="AK4" s="4" t="n">
+        <v>99</v>
+      </c>
+      <c r="AL4" s="4" t="inlineStr"/>
+      <c r="AM4" s="4" t="inlineStr"/>
+      <c r="AN4" s="4" t="inlineStr">
+        <is>
+          <t>Partial Withdrawal</t>
+        </is>
+      </c>
+      <c r="AO4" s="4" t="inlineStr"/>
+      <c r="AP4" s="4" t="inlineStr"/>
+      <c r="AQ4" s="4" t="inlineStr"/>
+      <c r="AR4" s="4" t="inlineStr"/>
+      <c r="AS4" s="4" t="inlineStr"/>
+      <c r="AT4" s="4" t="inlineStr"/>
+      <c r="AU4" s="4" t="inlineStr"/>
+      <c r="AV4" s="4" t="inlineStr"/>
+      <c r="AW4" s="4" t="inlineStr"/>
+      <c r="AX4" s="4" t="inlineStr"/>
+      <c r="AY4" s="4" t="inlineStr"/>
+      <c r="AZ4" s="4" t="inlineStr"/>
+      <c r="BA4" s="4" t="inlineStr"/>
+      <c r="BB4" s="4" t="inlineStr"/>
+      <c r="BC4" s="4" t="inlineStr"/>
+      <c r="BD4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1427,17 +1589,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>38344272</t>
+          <t>363144272</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>ONALENYA LORATO BOGOSING</t>
+          <t>Onalenna Bogosing</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>224922314</t>
+          <t>2249223M</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr"/>
@@ -1448,236 +1610,314 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>164914</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>Unknown - Fund Name Not Extracted</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>Rejected</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>Validation failed: instruction_type, id_expiry_date</t>
-        </is>
-      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
+          <t>Validation failed: id_expiry_date</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-07T17:58:29</t>
-        </is>
-      </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
+          <t>2026-07-08T10:33:03</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
           <t>marvel.ai-local-poc</t>
         </is>
       </c>
-      <c r="Q5" s="2" t="inlineStr"/>
-      <c r="R5" s="2" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr"/>
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>76749303</t>
         </is>
       </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>obogosinge@gmail.com</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>obagosing@gmail.com</t>
+        </is>
+      </c>
       <c r="U5" s="2" t="inlineStr"/>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr"/>
+      <c r="W5" s="2" t="inlineStr"/>
+      <c r="X5" s="2" t="inlineStr">
         <is>
           <t>1078631</t>
         </is>
       </c>
-      <c r="W5" s="2" t="inlineStr">
+      <c r="Y5" s="2" t="inlineStr">
         <is>
           <t>Current</t>
         </is>
       </c>
-      <c r="X5" s="2" t="inlineStr">
-        <is>
-          <t>Onalenya Bogosiny</t>
-        </is>
-      </c>
-      <c r="Y5" s="2" t="inlineStr">
+      <c r="Z5" s="2" t="inlineStr">
+        <is>
+          <t>Onalenna Bogosing</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
         <is>
           <t>ABSA</t>
         </is>
       </c>
-      <c r="Z5" s="2" t="inlineStr">
+      <c r="AB5" s="2" t="inlineStr">
         <is>
           <t>290167</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>MALL</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
-      <c r="AC5" s="2" t="inlineStr"/>
-      <c r="AD5" s="2" t="inlineStr"/>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>Maun</t>
+        </is>
+      </c>
+      <c r="AD5" s="2" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
       <c r="AE5" s="2" t="inlineStr">
         <is>
-          <t>11/02/2026</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="AF5" s="2" t="inlineStr"/>
       <c r="AG5" s="2" t="inlineStr"/>
       <c r="AH5" s="2" t="inlineStr"/>
       <c r="AI5" s="2" t="inlineStr"/>
-      <c r="AJ5" s="2" t="inlineStr"/>
-      <c r="AK5" s="2" t="inlineStr"/>
-      <c r="AL5" s="2" t="inlineStr"/>
+      <c r="AJ5" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="AK5" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="AL5" s="2" t="inlineStr">
+        <is>
+          <t>02/11/2016</t>
+        </is>
+      </c>
       <c r="AM5" s="2" t="inlineStr"/>
       <c r="AN5" s="2" t="inlineStr"/>
-      <c r="AO5" s="2" t="inlineStr"/>
+      <c r="AO5" s="2" t="inlineStr">
+        <is>
+          <t>Change existing debit order</t>
+        </is>
+      </c>
+      <c r="AP5" s="2" t="inlineStr"/>
+      <c r="AQ5" s="2" t="inlineStr"/>
+      <c r="AR5" s="2" t="inlineStr"/>
+      <c r="AS5" s="2" t="inlineStr"/>
+      <c r="AT5" s="2" t="inlineStr"/>
+      <c r="AU5" s="2" t="inlineStr"/>
+      <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" s="2" t="inlineStr"/>
+      <c r="AX5" s="2" t="inlineStr"/>
+      <c r="AY5" s="2" t="inlineStr"/>
+      <c r="AZ5" s="2" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="BA5" s="2" t="inlineStr"/>
+      <c r="BB5" s="2" t="inlineStr"/>
+      <c r="BC5" s="2" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="BD5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>ADD - ONALENNA</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>ADD</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Additional Investment Form</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>ONALENYA LORATO BOGOSING</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>BIFM Global Sustainable Growth Fund</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>Unknown - Fund Name Not Extracted</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>Rejected</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>Validation failed: fund_number</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>383144272</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Onalenna Boitshware</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Bifm Pula Money Market Fund</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>1673412</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>Money Market</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>1:00 PM</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>Captured</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr"/>
+      <c r="O6" s="3" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-07T17:58:29</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-08T10:33:03</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr">
         <is>
           <t>marvel.ai-local-poc</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr">
+      <c r="R6" s="3" t="inlineStr"/>
+      <c r="S6" s="3" t="inlineStr">
         <is>
           <t>76749303</t>
         </is>
       </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>obogosinge@gmail.com</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr"/>
-      <c r="U6" s="2" t="inlineStr"/>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="T6" s="3" t="inlineStr">
+        <is>
+          <t>oboitshware@gmail.com</t>
+        </is>
+      </c>
+      <c r="U6" s="3" t="inlineStr"/>
+      <c r="V6" s="3" t="inlineStr"/>
+      <c r="W6" s="3" t="inlineStr"/>
+      <c r="X6" s="3" t="inlineStr">
         <is>
           <t>1078631</t>
         </is>
       </c>
-      <c r="W6" s="2" t="inlineStr">
+      <c r="Y6" s="3" t="inlineStr">
         <is>
           <t>Current</t>
         </is>
       </c>
-      <c r="X6" s="2" t="inlineStr">
-        <is>
-          <t>Onalenya Bogosiny</t>
-        </is>
-      </c>
-      <c r="Y6" s="2" t="inlineStr">
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>Onalenna Bogosing</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
         <is>
           <t>ABSA</t>
         </is>
       </c>
-      <c r="Z6" s="2" t="inlineStr">
+      <c r="AB6" s="3" t="inlineStr">
         <is>
           <t>290167</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>MALL</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
-      <c r="AC6" s="2" t="inlineStr"/>
-      <c r="AD6" s="2" t="inlineStr"/>
-      <c r="AE6" s="2" t="inlineStr"/>
-      <c r="AF6" s="2" t="inlineStr"/>
-      <c r="AG6" s="2" t="inlineStr"/>
-      <c r="AH6" s="2" t="inlineStr"/>
-      <c r="AI6" s="2" t="inlineStr"/>
-      <c r="AJ6" s="2" t="inlineStr"/>
-      <c r="AK6" s="2" t="inlineStr"/>
-      <c r="AL6" s="2" t="inlineStr"/>
-      <c r="AM6" s="2" t="inlineStr"/>
-      <c r="AN6" s="2" t="inlineStr"/>
-      <c r="AO6" s="2" t="inlineStr"/>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>Maun</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr"/>
+      <c r="AE6" s="3" t="inlineStr"/>
+      <c r="AF6" s="3" t="inlineStr"/>
+      <c r="AG6" s="3" t="inlineStr"/>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr"/>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL6" s="3" t="inlineStr"/>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>Reinvest</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr"/>
+      <c r="AP6" s="3" t="inlineStr"/>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr"/>
+      <c r="AS6" s="3" t="inlineStr"/>
+      <c r="AT6" s="3" t="inlineStr"/>
+      <c r="AU6" s="3" t="n">
+        <v>100000</v>
+      </c>
+      <c r="AV6" s="3" t="n">
+        <v>280000</v>
+      </c>
+      <c r="AW6" s="3" t="inlineStr"/>
+      <c r="AX6" s="3" t="inlineStr">
+        <is>
+          <t>Investor's bank account</t>
+        </is>
+      </c>
+      <c r="AY6" s="3" t="inlineStr"/>
+      <c r="AZ6" s="3" t="inlineStr"/>
+      <c r="BA6" s="3" t="inlineStr">
+        <is>
+          <t>Salary</t>
+        </is>
+      </c>
+      <c r="BB6" s="3" t="inlineStr"/>
+      <c r="BC6" s="3" t="inlineStr"/>
+      <c r="BD6" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1738,7 +1978,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1805,264 +2045,260 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>id_number</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>224922314</t>
-        </is>
-      </c>
+          <t>gender</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="n"/>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>WARNING</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>Unknown ID type 'None' - cannot apply digit validation</t>
+          <t>Gender derivation not applicable for this ID type</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>38344272</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>KYC - ONALENNA</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>KYC</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>gender</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="n"/>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>id_expiry_date</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>11/02/2026</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>ID expiry date is not in the future</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>38344272</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>KYC - ONALENNA</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>KYC</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>date_of_birth</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>16/11/1993</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>Gender derivation not applicable for this ID type</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>38344272</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>KYC - ONALENNA</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>KYC</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>id_expiry_date</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>11/02/2026</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>ID expiry date is not in the future</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>obogosinge@gmail.com</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>38344272</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>KYC - ONALENNA</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>KYC</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>date_of_birth</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>16/11/1993</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>contact_number</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>76749303</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>38344272</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>KYC - ONALENNA</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>KYC</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>branch_code</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>290167</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>38344272</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>KYC - ONALENNA</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>KYC</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>kyc_completeness_flag</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>388144272</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>GSGF - ONALENNA BOGOSING</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>DIS_GSG</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>obogosinge@gmail.com</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>bogosing@gmail.com</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>KYC - ONALENNA</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>KYC</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>contact_number</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>76749303</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>KYC - ONALENNA</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>KYC</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>branch_code</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>290167</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>KYC - ONALENNA</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>KYC</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>kyc_completeness_flag</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>Complete</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>38344272</t>
+          <t>388144272</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -2077,29 +2313,25 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>id_number</t>
+          <t>contact_number</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>224922314</t>
+          <t>26749363</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>Unknown ID type 'None' - cannot apply digit validation</t>
-        </is>
-      </c>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>38344272</t>
+          <t>388144272</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2114,836 +2346,494 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
+          <t>branch_code</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>290167</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>388144272</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>GSGF - ONALENNA BOGOSING</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>DIS_GSG</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>fund_category</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Non-Money Market (GSGF)</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>3831 44272</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>DIS - ONALENNA BOGOSING</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>obogosinge@gmail.com</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>3831 44272</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>DIS - ONALENNA BOGOSING</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>contact_number</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>76749303</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>3831 44272</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>DIS - ONALENNA BOGOSING</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>branch_code</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>290167</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>3831 44272</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>DIS - ONALENNA BOGOSING</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>fund_category</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Unknown - Fund Name Not Extracted</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>Fund category could not be determined - fund name unclear</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>363144272</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>DEBIT - ONALENNA BOGOSING</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>DEBIT</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
           <t>id_expiry_date</t>
         </is>
       </c>
-      <c r="E11" s="3" t="n"/>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>02/11/2016</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>ID expiry date is not in the future</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>363144272</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT - ONALENNA BOGOSING</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>obagosing@gmail.com</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>363144272</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT - ONALENNA BOGOSING</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>contact_number</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>76749303</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>363144272</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT - ONALENNA BOGOSING</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>branch_code</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>290167</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>363144272</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>DEBIT - ONALENNA BOGOSING</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>DEBIT</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>fund_category</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Unknown - Fund Name Not Extracted</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>WARNING</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>ID expiry date not captured</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>GSGF - ONALENNA BOGOSING</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>DIS_GSG</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>Fund category could not be determined - fund name unclear</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>383144272</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>ADD - ONALENNA</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>obogosinge@gmail.com</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>oboitshware@gmail.com</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>GSGF - ONALENNA BOGOSING</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>DIS_GSG</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>contact_number</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>76749303</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>GSGF - ONALENNA BOGOSING</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>DIS_GSG</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>branch_code</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>290167</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>GSGF - ONALENNA BOGOSING</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>DIS_GSG</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>fund_category</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>Non-Money Market (GSGF)</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>DIS - ONALENNA BOGOSING</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>id_number</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>224922314</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>Unknown ID type 'None' - cannot apply digit validation</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>DIS - ONALENNA BOGOSING</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>id_expiry_date</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>ID expiry date not captured</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>DIS - ONALENNA BOGOSING</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>obogosinge@gmail.com</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>DIS - ONALENNA BOGOSING</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>contact_number</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>76749303</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>DIS - ONALENNA BOGOSING</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>branch_code</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>290167</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>DIS - ONALENNA BOGOSING</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>fund_category</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>Unknown - Fund Name Not Extracted</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>Fund category could not be determined - fund name unclear</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>DEBIT - ONALENNA BOGOSING</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>DEBIT</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>instruction_type</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="n"/>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>Mandatory field missing</t>
-        </is>
-      </c>
+      <c r="G22" s="3" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>38344272</t>
+          <t>383144272</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>DEBIT - ONALENNA BOGOSING</t>
+          <t>ADD - ONALENNA</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>DEBIT</t>
+          <t>ADD</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>id_number</t>
+          <t>contact_number</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>224922314</t>
+          <t>76749303</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>Unknown ID type 'None' - cannot apply digit validation</t>
-        </is>
-      </c>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>DEBIT - ONALENNA BOGOSING</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>DEBIT</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>id_expiry_date</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>11/02/2026</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>ID expiry date is not in the future</t>
-        </is>
-      </c>
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>383144272</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>ADD - ONALENNA</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>branch_code</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>290167</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>DEBIT - ONALENNA BOGOSING</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>DEBIT</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>obogosinge@gmail.com</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>383144272</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>ADD - ONALENNA</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>fund_category</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Money Market</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>DEBIT - ONALENNA BOGOSING</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>DEBIT</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>contact_number</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>76749303</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>DEBIT - ONALENNA BOGOSING</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>DEBIT</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>branch_code</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>290167</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>DEBIT - ONALENNA BOGOSING</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>DEBIT</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>fund_category</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>Unknown - Fund Name Not Extracted</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>Fund category could not be determined - fund name unclear</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>ADD - ONALENNA</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>fund_number</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="n"/>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>Mandatory field missing</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>ADD - ONALENNA</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>id_number</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="n"/>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>ID number not captured</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>ADD - ONALENNA</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>id_expiry_date</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="n"/>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>ID expiry date not captured</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>ADD - ONALENNA</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>obogosinge@gmail.com</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>ADD - ONALENNA</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>contact_number</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>76749303</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G33" s="4" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>ADD - ONALENNA</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>branch_code</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>290167</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G34" s="4" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>ADD - ONALENNA</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>fund_category</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>Unknown - Fund Name Not Extracted</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>Fund category could not be determined - fund name unclear</t>
-        </is>
-      </c>
+      <c r="G25" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2965,7 +2855,7 @@
     <col width="34" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3036,11 +2926,7 @@
           <t>no</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>'page_initials_complete' not verifiable from current extraction (known POC limitation)</t>
-        </is>
-      </c>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -3115,7 +3001,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>38344272</t>
+          <t>388144272</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3143,16 +3029,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>'page_initials_complete' not verifiable from current extraction (known POC limitation)</t>
-        </is>
-      </c>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>38344272</t>
+          <t>388144272</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -3189,7 +3071,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>38344272</t>
+          <t>388144272</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3222,7 +3104,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>38344272</t>
+          <t>388144272</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3255,7 +3137,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>38344272</t>
+          <t>388144272</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3288,7 +3170,7 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>38344272</t>
+          <t>388144272</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -3325,7 +3207,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>38344272</t>
+          <t>3831 44272</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3353,16 +3235,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>'page_initials_complete' not verifiable from current extraction (known POC limitation)</t>
-        </is>
-      </c>
+      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>38344272</t>
+          <t>3831 44272</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -3399,7 +3277,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>38344272</t>
+          <t>3831 44272</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3432,7 +3310,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>38344272</t>
+          <t>3831 44272</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3465,7 +3343,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>38344272</t>
+          <t>3831 44272</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3498,7 +3376,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>38344272</t>
+          <t>363144272</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3526,16 +3404,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>'page_initials_complete' not verifiable from current extraction (known POC limitation)</t>
-        </is>
-      </c>
+      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>38344272</t>
+          <t>363144272</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -3572,7 +3446,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>38344272</t>
+          <t>363144272</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3605,7 +3479,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>38344272</t>
+          <t>363144272</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3638,7 +3512,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>38344272</t>
+          <t>363144272</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3671,7 +3545,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>38344272</t>
+          <t>363144272</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3704,7 +3578,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>38344272</t>
+          <t>363144272</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3737,7 +3611,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>38344272</t>
+          <t>383144272</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3765,16 +3639,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>'page_initials_complete' not verifiable from current extraction (known POC limitation)</t>
-        </is>
-      </c>
+      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>38344272</t>
+          <t>383144272</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -3811,7 +3681,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>38344272</t>
+          <t>383144272</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3844,7 +3714,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>38344272</t>
+          <t>383144272</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3877,7 +3747,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>38344272</t>
+          <t>383144272</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -3914,7 +3784,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>38344272</t>
+          <t>383144272</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3947,7 +3817,7 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>38344272</t>
+          <t>383144272</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -3992,13 +3862,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G91"/>
+  <dimension ref="A1:G113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="27" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
     <col width="42" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="37" customWidth="1" min="7" max="7"/>
@@ -4042,525 +3912,525 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>38344272</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>KYC - ONALENNA</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>KYC</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>entity_number</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>38344272</t>
         </is>
       </c>
-      <c r="F2" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="F2" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>extracted</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>38344272</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>KYC - ONALENNA</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>KYC</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>entity_name</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>ONALENYA BOGOSING</t>
         </is>
       </c>
-      <c r="F3" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="F3" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>extracted</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>38344272</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>KYC - ONALENNA</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>KYC</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>account_category</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Joint Signature</t>
         </is>
       </c>
-      <c r="F4" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="F4" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>extracted</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>38344272</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>KYC - ONALENNA</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>KYC</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>full_name</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>ONALENYA LORATO BOGOSING</t>
         </is>
       </c>
-      <c r="F5" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="F5" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>extracted</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>38344272</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>KYC - ONALENNA</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>KYC</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>citizenship</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>MOTSWANA</t>
         </is>
       </c>
-      <c r="F6" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="F6" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>extracted</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>38344272</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>KYC - ONALENNA</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>KYC</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>residential_address</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>PLOT 40353, BLOCKS  GABS</t>
         </is>
       </c>
-      <c r="F7" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="F7" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>extracted</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>38344272</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>KYC - ONALENNA</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>KYC</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>date_of_birth</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>16/11/1993</t>
         </is>
       </c>
-      <c r="F8" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="F8" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>extracted</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>38344272</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>KYC - ONALENNA</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>KYC</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>country_of_birth</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>BOTSWANA</t>
         </is>
       </c>
-      <c r="F9" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="F9" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>extracted</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>38344272</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>KYC - ONALENNA</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>KYC</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>id_number</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>224922314</t>
         </is>
       </c>
-      <c r="F10" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="F10" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>extracted</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>38344272</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>KYC - ONALENNA</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>KYC</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>id_expiry_date</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>11/02/2026</t>
         </is>
       </c>
-      <c r="F11" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="F11" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>extracted</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>38344272</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>KYC - ONALENNA</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>KYC</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>us_ssn</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F12" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="F12" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>extracted</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>38344272</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>KYC - ONALENNA</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>KYC</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>contact_number</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>76749303</t>
         </is>
       </c>
-      <c r="F13" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="F13" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>extracted</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>38344272</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>KYC - ONALENNA</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>KYC</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>obogosinge@gmail.com</t>
         </is>
       </c>
-      <c r="F14" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="F14" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>extracted</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>38344272</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>KYC - ONALENNA</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>KYC</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>occupation</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>DIPLOMAT</t>
         </is>
       </c>
-      <c r="F15" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="F15" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>extracted</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>38344272</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>KYC - ONALENNA</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>KYC</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>employer</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>THE UNITED NATIONS</t>
         </is>
       </c>
-      <c r="F16" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="F16" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>extracted</t>
         </is>
@@ -4593,7 +4463,7 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
@@ -4602,771 +4472,767 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>38344272</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>KYC - ONALENNA</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>KYC</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>bank_name</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>ABSA</t>
         </is>
       </c>
-      <c r="F18" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="F18" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>extracted</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>38344272</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>KYC - ONALENNA</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>KYC</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>account_number</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>1078631</t>
         </is>
       </c>
-      <c r="F19" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="F19" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>extracted</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>38344272</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>KYC - ONALENNA</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>KYC</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>branch_name</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>MALL</t>
         </is>
       </c>
-      <c r="F20" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="F20" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>extracted</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>38344272</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>KYC - ONALENNA</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>KYC</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>branch_code</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>290167</t>
         </is>
       </c>
-      <c r="F21" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="F21" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>extracted</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>38344272</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>KYC - ONALENNA</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>KYC</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>account_type_banking</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>Current</t>
         </is>
       </c>
-      <c r="F22" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="F22" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t>extracted</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>38344272</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>KYC - ONALENNA</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>KYC</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>source_of_income</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>Salary</t>
         </is>
       </c>
-      <c r="F23" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="F23" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
         <is>
           <t>extracted</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>38344272</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>KYC - ONALENNA</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>KYC</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>kyc_certified_id</t>
         </is>
       </c>
-      <c r="E24" s="4" t="b">
+      <c r="E24" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="F24" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="F24" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
         <is>
           <t>extracted</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>38344272</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>KYC - ONALENNA</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>KYC</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>kyc_proof_address</t>
         </is>
       </c>
-      <c r="E25" s="4" t="b">
+      <c r="E25" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="F25" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="F25" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
         <is>
           <t>extracted</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>38344272</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>KYC - ONALENNA</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>KYC</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>kyc_proof_banking</t>
         </is>
       </c>
-      <c r="E26" s="4" t="b">
+      <c r="E26" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="F26" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="F26" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
         <is>
           <t>extracted</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>38344272</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>KYC - ONALENNA</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>KYC</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>kyc_proof_source</t>
         </is>
       </c>
-      <c r="E27" s="4" t="b">
+      <c r="E27" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="F27" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="F27" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>extracted</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>38344272</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>KYC - ONALENNA</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>KYC</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>form_type</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>KYC (Know Your Customer)</t>
         </is>
       </c>
-      <c r="F28" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="G28" s="4" t="inlineStr">
+      <c r="F28" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
         <is>
           <t>extracted</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>38344272</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>KYC - ONALENNA</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>KYC</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>kyc_completeness_flag</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
       </c>
-      <c r="F29" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="G29" s="4" t="inlineStr">
+      <c r="F29" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>extracted</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>388144272</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>GSGF - ONALENNA BOGOSING</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>DIS_GSG</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>form_type</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>Disinvestment Form (GSGF)</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="G30" s="4" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>entity_number</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>388144272</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
         <is>
           <t>extracted</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>388144272</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>GSGF - ONALENNA BOGOSING</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>DIS_GSG</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>fund_name</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>BIFM Global Sustainable Growth Fund</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="G31" s="4" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>full_name</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Onalenna Bogosing</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t>extracted</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>388144272</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>GSGF - ONALENNA BOGOSING</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>DIS_GSG</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>fund_category</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>Non-Money Market (GSGF)</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="G32" s="4" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>id_number</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>224922316</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
         <is>
           <t>extracted</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>388144272</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>GSGF - ONALENNA BOGOSING</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>DIS_GSG</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>processing_cutoff</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>Quarterly - 7th of last month of quarter</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="G33" s="4" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>contact_number</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>26749363</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
         <is>
           <t>extracted</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>388144272</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>GSGF - ONALENNA BOGOSING</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>DIS_GSG</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>instruction_mode</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="G34" s="4" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>bogosing@gmail.com</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
         <is>
           <t>extracted</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>388144272</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>GSGF - ONALENNA BOGOSING</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>DIS_GSG</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>entity_number</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="n">
-        <v>85</v>
-      </c>
-      <c r="G35" s="4" t="inlineStr">
-        <is>
-          <t>backfilled:KYC - ONALENNA</t>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>disinvestment_amount</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>extracted</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>388144272</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>GSGF - ONALENNA BOGOSING</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>DIS_GSG</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>full_name</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>ONALENYA LORATO BOGOSING</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="n">
-        <v>85</v>
-      </c>
-      <c r="G36" s="4" t="inlineStr">
-        <is>
-          <t>backfilled:KYC - ONALENNA</t>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>account_closure</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>extracted</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>388144272</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>GSGF - ONALENNA BOGOSING</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>DIS_GSG</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>id_number</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>224922314</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="n">
-        <v>85</v>
-      </c>
-      <c r="G37" s="4" t="inlineStr">
-        <is>
-          <t>backfilled:KYC - ONALENNA</t>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>bank_account_name</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Onalenna Bogosing</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>extracted</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>388144272</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>GSGF - ONALENNA BOGOSING</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>DIS_GSG</t>
         </is>
       </c>
-      <c r="D38" s="4" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>obogosinge@gmail.com</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="n">
-        <v>85</v>
-      </c>
-      <c r="G38" s="4" t="inlineStr">
-        <is>
-          <t>backfilled:KYC - ONALENNA</t>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>bank_name</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>ABSA</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>extracted</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>388144272</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>GSGF - ONALENNA BOGOSING</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>DIS_GSG</t>
         </is>
       </c>
-      <c r="D39" s="4" t="inlineStr">
-        <is>
-          <t>contact_number</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>76749303</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="n">
-        <v>85</v>
-      </c>
-      <c r="G39" s="4" t="inlineStr">
-        <is>
-          <t>backfilled:KYC - ONALENNA</t>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>account_number</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>4072341</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>extracted</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>38344272</t>
+          <t>388144272</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -5381,552 +5247,546 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>bank_account_name</t>
+          <t>branch_name</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Onalenya Bogosiny</t>
+          <t>Maun</t>
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>backfilled:KYC - ONALENNA</t>
+          <t>extracted</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>388144272</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>GSGF - ONALENNA BOGOSING</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>DIS_GSG</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>bank_name</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>ABSA</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="n">
-        <v>85</v>
-      </c>
-      <c r="G41" s="4" t="inlineStr">
-        <is>
-          <t>backfilled:KYC - ONALENNA</t>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>branch_code</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>290167</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>extracted</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>388144272</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>GSGF - ONALENNA BOGOSING</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>DIS_GSG</t>
         </is>
       </c>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>account_number</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>1078631</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="n">
-        <v>85</v>
-      </c>
-      <c r="G42" s="4" t="inlineStr">
-        <is>
-          <t>backfilled:KYC - ONALENNA</t>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>account_type_banking</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Current</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>extracted</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>388144272</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>GSGF - ONALENNA BOGOSING</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>DIS_GSG</t>
         </is>
       </c>
-      <c r="D43" s="4" t="inlineStr">
-        <is>
-          <t>branch_name</t>
-        </is>
-      </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>MALL</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="n">
-        <v>85</v>
-      </c>
-      <c r="G43" s="4" t="inlineStr">
-        <is>
-          <t>backfilled:KYC - ONALENNA</t>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>form_type</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Disinvestment Form (GSGF)</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>extracted</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>388144272</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>GSGF - ONALENNA BOGOSING</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>DIS_GSG</t>
         </is>
       </c>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>branch_code</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>290167</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="n">
-        <v>85</v>
-      </c>
-      <c r="G44" s="4" t="inlineStr">
-        <is>
-          <t>backfilled:KYC - ONALENNA</t>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>fund_name</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>BIFM Global Sustainable Growth Fund</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>extracted</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>388144272</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>GSGF - ONALENNA BOGOSING</t>
         </is>
       </c>
-      <c r="C45" s="4" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t>DIS_GSG</t>
         </is>
       </c>
-      <c r="D45" s="4" t="inlineStr">
-        <is>
-          <t>account_type_banking</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>Current</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="n">
-        <v>85</v>
-      </c>
-      <c r="G45" s="4" t="inlineStr">
-        <is>
-          <t>backfilled:KYC - ONALENNA</t>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>fund_category</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Non-Money Market (GSGF)</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>extracted</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>388144272</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>GSGF - ONALENNA BOGOSING</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>DIS_GSG</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>processing_cutoff</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Quarterly - 7th of last month of quarter</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>388144272</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>GSGF - ONALENNA BOGOSING</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>DIS_GSG</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>fund_category_priority</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>388144272</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>GSGF - ONALENNA BOGOSING</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>DIS_GSG</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>instruction_mode</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Partial Withdrawal</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>3831 44272</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>DIS - ONALENNA BOGOSING</t>
         </is>
       </c>
-      <c r="C46" s="4" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>DIS</t>
         </is>
       </c>
-      <c r="D46" s="4" t="inlineStr">
-        <is>
-          <t>form_type</t>
-        </is>
-      </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>Disinvestment Form (Standard)</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="G46" s="4" t="inlineStr">
-        <is>
-          <t>extracted</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>entity_number</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>3831 44272</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>3831 44272</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
         <is>
           <t>DIS - ONALENNA BOGOSING</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr">
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t>DIS</t>
         </is>
       </c>
-      <c r="D47" s="4" t="inlineStr">
-        <is>
-          <t>fund_category</t>
-        </is>
-      </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>Unknown - Fund Name Not Extracted</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="G47" s="4" t="inlineStr">
-        <is>
-          <t>extracted</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>full_name</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Onalenna Bogosing</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>3831 44272</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>DIS - ONALENNA BOGOSING</t>
         </is>
       </c>
-      <c r="C48" s="4" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>DIS</t>
         </is>
       </c>
-      <c r="D48" s="4" t="inlineStr">
-        <is>
-          <t>processing_cutoff</t>
-        </is>
-      </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F48" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="G48" s="4" t="inlineStr">
-        <is>
-          <t>extracted</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>id_number</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>222922316</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>3831 44272</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
         <is>
           <t>DIS - ONALENNA BOGOSING</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C52" s="3" t="inlineStr">
         <is>
           <t>DIS</t>
         </is>
       </c>
-      <c r="D49" s="4" t="inlineStr">
-        <is>
-          <t>instruction_mode</t>
-        </is>
-      </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F49" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="G49" s="4" t="inlineStr">
-        <is>
-          <t>extracted</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>contact_number</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>76749303</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>3831 44272</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t>DIS - ONALENNA BOGOSING</t>
         </is>
       </c>
-      <c r="C50" s="4" t="inlineStr">
+      <c r="C53" s="3" t="inlineStr">
         <is>
           <t>DIS</t>
         </is>
       </c>
-      <c r="D50" s="4" t="inlineStr">
-        <is>
-          <t>entity_number</t>
-        </is>
-      </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="F50" s="4" t="n">
-        <v>85</v>
-      </c>
-      <c r="G50" s="4" t="inlineStr">
-        <is>
-          <t>backfilled:KYC - ONALENNA</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>fund_number</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>1674982</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>3831 44272</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
         <is>
           <t>DIS - ONALENNA BOGOSING</t>
         </is>
       </c>
-      <c r="C51" s="4" t="inlineStr">
+      <c r="C54" s="3" t="inlineStr">
         <is>
           <t>DIS</t>
         </is>
       </c>
-      <c r="D51" s="4" t="inlineStr">
-        <is>
-          <t>full_name</t>
-        </is>
-      </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>ONALENYA LORATO BOGOSING</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="n">
-        <v>85</v>
-      </c>
-      <c r="G51" s="4" t="inlineStr">
-        <is>
-          <t>backfilled:KYC - ONALENNA</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>disinvestment_amount</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>200000</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>3831 44272</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t>DIS - ONALENNA BOGOSING</t>
         </is>
       </c>
-      <c r="C52" s="4" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr">
         <is>
           <t>DIS</t>
         </is>
       </c>
-      <c r="D52" s="4" t="inlineStr">
-        <is>
-          <t>id_number</t>
-        </is>
-      </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>224922314</t>
-        </is>
-      </c>
-      <c r="F52" s="4" t="n">
-        <v>85</v>
-      </c>
-      <c r="G52" s="4" t="inlineStr">
-        <is>
-          <t>backfilled:KYC - ONALENNA</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>DIS - ONALENNA BOGOSING</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
-      </c>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>obogosinge@gmail.com</t>
-        </is>
-      </c>
-      <c r="F53" s="4" t="n">
-        <v>85</v>
-      </c>
-      <c r="G53" s="4" t="inlineStr">
-        <is>
-          <t>backfilled:KYC - ONALENNA</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>DIS - ONALENNA BOGOSING</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
-      </c>
-      <c r="D54" s="4" t="inlineStr">
-        <is>
-          <t>contact_number</t>
-        </is>
-      </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>76749303</t>
-        </is>
-      </c>
-      <c r="F54" s="4" t="n">
-        <v>85</v>
-      </c>
-      <c r="G54" s="4" t="inlineStr">
-        <is>
-          <t>backfilled:KYC - ONALENNA</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>DIS - ONALENNA BOGOSING</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
-      </c>
-      <c r="D55" s="4" t="inlineStr">
-        <is>
-          <t>fund_name</t>
-        </is>
-      </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>BIFM Global Sustainable Growth Fund</t>
-        </is>
-      </c>
-      <c r="F55" s="4" t="n">
-        <v>85</v>
-      </c>
-      <c r="G55" s="4" t="inlineStr">
-        <is>
-          <t>backfilled:GSGF - ONALENNA BOGOSING</t>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>account_closure</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>extracted</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>38344272</t>
+          <t>3831 44272</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -5946,22 +5806,22 @@
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Onalenya Bogosiny</t>
+          <t>Onalenna Bogosing</t>
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>backfilled:KYC - ONALENNA</t>
+          <t>extracted</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>38344272</t>
+          <t>3831 44272</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
@@ -5981,57 +5841,57 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>ABSA</t>
+          <t>NBSA</t>
         </is>
       </c>
       <c r="F57" s="4" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>backfilled:KYC - ONALENNA</t>
+          <t>extracted</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="inlineStr">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>3831 44272</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t>DIS - ONALENNA BOGOSING</t>
         </is>
       </c>
-      <c r="C58" s="4" t="inlineStr">
+      <c r="C58" s="3" t="inlineStr">
         <is>
           <t>DIS</t>
         </is>
       </c>
-      <c r="D58" s="4" t="inlineStr">
+      <c r="D58" s="3" t="inlineStr">
         <is>
           <t>account_number</t>
         </is>
       </c>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>1078631</t>
-        </is>
-      </c>
-      <c r="F58" s="4" t="n">
-        <v>85</v>
-      </c>
-      <c r="G58" s="4" t="inlineStr">
-        <is>
-          <t>backfilled:KYC - ONALENNA</t>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>1033921</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>extracted</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>38344272</t>
+          <t>3831 44272</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
@@ -6051,442 +5911,440 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>MALL</t>
+          <t>Maun</t>
         </is>
       </c>
       <c r="F59" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>3831 44272</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>DIS - ONALENNA BOGOSING</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>branch_code</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>290167</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>3831 44272</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>DIS - ONALENNA BOGOSING</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>form_type</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>Disinvestment Form (Standard)</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>3831 44272</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>DIS - ONALENNA BOGOSING</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>fund_category</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>Unknown - Fund Name Not Extracted</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>3831 44272</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>DIS - ONALENNA BOGOSING</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>processing_cutoff</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>3831 44272</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>DIS - ONALENNA BOGOSING</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>fund_category_priority</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>99</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>3831 44272</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>DIS - ONALENNA BOGOSING</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>instruction_mode</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>Partial Withdrawal</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>3831 44272</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>DIS - ONALENNA BOGOSING</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>obogosinge@gmail.com</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="n">
         <v>85</v>
       </c>
-      <c r="G59" s="4" t="inlineStr">
+      <c r="G66" s="3" t="inlineStr">
         <is>
           <t>backfilled:KYC - ONALENNA</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>3831 44272</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>DIS - ONALENNA BOGOSING</t>
         </is>
       </c>
-      <c r="C60" s="4" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t>DIS</t>
         </is>
       </c>
-      <c r="D60" s="4" t="inlineStr">
-        <is>
-          <t>branch_code</t>
-        </is>
-      </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>290167</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="n">
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>fund_name</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>BIFM Global Sustainable Growth Fund</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="n">
         <v>85</v>
       </c>
-      <c r="G60" s="4" t="inlineStr">
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>backfilled:GSGF - ONALENNA BOGOSING</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>3831 44272</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>DIS - ONALENNA BOGOSING</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>account_type_banking</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>Current</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="G68" s="3" t="inlineStr">
         <is>
           <t>backfilled:KYC - ONALENNA</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B61" s="4" t="inlineStr">
-        <is>
-          <t>DIS - ONALENNA BOGOSING</t>
-        </is>
-      </c>
-      <c r="C61" s="4" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
-      </c>
-      <c r="D61" s="4" t="inlineStr">
-        <is>
-          <t>account_type_banking</t>
-        </is>
-      </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>Current</t>
-        </is>
-      </c>
-      <c r="F61" s="4" t="n">
-        <v>85</v>
-      </c>
-      <c r="G61" s="4" t="inlineStr">
-        <is>
-          <t>backfilled:KYC - ONALENNA</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B62" s="4" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>363144272</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
         <is>
           <t>DEBIT - ONALENNA BOGOSING</t>
         </is>
       </c>
-      <c r="C62" s="4" t="inlineStr">
+      <c r="C69" s="3" t="inlineStr">
         <is>
           <t>DEBIT</t>
         </is>
       </c>
-      <c r="D62" s="4" t="inlineStr">
-        <is>
-          <t>form_type</t>
-        </is>
-      </c>
-      <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t>Debit Order Form</t>
-        </is>
-      </c>
-      <c r="F62" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="G62" s="4" t="inlineStr">
-        <is>
-          <t>extracted</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B63" s="4" t="inlineStr">
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>entity_number</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>363144272</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>363144272</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
         <is>
           <t>DEBIT - ONALENNA BOGOSING</t>
         </is>
       </c>
-      <c r="C63" s="4" t="inlineStr">
+      <c r="C70" s="3" t="inlineStr">
         <is>
           <t>DEBIT</t>
         </is>
       </c>
-      <c r="D63" s="4" t="inlineStr">
-        <is>
-          <t>fund_category</t>
-        </is>
-      </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>Unknown - Fund Name Not Extracted</t>
-        </is>
-      </c>
-      <c r="F63" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="G63" s="4" t="inlineStr">
-        <is>
-          <t>extracted</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B64" s="4" t="inlineStr">
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>full_name</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>Onalenna Bogosing</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G70" s="3" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>363144272</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
         <is>
           <t>DEBIT - ONALENNA BOGOSING</t>
         </is>
       </c>
-      <c r="C64" s="4" t="inlineStr">
+      <c r="C71" s="3" t="inlineStr">
         <is>
           <t>DEBIT</t>
         </is>
       </c>
-      <c r="D64" s="4" t="inlineStr">
-        <is>
-          <t>processing_cutoff</t>
-        </is>
-      </c>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F64" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="G64" s="4" t="inlineStr">
-        <is>
-          <t>extracted</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B65" s="4" t="inlineStr">
-        <is>
-          <t>DEBIT - ONALENNA BOGOSING</t>
-        </is>
-      </c>
-      <c r="C65" s="4" t="inlineStr">
-        <is>
-          <t>DEBIT</t>
-        </is>
-      </c>
-      <c r="D65" s="4" t="inlineStr">
-        <is>
-          <t>entity_number</t>
-        </is>
-      </c>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="F65" s="4" t="n">
-        <v>85</v>
-      </c>
-      <c r="G65" s="4" t="inlineStr">
-        <is>
-          <t>backfilled:KYC - ONALENNA</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B66" s="4" t="inlineStr">
-        <is>
-          <t>DEBIT - ONALENNA BOGOSING</t>
-        </is>
-      </c>
-      <c r="C66" s="4" t="inlineStr">
-        <is>
-          <t>DEBIT</t>
-        </is>
-      </c>
-      <c r="D66" s="4" t="inlineStr">
-        <is>
-          <t>full_name</t>
-        </is>
-      </c>
-      <c r="E66" s="4" t="inlineStr">
-        <is>
-          <t>ONALENYA LORATO BOGOSING</t>
-        </is>
-      </c>
-      <c r="F66" s="4" t="n">
-        <v>85</v>
-      </c>
-      <c r="G66" s="4" t="inlineStr">
-        <is>
-          <t>backfilled:KYC - ONALENNA</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B67" s="4" t="inlineStr">
-        <is>
-          <t>DEBIT - ONALENNA BOGOSING</t>
-        </is>
-      </c>
-      <c r="C67" s="4" t="inlineStr">
-        <is>
-          <t>DEBIT</t>
-        </is>
-      </c>
-      <c r="D67" s="4" t="inlineStr">
+      <c r="D71" s="3" t="inlineStr">
         <is>
           <t>id_number</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>224922314</t>
-        </is>
-      </c>
-      <c r="F67" s="4" t="n">
-        <v>85</v>
-      </c>
-      <c r="G67" s="4" t="inlineStr">
-        <is>
-          <t>backfilled:KYC - ONALENNA</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B68" s="4" t="inlineStr">
-        <is>
-          <t>DEBIT - ONALENNA BOGOSING</t>
-        </is>
-      </c>
-      <c r="C68" s="4" t="inlineStr">
-        <is>
-          <t>DEBIT</t>
-        </is>
-      </c>
-      <c r="D68" s="4" t="inlineStr">
-        <is>
-          <t>id_expiry_date</t>
-        </is>
-      </c>
-      <c r="E68" s="4" t="inlineStr">
-        <is>
-          <t>11/02/2026</t>
-        </is>
-      </c>
-      <c r="F68" s="4" t="n">
-        <v>85</v>
-      </c>
-      <c r="G68" s="4" t="inlineStr">
-        <is>
-          <t>backfilled:KYC - ONALENNA</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B69" s="4" t="inlineStr">
-        <is>
-          <t>DEBIT - ONALENNA BOGOSING</t>
-        </is>
-      </c>
-      <c r="C69" s="4" t="inlineStr">
-        <is>
-          <t>DEBIT</t>
-        </is>
-      </c>
-      <c r="D69" s="4" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>obogosinge@gmail.com</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="n">
-        <v>85</v>
-      </c>
-      <c r="G69" s="4" t="inlineStr">
-        <is>
-          <t>backfilled:KYC - ONALENNA</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B70" s="4" t="inlineStr">
-        <is>
-          <t>DEBIT - ONALENNA BOGOSING</t>
-        </is>
-      </c>
-      <c r="C70" s="4" t="inlineStr">
-        <is>
-          <t>DEBIT</t>
-        </is>
-      </c>
-      <c r="D70" s="4" t="inlineStr">
-        <is>
-          <t>contact_number</t>
-        </is>
-      </c>
-      <c r="E70" s="4" t="inlineStr">
-        <is>
-          <t>76749303</t>
-        </is>
-      </c>
-      <c r="F70" s="4" t="n">
-        <v>85</v>
-      </c>
-      <c r="G70" s="4" t="inlineStr">
-        <is>
-          <t>backfilled:KYC - ONALENNA</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B71" s="4" t="inlineStr">
-        <is>
-          <t>DEBIT - ONALENNA BOGOSING</t>
-        </is>
-      </c>
-      <c r="C71" s="4" t="inlineStr">
-        <is>
-          <t>DEBIT</t>
-        </is>
-      </c>
-      <c r="D71" s="4" t="inlineStr">
-        <is>
-          <t>fund_name</t>
-        </is>
-      </c>
-      <c r="E71" s="4" t="inlineStr">
-        <is>
-          <t>BIFM Global Sustainable Growth Fund</t>
-        </is>
-      </c>
-      <c r="F71" s="4" t="n">
-        <v>85</v>
-      </c>
-      <c r="G71" s="4" t="inlineStr">
-        <is>
-          <t>backfilled:GSGF - ONALENNA BOGOSING</t>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>2249223M</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>extracted</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>38344272</t>
+          <t>363144272</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -6501,683 +6359,1445 @@
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>bank_account_name</t>
+          <t>id_expiry_date</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>Onalenya Bogosiny</t>
+          <t>02/11/2016</t>
         </is>
       </c>
       <c r="F72" s="3" t="n">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>backfilled:KYC - ONALENNA</t>
+          <t>extracted</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B73" s="4" t="inlineStr">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>363144272</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
         <is>
           <t>DEBIT - ONALENNA BOGOSING</t>
         </is>
       </c>
-      <c r="C73" s="4" t="inlineStr">
+      <c r="C73" s="3" t="inlineStr">
         <is>
           <t>DEBIT</t>
         </is>
       </c>
-      <c r="D73" s="4" t="inlineStr">
-        <is>
-          <t>bank_name</t>
-        </is>
-      </c>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>ABSA</t>
-        </is>
-      </c>
-      <c r="F73" s="4" t="n">
-        <v>85</v>
-      </c>
-      <c r="G73" s="4" t="inlineStr">
-        <is>
-          <t>backfilled:KYC - ONALENNA</t>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>contact_number</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>76749303</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G73" s="3" t="inlineStr">
+        <is>
+          <t>extracted</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B74" s="4" t="inlineStr">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>363144272</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
         <is>
           <t>DEBIT - ONALENNA BOGOSING</t>
         </is>
       </c>
-      <c r="C74" s="4" t="inlineStr">
+      <c r="C74" s="3" t="inlineStr">
         <is>
           <t>DEBIT</t>
         </is>
       </c>
-      <c r="D74" s="4" t="inlineStr">
-        <is>
-          <t>account_number</t>
-        </is>
-      </c>
-      <c r="E74" s="4" t="inlineStr">
-        <is>
-          <t>1078631</t>
-        </is>
-      </c>
-      <c r="F74" s="4" t="n">
-        <v>85</v>
-      </c>
-      <c r="G74" s="4" t="inlineStr">
-        <is>
-          <t>backfilled:KYC - ONALENNA</t>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>obagosing@gmail.com</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G74" s="3" t="inlineStr">
+        <is>
+          <t>extracted</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B75" s="4" t="inlineStr">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>363144272</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
         <is>
           <t>DEBIT - ONALENNA BOGOSING</t>
         </is>
       </c>
-      <c r="C75" s="4" t="inlineStr">
+      <c r="C75" s="3" t="inlineStr">
         <is>
           <t>DEBIT</t>
         </is>
       </c>
-      <c r="D75" s="4" t="inlineStr">
-        <is>
-          <t>branch_name</t>
-        </is>
-      </c>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>MALL</t>
-        </is>
-      </c>
-      <c r="F75" s="4" t="n">
-        <v>85</v>
-      </c>
-      <c r="G75" s="4" t="inlineStr">
-        <is>
-          <t>backfilled:KYC - ONALENNA</t>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>source_of_contribution</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G75" s="3" t="inlineStr">
+        <is>
+          <t>extracted</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B76" s="4" t="inlineStr">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>363144272</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
         <is>
           <t>DEBIT - ONALENNA BOGOSING</t>
         </is>
       </c>
-      <c r="C76" s="4" t="inlineStr">
+      <c r="C76" s="3" t="inlineStr">
         <is>
           <t>DEBIT</t>
         </is>
       </c>
-      <c r="D76" s="4" t="inlineStr">
-        <is>
-          <t>branch_code</t>
-        </is>
-      </c>
-      <c r="E76" s="4" t="inlineStr">
-        <is>
-          <t>290167</t>
-        </is>
-      </c>
-      <c r="F76" s="4" t="n">
-        <v>85</v>
-      </c>
-      <c r="G76" s="4" t="inlineStr">
-        <is>
-          <t>backfilled:KYC - ONALENNA</t>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>instruction_type</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>Change existing debit order</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t>extracted</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B77" s="4" t="inlineStr">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>363144272</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
         <is>
           <t>DEBIT - ONALENNA BOGOSING</t>
         </is>
       </c>
-      <c r="C77" s="4" t="inlineStr">
+      <c r="C77" s="3" t="inlineStr">
         <is>
           <t>DEBIT</t>
         </is>
       </c>
-      <c r="D77" s="4" t="inlineStr">
-        <is>
-          <t>account_type_banking</t>
-        </is>
-      </c>
-      <c r="E77" s="4" t="inlineStr">
-        <is>
-          <t>Current</t>
-        </is>
-      </c>
-      <c r="F77" s="4" t="n">
-        <v>85</v>
-      </c>
-      <c r="G77" s="4" t="inlineStr">
-        <is>
-          <t>backfilled:KYC - ONALENNA</t>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>fund_number</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>164914</t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t>extracted</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B78" s="4" t="inlineStr">
-        <is>
-          <t>ADD - ONALENNA</t>
-        </is>
-      </c>
-      <c r="C78" s="4" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="D78" s="4" t="inlineStr">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>363144272</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT - ONALENNA BOGOSING</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>change_amount</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G78" s="3" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>363144272</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT - ONALENNA BOGOSING</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>commencement_date</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G79" s="3" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>363144272</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT - ONALENNA BOGOSING</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>escalation_rate</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G80" s="3" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>363144272</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT - ONALENNA BOGOSING</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
         <is>
           <t>form_type</t>
         </is>
       </c>
-      <c r="E78" s="4" t="inlineStr">
-        <is>
-          <t>Additional Investment Form</t>
-        </is>
-      </c>
-      <c r="F78" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="G78" s="4" t="inlineStr">
-        <is>
-          <t>extracted</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B79" s="4" t="inlineStr">
-        <is>
-          <t>ADD - ONALENNA</t>
-        </is>
-      </c>
-      <c r="C79" s="4" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="D79" s="4" t="inlineStr">
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>Debit Order Form</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G81" s="3" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>363144272</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT - ONALENNA BOGOSING</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
         <is>
           <t>fund_category</t>
         </is>
       </c>
-      <c r="E79" s="4" t="inlineStr">
+      <c r="E82" s="3" t="inlineStr">
         <is>
           <t>Unknown - Fund Name Not Extracted</t>
         </is>
       </c>
-      <c r="F79" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="G79" s="4" t="inlineStr">
-        <is>
-          <t>extracted</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B80" s="4" t="inlineStr">
-        <is>
-          <t>ADD - ONALENNA</t>
-        </is>
-      </c>
-      <c r="C80" s="4" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="D80" s="4" t="inlineStr">
+      <c r="F82" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G82" s="3" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>363144272</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT - ONALENNA BOGOSING</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
         <is>
           <t>processing_cutoff</t>
         </is>
       </c>
-      <c r="E80" s="4" t="inlineStr">
+      <c r="E83" s="3" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="F80" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="G80" s="4" t="inlineStr">
-        <is>
-          <t>extracted</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B81" s="4" t="inlineStr">
-        <is>
-          <t>ADD - ONALENNA</t>
-        </is>
-      </c>
-      <c r="C81" s="4" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="D81" s="4" t="inlineStr">
-        <is>
-          <t>entity_number</t>
-        </is>
-      </c>
-      <c r="E81" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="F81" s="4" t="n">
-        <v>85</v>
-      </c>
-      <c r="G81" s="4" t="inlineStr">
-        <is>
-          <t>backfilled:KYC - ONALENNA</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B82" s="4" t="inlineStr">
-        <is>
-          <t>ADD - ONALENNA</t>
-        </is>
-      </c>
-      <c r="C82" s="4" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="D82" s="4" t="inlineStr">
-        <is>
-          <t>full_name</t>
-        </is>
-      </c>
-      <c r="E82" s="4" t="inlineStr">
-        <is>
-          <t>ONALENYA LORATO BOGOSING</t>
-        </is>
-      </c>
-      <c r="F82" s="4" t="n">
-        <v>85</v>
-      </c>
-      <c r="G82" s="4" t="inlineStr">
-        <is>
-          <t>backfilled:KYC - ONALENNA</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B83" s="4" t="inlineStr">
-        <is>
-          <t>ADD - ONALENNA</t>
-        </is>
-      </c>
-      <c r="C83" s="4" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="D83" s="4" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="E83" s="4" t="inlineStr">
-        <is>
-          <t>obogosinge@gmail.com</t>
-        </is>
-      </c>
-      <c r="F83" s="4" t="n">
-        <v>85</v>
-      </c>
-      <c r="G83" s="4" t="inlineStr">
-        <is>
-          <t>backfilled:KYC - ONALENNA</t>
+      <c r="F83" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>extracted</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B84" s="4" t="inlineStr">
-        <is>
-          <t>ADD - ONALENNA</t>
-        </is>
-      </c>
-      <c r="C84" s="4" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="D84" s="4" t="inlineStr">
-        <is>
-          <t>contact_number</t>
-        </is>
-      </c>
-      <c r="E84" s="4" t="inlineStr">
-        <is>
-          <t>76749303</t>
-        </is>
-      </c>
-      <c r="F84" s="4" t="n">
-        <v>85</v>
-      </c>
-      <c r="G84" s="4" t="inlineStr">
-        <is>
-          <t>backfilled:KYC - ONALENNA</t>
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>363144272</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT - ONALENNA BOGOSING</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>fund_category_priority</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>99</v>
+      </c>
+      <c r="F84" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G84" s="3" t="inlineStr">
+        <is>
+          <t>extracted</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B85" s="4" t="inlineStr">
-        <is>
-          <t>ADD - ONALENNA</t>
-        </is>
-      </c>
-      <c r="C85" s="4" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="D85" s="4" t="inlineStr">
-        <is>
-          <t>fund_name</t>
-        </is>
-      </c>
-      <c r="E85" s="4" t="inlineStr">
-        <is>
-          <t>BIFM Global Sustainable Growth Fund</t>
-        </is>
-      </c>
-      <c r="F85" s="4" t="n">
-        <v>85</v>
-      </c>
-      <c r="G85" s="4" t="inlineStr">
-        <is>
-          <t>backfilled:GSGF - ONALENNA BOGOSING</t>
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>363144272</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT - ONALENNA BOGOSING</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>sub_instruction_type</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G85" s="3" t="inlineStr">
+        <is>
+          <t>extracted</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>38344272</t>
+          <t>363144272</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
+          <t>DEBIT - ONALENNA BOGOSING</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>fund_name</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>BIFM Global Sustainable Growth Fund</t>
+        </is>
+      </c>
+      <c r="F86" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="G86" s="3" t="inlineStr">
+        <is>
+          <t>backfilled:GSGF - ONALENNA BOGOSING</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>363144272</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT - ONALENNA BOGOSING</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>bank_account_name</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>Onalenna Bogosing</t>
+        </is>
+      </c>
+      <c r="F87" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="G87" s="3" t="inlineStr">
+        <is>
+          <t>backfilled:GSGF - ONALENNA BOGOSING</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>363144272</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT - ONALENNA BOGOSING</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>bank_name</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>ABSA</t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="G88" s="3" t="inlineStr">
+        <is>
+          <t>backfilled:KYC - ONALENNA</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>363144272</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT - ONALENNA BOGOSING</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>account_number</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>1078631</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="G89" s="3" t="inlineStr">
+        <is>
+          <t>backfilled:KYC - ONALENNA</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>363144272</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT - ONALENNA BOGOSING</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>branch_name</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>Maun</t>
+        </is>
+      </c>
+      <c r="F90" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="G90" s="3" t="inlineStr">
+        <is>
+          <t>backfilled:GSGF - ONALENNA BOGOSING</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>363144272</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT - ONALENNA BOGOSING</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>branch_code</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>290167</t>
+        </is>
+      </c>
+      <c r="F91" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="G91" s="3" t="inlineStr">
+        <is>
+          <t>backfilled:KYC - ONALENNA</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>363144272</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT - ONALENNA BOGOSING</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>DEBIT</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>account_type_banking</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>Current</t>
+        </is>
+      </c>
+      <c r="F92" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="G92" s="3" t="inlineStr">
+        <is>
+          <t>backfilled:KYC - ONALENNA</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>383144272</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
           <t>ADD - ONALENNA</t>
         </is>
       </c>
-      <c r="C86" s="3" t="inlineStr">
+      <c r="C93" s="3" t="inlineStr">
         <is>
           <t>ADD</t>
         </is>
       </c>
-      <c r="D86" s="3" t="inlineStr">
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>entity_number</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>383144272</t>
+        </is>
+      </c>
+      <c r="F93" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G93" s="3" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>383144272</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>ADD - ONALENNA</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>full_name</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>Onalenna Boitshware</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="G94" s="3" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>383144272</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>ADD - ONALENNA</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>contact_number</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>76749303</t>
+        </is>
+      </c>
+      <c r="F95" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G95" s="3" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>383144272</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>ADD - ONALENNA</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>oboitshware@gmail.com</t>
+        </is>
+      </c>
+      <c r="F96" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="G96" s="3" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>383144272</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>ADD - ONALENNA</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>source_of_funds</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>Salary</t>
+        </is>
+      </c>
+      <c r="F97" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G97" s="3" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>383144272</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>ADD - ONALENNA</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>fund_number</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>1673412</t>
+        </is>
+      </c>
+      <c r="F98" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G98" s="3" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>383144272</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>ADD - ONALENNA</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t>fund_name</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>Bifm Pula Money Market Fund</t>
+        </is>
+      </c>
+      <c r="F99" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="G99" s="4" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>383144272</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>ADD - ONALENNA</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>lump_sum_deposit_amount</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>280000</v>
+      </c>
+      <c r="F100" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G100" s="3" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>383144272</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>ADD - ONALENNA</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>lump_sum_debit_amount</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>100000</v>
+      </c>
+      <c r="F101" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G101" s="3" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>383144272</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>ADD - ONALENNA</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>income_distribution</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>Reinvest</t>
+        </is>
+      </c>
+      <c r="F102" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G102" s="3" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>383144272</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>ADD - ONALENNA</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>payment_method</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>Investor's bank account</t>
+        </is>
+      </c>
+      <c r="F103" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G103" s="3" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>383144272</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>ADD - ONALENNA</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t>form_type</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="inlineStr">
+        <is>
+          <t>Additional Investment Form</t>
+        </is>
+      </c>
+      <c r="F104" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G104" s="3" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>383144272</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>ADD - ONALENNA</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>fund_category</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>Money Market</t>
+        </is>
+      </c>
+      <c r="F105" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G105" s="3" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>383144272</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>ADD - ONALENNA</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t>processing_cutoff</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="inlineStr">
+        <is>
+          <t>1:00 PM</t>
+        </is>
+      </c>
+      <c r="F106" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G106" s="3" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>383144272</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>ADD - ONALENNA</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>fund_category_priority</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F107" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G107" s="3" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>383144272</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>ADD - ONALENNA</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
         <is>
           <t>bank_account_name</t>
         </is>
       </c>
-      <c r="E86" s="3" t="inlineStr">
-        <is>
-          <t>Onalenya Bogosiny</t>
-        </is>
-      </c>
-      <c r="F86" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="G86" s="3" t="inlineStr">
+      <c r="E108" s="3" t="inlineStr">
+        <is>
+          <t>Onalenna Bogosing</t>
+        </is>
+      </c>
+      <c r="F108" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="G108" s="3" t="inlineStr">
+        <is>
+          <t>backfilled:GSGF - ONALENNA BOGOSING</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="inlineStr">
+        <is>
+          <t>383144272</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>ADD - ONALENNA</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t>bank_name</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="inlineStr">
+        <is>
+          <t>ABSA</t>
+        </is>
+      </c>
+      <c r="F109" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="G109" s="3" t="inlineStr">
         <is>
           <t>backfilled:KYC - ONALENNA</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B87" s="4" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="3" t="inlineStr">
+        <is>
+          <t>383144272</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
         <is>
           <t>ADD - ONALENNA</t>
         </is>
       </c>
-      <c r="C87" s="4" t="inlineStr">
+      <c r="C110" s="3" t="inlineStr">
         <is>
           <t>ADD</t>
         </is>
       </c>
-      <c r="D87" s="4" t="inlineStr">
-        <is>
-          <t>bank_name</t>
-        </is>
-      </c>
-      <c r="E87" s="4" t="inlineStr">
-        <is>
-          <t>ABSA</t>
-        </is>
-      </c>
-      <c r="F87" s="4" t="n">
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>account_number</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t>1078631</t>
+        </is>
+      </c>
+      <c r="F110" s="3" t="n">
         <v>85</v>
       </c>
-      <c r="G87" s="4" t="inlineStr">
+      <c r="G110" s="3" t="inlineStr">
         <is>
           <t>backfilled:KYC - ONALENNA</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B88" s="4" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>383144272</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
         <is>
           <t>ADD - ONALENNA</t>
         </is>
       </c>
-      <c r="C88" s="4" t="inlineStr">
+      <c r="C111" s="3" t="inlineStr">
         <is>
           <t>ADD</t>
         </is>
       </c>
-      <c r="D88" s="4" t="inlineStr">
-        <is>
-          <t>account_number</t>
-        </is>
-      </c>
-      <c r="E88" s="4" t="inlineStr">
-        <is>
-          <t>1078631</t>
-        </is>
-      </c>
-      <c r="F88" s="4" t="n">
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>branch_name</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="inlineStr">
+        <is>
+          <t>Maun</t>
+        </is>
+      </c>
+      <c r="F111" s="3" t="n">
         <v>85</v>
       </c>
-      <c r="G88" s="4" t="inlineStr">
+      <c r="G111" s="3" t="inlineStr">
+        <is>
+          <t>backfilled:GSGF - ONALENNA BOGOSING</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>383144272</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>ADD - ONALENNA</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="inlineStr">
+        <is>
+          <t>branch_code</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="inlineStr">
+        <is>
+          <t>290167</t>
+        </is>
+      </c>
+      <c r="F112" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="G112" s="3" t="inlineStr">
         <is>
           <t>backfilled:KYC - ONALENNA</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B89" s="4" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>383144272</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
         <is>
           <t>ADD - ONALENNA</t>
         </is>
       </c>
-      <c r="C89" s="4" t="inlineStr">
+      <c r="C113" s="3" t="inlineStr">
         <is>
           <t>ADD</t>
         </is>
       </c>
-      <c r="D89" s="4" t="inlineStr">
-        <is>
-          <t>branch_name</t>
-        </is>
-      </c>
-      <c r="E89" s="4" t="inlineStr">
-        <is>
-          <t>MALL</t>
-        </is>
-      </c>
-      <c r="F89" s="4" t="n">
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>account_type_banking</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="inlineStr">
+        <is>
+          <t>Current</t>
+        </is>
+      </c>
+      <c r="F113" s="3" t="n">
         <v>85</v>
       </c>
-      <c r="G89" s="4" t="inlineStr">
-        <is>
-          <t>backfilled:KYC - ONALENNA</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B90" s="4" t="inlineStr">
-        <is>
-          <t>ADD - ONALENNA</t>
-        </is>
-      </c>
-      <c r="C90" s="4" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="D90" s="4" t="inlineStr">
-        <is>
-          <t>branch_code</t>
-        </is>
-      </c>
-      <c r="E90" s="4" t="inlineStr">
-        <is>
-          <t>290167</t>
-        </is>
-      </c>
-      <c r="F90" s="4" t="n">
-        <v>85</v>
-      </c>
-      <c r="G90" s="4" t="inlineStr">
-        <is>
-          <t>backfilled:KYC - ONALENNA</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="4" t="inlineStr">
-        <is>
-          <t>38344272</t>
-        </is>
-      </c>
-      <c r="B91" s="4" t="inlineStr">
-        <is>
-          <t>ADD - ONALENNA</t>
-        </is>
-      </c>
-      <c r="C91" s="4" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="D91" s="4" t="inlineStr">
-        <is>
-          <t>account_type_banking</t>
-        </is>
-      </c>
-      <c r="E91" s="4" t="inlineStr">
-        <is>
-          <t>Current</t>
-        </is>
-      </c>
-      <c r="F91" s="4" t="n">
-        <v>85</v>
-      </c>
-      <c r="G91" s="4" t="inlineStr">
+      <c r="G113" s="3" t="inlineStr">
         <is>
           <t>backfilled:KYC - ONALENNA</t>
         </is>
@@ -7204,7 +7824,7 @@
     <col width="27" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="35" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
     <col width="45" customWidth="1" min="11" max="11"/>
@@ -7288,7 +7908,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-07T17:59:40</t>
+          <t>2026-07-08T10:35:10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -7298,7 +7918,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>KYC_38344272_BOGOSING_20260707_VALIDATIONFAILEDID_EXPIRY_DATE.pdf</t>
+          <t>KYC_38344272_BOGOSING_20260708_VALIDATIONFAILEDID_EXPIRY_DATE.pdf</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -7331,12 +7951,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-07T17:58:29</t>
+          <t>2026-07-08T10:33:03</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\KYC\2026\July\KYC_38344272_BOGOSING_20260707_VALIDATIONFAILEDID_EXPIRY_DATE.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\KYC\2026\July\KYC_38344272_BOGOSING_20260708_VALIDATIONFAILEDID_EXPIRY_DATE.pdf</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -7354,7 +7974,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-07T17:59:40</t>
+          <t>2026-07-08T10:35:10</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -7364,7 +7984,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DIS_GSG_38344272_BOGOSING_20260707.pdf</t>
+          <t>DIS_GSG_388144272_BOGOSING_20260708.pdf</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -7377,7 +7997,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>WARNING</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -7393,12 +8013,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-07-07T17:58:29</t>
+          <t>2026-07-08T10:33:03</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\Disinvestments\GSGF\2026\Q3-2026\30-Sep-2026\Captured\DIS_GSG_38344272_BOGOSING_20260707.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\Disinvestments\GSGF\2026\Q3-2026\30-Sep-2026\Captured\DIS_GSG_388144272_BOGOSING_20260708.pdf</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -7416,7 +8036,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-07T17:59:40</t>
+          <t>2026-07-08T10:35:10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -7426,7 +8046,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DIS_38344272_BOGOSING_20260707.pdf</t>
+          <t>DIS_383144272_BOGOSING_20260708.pdf</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -7455,12 +8075,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-07-07T17:58:29</t>
+          <t>2026-07-08T10:33:03</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\Disinvestments\2026\July\07-Jul-2026\Non-Money Market\Captured\DIS_38344272_BOGOSING_20260707.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\Disinvestments\2026\July\08-Jul-2026\Non-Money Market\Captured\DIS_383144272_BOGOSING_20260708.pdf</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -7478,7 +8098,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-07T17:59:40</t>
+          <t>2026-07-08T10:35:10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -7488,7 +8108,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DEBIT_38344272_BOGOSING_20260707_VALIDATIONFAILEDINSTRUCTION_TYPEID_EXPIRY_DATE.pdf</t>
+          <t>DEBIT_363144272_BOGOSING_20260708_VALIDATIONFAILEDID_EXPIRY_DATE.pdf</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -7511,7 +8131,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Validation failed: instruction_type, id_expiry_date</t>
+          <t>Validation failed: id_expiry_date</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -7521,12 +8141,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-07-07T17:58:29</t>
+          <t>2026-07-08T10:33:03</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\Debit Orders\2026\July\Send to AWD\07-Jul-2026\DEBIT_38344272_BOGOSING_20260707_VALIDATIONFAILEDINSTRUCTION_TYPEID_EXPIRY_DATE.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\Debit Orders\2026\July\Send to AWD\08-Jul-2026\DEBIT_363144272_BOGOSING_20260708_VALIDATIONFAILEDID_EXPIRY_DATE.pdf</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -7544,7 +8164,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-07T17:59:40</t>
+          <t>2026-07-08T10:35:10</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -7554,7 +8174,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ADD_38344272_BOGOSING_20260707_VALIDATIONFAILEDFUND_NUMBER.pdf</t>
+          <t>ADD_383144272_BOITSHWARE_20260708.pdf</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -7567,19 +8187,15 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rejected</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Validation failed: fund_number</t>
-        </is>
-      </c>
+          <t>Captured</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Email</t>
@@ -7587,12 +8203,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-07-07T17:58:29</t>
+          <t>2026-07-08T10:33:03</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\Additional Investments\2026\July\07-Jul-2026\NonMoneyMarket\Captured\Rejected\ADD_38344272_BOGOSING_20260707_VALIDATIONFAILEDFUND_NUMBER.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\Additional Investments\2026\July\08-Jul-2026\MoneyMarket\Captured\ADD_383144272_BOITSHWARE_20260708.pdf</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">

--- a/output/BIFM_UT_Processing_Report.xlsx
+++ b/output/BIFM_UT_Processing_Report.xlsx
@@ -471,11 +471,11 @@
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="26" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="37" customWidth="1" min="15" max="15"/>
+    <col width="29" customWidth="1" min="15" max="15"/>
     <col width="13" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
@@ -648,7 +648,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>obogosinge@gmail.com</t>
+          <t>obogosing@gmail.com</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>BIFM Global Sustainable Growth Fund</t>
+          <t>Bifm Pula Money Market Fund</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -740,7 +740,7 @@
     <col width="21" customWidth="1" min="17" max="17"/>
     <col width="15" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
-    <col width="23" customWidth="1" min="20" max="20"/>
+    <col width="25" customWidth="1" min="20" max="20"/>
     <col width="13" customWidth="1" min="21" max="21"/>
     <col width="18" customWidth="1" min="22" max="22"/>
     <col width="17" customWidth="1" min="23" max="23"/>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T10:33:03</t>
+          <t>2026-07-08T10:52:43</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
-          <t>obogosinge@gmail.com</t>
+          <t>obogosing@gmail.com</t>
         </is>
       </c>
       <c r="U2" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>Onalenya Bogosiny</t>
+          <t>Onalenya Bogosing</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>2026-07-08T10:33:03</t>
+          <t>2026-07-08T10:52:43</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -1412,164 +1412,164 @@
       <c r="BD3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>DIS - ONALENNA BOGOSING</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>DIS</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Disinvestment Form (Standard)</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>3831 44272</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Onalenna Bogosing</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>222922316</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>BIFM Global Sustainable Growth Fund</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Bifm Pula Money Market Fund</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>1674982</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>Unknown - Fund Name Not Extracted</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Money Market</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>1:00 PM</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>Captured</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr"/>
-      <c r="O4" s="4" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr"/>
+      <c r="O4" s="3" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="P4" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-08T10:33:03</t>
-        </is>
-      </c>
-      <c r="Q4" s="4" t="inlineStr">
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-08T10:52:43</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
         <is>
           <t>marvel.ai-local-poc</t>
         </is>
       </c>
-      <c r="R4" s="4" t="inlineStr"/>
-      <c r="S4" s="4" t="inlineStr">
+      <c r="R4" s="3" t="inlineStr"/>
+      <c r="S4" s="3" t="inlineStr">
         <is>
           <t>76749303</t>
         </is>
       </c>
-      <c r="T4" s="4" t="inlineStr">
-        <is>
-          <t>obogosinge@gmail.com</t>
-        </is>
-      </c>
-      <c r="U4" s="4" t="inlineStr"/>
-      <c r="V4" s="4" t="inlineStr"/>
-      <c r="W4" s="4" t="b">
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>obogosing@gmail.com</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr"/>
+      <c r="V4" s="3" t="inlineStr"/>
+      <c r="W4" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="X4" s="4" t="inlineStr">
+      <c r="X4" s="3" t="inlineStr">
         <is>
           <t>1033921</t>
         </is>
       </c>
-      <c r="Y4" s="4" t="inlineStr">
+      <c r="Y4" s="3" t="inlineStr">
         <is>
           <t>Current</t>
         </is>
       </c>
-      <c r="Z4" s="4" t="inlineStr">
+      <c r="Z4" s="3" t="inlineStr">
         <is>
           <t>Onalenna Bogosing</t>
         </is>
       </c>
-      <c r="AA4" s="4" t="inlineStr">
+      <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>NBSA</t>
         </is>
       </c>
-      <c r="AB4" s="4" t="inlineStr">
+      <c r="AB4" s="3" t="inlineStr">
         <is>
           <t>290167</t>
         </is>
       </c>
-      <c r="AC4" s="4" t="inlineStr">
+      <c r="AC4" s="3" t="inlineStr">
         <is>
           <t>Maun</t>
         </is>
       </c>
-      <c r="AD4" s="4" t="inlineStr"/>
-      <c r="AE4" s="4" t="inlineStr"/>
-      <c r="AF4" s="4" t="inlineStr"/>
-      <c r="AG4" s="4" t="n">
+      <c r="AD4" s="3" t="inlineStr"/>
+      <c r="AE4" s="3" t="inlineStr"/>
+      <c r="AF4" s="3" t="inlineStr"/>
+      <c r="AG4" s="3" t="n">
         <v>200000</v>
       </c>
-      <c r="AH4" s="4" t="inlineStr"/>
-      <c r="AI4" s="4" t="inlineStr"/>
-      <c r="AJ4" s="4" t="inlineStr"/>
-      <c r="AK4" s="4" t="n">
-        <v>99</v>
-      </c>
-      <c r="AL4" s="4" t="inlineStr"/>
-      <c r="AM4" s="4" t="inlineStr"/>
-      <c r="AN4" s="4" t="inlineStr">
+      <c r="AH4" s="3" t="inlineStr"/>
+      <c r="AI4" s="3" t="inlineStr"/>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL4" s="3" t="inlineStr"/>
+      <c r="AM4" s="3" t="inlineStr"/>
+      <c r="AN4" s="3" t="inlineStr">
         <is>
           <t>Partial Withdrawal</t>
         </is>
       </c>
-      <c r="AO4" s="4" t="inlineStr"/>
-      <c r="AP4" s="4" t="inlineStr"/>
-      <c r="AQ4" s="4" t="inlineStr"/>
-      <c r="AR4" s="4" t="inlineStr"/>
-      <c r="AS4" s="4" t="inlineStr"/>
-      <c r="AT4" s="4" t="inlineStr"/>
-      <c r="AU4" s="4" t="inlineStr"/>
-      <c r="AV4" s="4" t="inlineStr"/>
-      <c r="AW4" s="4" t="inlineStr"/>
-      <c r="AX4" s="4" t="inlineStr"/>
-      <c r="AY4" s="4" t="inlineStr"/>
-      <c r="AZ4" s="4" t="inlineStr"/>
-      <c r="BA4" s="4" t="inlineStr"/>
-      <c r="BB4" s="4" t="inlineStr"/>
-      <c r="BC4" s="4" t="inlineStr"/>
-      <c r="BD4" s="4" t="inlineStr"/>
+      <c r="AO4" s="3" t="inlineStr"/>
+      <c r="AP4" s="3" t="inlineStr"/>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr"/>
+      <c r="AS4" s="3" t="inlineStr"/>
+      <c r="AT4" s="3" t="inlineStr"/>
+      <c r="AU4" s="3" t="inlineStr"/>
+      <c r="AV4" s="3" t="inlineStr"/>
+      <c r="AW4" s="3" t="inlineStr"/>
+      <c r="AX4" s="3" t="inlineStr"/>
+      <c r="AY4" s="3" t="inlineStr"/>
+      <c r="AZ4" s="3" t="inlineStr"/>
+      <c r="BA4" s="3" t="inlineStr"/>
+      <c r="BB4" s="3" t="inlineStr"/>
+      <c r="BC4" s="3" t="inlineStr"/>
+      <c r="BD4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1605,7 +1605,7 @@
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>BIFM Global Sustainable Growth Fund</t>
+          <t>Bifm Pula Money Market Fund</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T10:33:03</t>
+          <t>2026-07-08T10:52:43</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="AL5" s="2" t="inlineStr">
         <is>
-          <t>02/11/2016</t>
+          <t>22/11/2016</t>
         </is>
       </c>
       <c r="AM5" s="2" t="inlineStr"/>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Onalenna Boitshware</t>
+          <t>Onalenna Boitshwarelo</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr"/>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>2026-07-08T10:33:03</t>
+          <t>2026-07-08T10:52:43</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t>oboitshware@gmail.com</t>
+          <t>oboitshwarelo@gmail.com</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr"/>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>obogosinge@gmail.com</t>
+          <t>obogosing@gmail.com</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>obogosinge@gmail.com</t>
+          <t>obogosing@gmail.com</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -2494,41 +2494,37 @@
       <c r="G15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>3831 44272</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>DIS - ONALENNA BOGOSING</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>DIS</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>fund_category</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>Unknown - Fund Name Not Extracted</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>Fund category could not be determined - fund name unclear</t>
-        </is>
-      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Money Market</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -2553,7 +2549,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>02/11/2016</t>
+          <t>22/11/2016</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2726,7 +2722,7 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>oboitshware@gmail.com</t>
+          <t>oboitshwarelo@gmail.com</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
@@ -4354,7 +4350,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>obogosinge@gmail.com</t>
+          <t>obogosing@gmail.com</t>
         </is>
       </c>
       <c r="F14" s="3" t="n">
@@ -4459,11 +4455,11 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Onalenya Bogosiny</t>
+          <t>Onalenya Bogosing</t>
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
@@ -5735,11 +5731,13 @@
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>disinvestment_amount</t>
-        </is>
-      </c>
-      <c r="E54" s="3" t="n">
-        <v>200000</v>
+          <t>fund_name</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Bifm Pula Money Market Fund</t>
+        </is>
       </c>
       <c r="F54" s="3" t="n">
         <v>98</v>
@@ -5768,11 +5766,11 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>account_closure</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="b">
-        <v>0</v>
+          <t>disinvestment_amount</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>200000</v>
       </c>
       <c r="F55" s="3" t="n">
         <v>98</v>
@@ -5801,158 +5799,156 @@
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
+          <t>account_closure</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>3831 44272</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>DIS - ONALENNA BOGOSING</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
           <t>bank_account_name</t>
         </is>
       </c>
-      <c r="E56" s="3" t="inlineStr">
+      <c r="E57" s="3" t="inlineStr">
         <is>
           <t>Onalenna Bogosing</t>
         </is>
       </c>
-      <c r="F56" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="G56" s="3" t="inlineStr">
-        <is>
-          <t>extracted</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="4" t="inlineStr">
+      <c r="F57" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
         <is>
           <t>3831 44272</t>
         </is>
       </c>
-      <c r="B57" s="4" t="inlineStr">
+      <c r="B58" s="4" t="inlineStr">
         <is>
           <t>DIS - ONALENNA BOGOSING</t>
         </is>
       </c>
-      <c r="C57" s="4" t="inlineStr">
+      <c r="C58" s="4" t="inlineStr">
         <is>
           <t>DIS</t>
         </is>
       </c>
-      <c r="D57" s="4" t="inlineStr">
+      <c r="D58" s="4" t="inlineStr">
         <is>
           <t>bank_name</t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr">
+      <c r="E58" s="4" t="inlineStr">
         <is>
           <t>NBSA</t>
         </is>
       </c>
-      <c r="F57" s="4" t="n">
+      <c r="F58" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="G57" s="4" t="inlineStr">
-        <is>
-          <t>extracted</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="3" t="inlineStr">
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t>3831 44272</t>
         </is>
       </c>
-      <c r="B58" s="3" t="inlineStr">
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t>DIS - ONALENNA BOGOSING</t>
         </is>
       </c>
-      <c r="C58" s="3" t="inlineStr">
+      <c r="C59" s="3" t="inlineStr">
         <is>
           <t>DIS</t>
         </is>
       </c>
-      <c r="D58" s="3" t="inlineStr">
+      <c r="D59" s="3" t="inlineStr">
         <is>
           <t>account_number</t>
         </is>
       </c>
-      <c r="E58" s="3" t="inlineStr">
+      <c r="E59" s="3" t="inlineStr">
         <is>
           <t>1033921</t>
         </is>
       </c>
-      <c r="F58" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="G58" s="3" t="inlineStr">
-        <is>
-          <t>extracted</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="4" t="inlineStr">
+      <c r="F59" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
         <is>
           <t>3831 44272</t>
         </is>
       </c>
-      <c r="B59" s="4" t="inlineStr">
+      <c r="B60" s="4" t="inlineStr">
         <is>
           <t>DIS - ONALENNA BOGOSING</t>
         </is>
       </c>
-      <c r="C59" s="4" t="inlineStr">
+      <c r="C60" s="4" t="inlineStr">
         <is>
           <t>DIS</t>
         </is>
       </c>
-      <c r="D59" s="4" t="inlineStr">
+      <c r="D60" s="4" t="inlineStr">
         <is>
           <t>branch_name</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
+      <c r="E60" s="4" t="inlineStr">
         <is>
           <t>Maun</t>
         </is>
       </c>
-      <c r="F59" s="4" t="n">
+      <c r="F60" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="G59" s="4" t="inlineStr">
-        <is>
-          <t>extracted</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="3" t="inlineStr">
-        <is>
-          <t>3831 44272</t>
-        </is>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t>DIS - ONALENNA BOGOSING</t>
-        </is>
-      </c>
-      <c r="C60" s="3" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
-      </c>
-      <c r="D60" s="3" t="inlineStr">
-        <is>
-          <t>branch_code</t>
-        </is>
-      </c>
-      <c r="E60" s="3" t="inlineStr">
-        <is>
-          <t>290167</t>
-        </is>
-      </c>
-      <c r="F60" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="G60" s="3" t="inlineStr">
+      <c r="G60" s="4" t="inlineStr">
         <is>
           <t>extracted</t>
         </is>
@@ -5976,12 +5972,12 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>form_type</t>
+          <t>branch_code</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Disinvestment Form (Standard)</t>
+          <t>290167</t>
         </is>
       </c>
       <c r="F61" s="3" t="n">
@@ -6011,12 +6007,12 @@
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>fund_category</t>
+          <t>form_type</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>Unknown - Fund Name Not Extracted</t>
+          <t>Disinvestment Form (Standard)</t>
         </is>
       </c>
       <c r="F62" s="3" t="n">
@@ -6046,12 +6042,12 @@
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>processing_cutoff</t>
+          <t>fund_category</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Money Market</t>
         </is>
       </c>
       <c r="F63" s="3" t="n">
@@ -6081,11 +6077,13 @@
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>fund_category_priority</t>
-        </is>
-      </c>
-      <c r="E64" s="3" t="n">
-        <v>99</v>
+          <t>processing_cutoff</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>1:00 PM</t>
+        </is>
       </c>
       <c r="F64" s="3" t="n">
         <v>98</v>
@@ -6114,13 +6112,11 @@
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>instruction_mode</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="inlineStr">
-        <is>
-          <t>Partial Withdrawal</t>
-        </is>
+          <t>fund_category_priority</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="F65" s="3" t="n">
         <v>98</v>
@@ -6149,20 +6145,20 @@
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>instruction_mode</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>obogosinge@gmail.com</t>
+          <t>Partial Withdrawal</t>
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>backfilled:KYC - ONALENNA</t>
+          <t>extracted</t>
         </is>
       </c>
     </row>
@@ -6184,12 +6180,12 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>fund_name</t>
+          <t>email</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>BIFM Global Sustainable Growth Fund</t>
+          <t>obogosing@gmail.com</t>
         </is>
       </c>
       <c r="F67" s="3" t="n">
@@ -6197,7 +6193,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>backfilled:GSGF - ONALENNA BOGOSING</t>
+          <t>backfilled:KYC - ONALENNA</t>
         </is>
       </c>
     </row>
@@ -6364,7 +6360,7 @@
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>02/11/2016</t>
+          <t>22/11/2016</t>
         </is>
       </c>
       <c r="F72" s="3" t="n">
@@ -6852,7 +6848,7 @@
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>BIFM Global Sustainable Growth Fund</t>
+          <t>Bifm Pula Money Market Fund</t>
         </is>
       </c>
       <c r="F86" s="3" t="n">
@@ -6860,7 +6856,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>backfilled:GSGF - ONALENNA BOGOSING</t>
+          <t>backfilled:DIS - ONALENNA BOGOSING</t>
         </is>
       </c>
     </row>
@@ -7132,7 +7128,7 @@
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>Onalenna Boitshware</t>
+          <t>Onalenna Boitshwarelo</t>
         </is>
       </c>
       <c r="F94" s="3" t="n">
@@ -7202,7 +7198,7 @@
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>oboitshware@gmail.com</t>
+          <t>oboitshwarelo@gmail.com</t>
         </is>
       </c>
       <c r="F96" s="3" t="n">
@@ -7908,7 +7904,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-08T10:35:10</t>
+          <t>2026-07-08T10:56:14</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -7918,7 +7914,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>KYC_38344272_BOGOSING_20260708_VALIDATIONFAILEDID_EXPIRY_DATE.pdf</t>
+          <t>KYC_38344272_BOGOSING_20260708_VALIDATIONFAILEDID_EXPIRY_DATE_1.pdf</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -7951,12 +7947,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-08T10:33:03</t>
+          <t>2026-07-08T10:52:43</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\KYC\2026\July\KYC_38344272_BOGOSING_20260708_VALIDATIONFAILEDID_EXPIRY_DATE.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\KYC\2026\July\KYC_38344272_BOGOSING_20260708_VALIDATIONFAILEDID_EXPIRY_DATE_1.pdf</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -7974,7 +7970,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-08T10:35:10</t>
+          <t>2026-07-08T10:56:15</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -7984,7 +7980,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DIS_GSG_388144272_BOGOSING_20260708.pdf</t>
+          <t>DIS_GSG_388144272_BOGOSING_20260708_1.pdf</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -8013,12 +8009,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-07-08T10:33:03</t>
+          <t>2026-07-08T10:52:43</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\Disinvestments\GSGF\2026\Q3-2026\30-Sep-2026\Captured\DIS_GSG_388144272_BOGOSING_20260708.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\Disinvestments\GSGF\2026\Q3-2026\30-Sep-2026\Captured\DIS_GSG_388144272_BOGOSING_20260708_1.pdf</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -8036,7 +8032,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-08T10:35:10</t>
+          <t>2026-07-08T10:56:15</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -8059,7 +8055,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>WARNING</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -8075,12 +8071,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-07-08T10:33:03</t>
+          <t>2026-07-08T10:52:43</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\Disinvestments\2026\July\08-Jul-2026\Non-Money Market\Captured\DIS_383144272_BOGOSING_20260708.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\Disinvestments\2026\July\08-Jul-2026\Money Market\Captured\DIS_383144272_BOGOSING_20260708.pdf</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -8098,7 +8094,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-08T10:35:10</t>
+          <t>2026-07-08T10:56:15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -8108,7 +8104,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DEBIT_363144272_BOGOSING_20260708_VALIDATIONFAILEDID_EXPIRY_DATE.pdf</t>
+          <t>DEBIT_363144272_BOGOSING_20260708_VALIDATIONFAILEDID_EXPIRY_DATE_1.pdf</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -8141,12 +8137,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-07-08T10:33:03</t>
+          <t>2026-07-08T10:52:43</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\Debit Orders\2026\July\Send to AWD\08-Jul-2026\DEBIT_363144272_BOGOSING_20260708_VALIDATIONFAILEDID_EXPIRY_DATE.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\Debit Orders\2026\July\Send to AWD\08-Jul-2026\DEBIT_363144272_BOGOSING_20260708_VALIDATIONFAILEDID_EXPIRY_DATE_1.pdf</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -8164,7 +8160,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-08T10:35:10</t>
+          <t>2026-07-08T10:56:15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -8174,7 +8170,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ADD_383144272_BOITSHWARE_20260708.pdf</t>
+          <t>ADD_383144272_BOITSHWARELO_20260708.pdf</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -8203,12 +8199,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-07-08T10:33:03</t>
+          <t>2026-07-08T10:52:43</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\Additional Investments\2026\July\08-Jul-2026\MoneyMarket\Captured\ADD_383144272_BOITSHWARE_20260708.pdf</t>
+          <t>C:\Users\dhruv\OneDrive\Documents\GitHub\BIFMPoC\output\filed_documents\Additional Investments\2026\July\08-Jul-2026\MoneyMarket\Captured\ADD_383144272_BOITSHWARELO_20260708.pdf</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
